--- a/output/Nasarawa/results.xlsx
+++ b/output/Nasarawa/results.xlsx
@@ -3181,7 +3181,11 @@
         <v>161315</v>
       </c>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>1781968172547</t>
+        </is>
+      </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
@@ -3202,7 +3206,11 @@
         <v>0</v>
       </c>
       <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6013/656521/68761de4-2c76-421f-9e82-f72ce0c2776d.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4924,7 +4932,11 @@
         <v>86134</v>
       </c>
       <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>1781968186456</t>
+        </is>
+      </c>
       <c r="O54" t="n">
         <v>0</v>
       </c>
@@ -4945,7 +4957,11 @@
         <v>0</v>
       </c>
       <c r="V54" t="inlineStr"/>
-      <c r="W54" t="inlineStr"/>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6012/85070/53d7645d-43b6-4499-b506-028b6bd69063.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5505,7 +5521,11 @@
         <v>86141</v>
       </c>
       <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>1781968197609</t>
+        </is>
+      </c>
       <c r="O61" t="n">
         <v>0</v>
       </c>
@@ -5526,7 +5546,11 @@
         <v>0</v>
       </c>
       <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr"/>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6012/85077/522ca130-01ab-4d02-b495-362c1fd75a1c.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5754,7 +5778,11 @@
         <v>161272</v>
       </c>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>1781968263266</t>
+        </is>
+      </c>
       <c r="O64" t="n">
         <v>0</v>
       </c>
@@ -5775,7 +5803,11 @@
         <v>0</v>
       </c>
       <c r="V64" t="inlineStr"/>
-      <c r="W64" t="inlineStr"/>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6012/656543/2a1d9395-52f9-40aa-941a-9ff33dad4117.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5837,7 +5869,11 @@
         <v>161273</v>
       </c>
       <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>1781970490370</t>
+        </is>
+      </c>
       <c r="O65" t="n">
         <v>0</v>
       </c>
@@ -5858,7 +5894,11 @@
         <v>0</v>
       </c>
       <c r="V65" t="inlineStr"/>
-      <c r="W65" t="inlineStr"/>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6012/656544/49e70484-3190-43e4-a822-fa0b4d8afe6a.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6169,7 +6209,11 @@
         <v>161277</v>
       </c>
       <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>1781968283938</t>
+        </is>
+      </c>
       <c r="O69" t="n">
         <v>0</v>
       </c>
@@ -6190,7 +6234,11 @@
         <v>0</v>
       </c>
       <c r="V69" t="inlineStr"/>
-      <c r="W69" t="inlineStr"/>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6012/656548/fc0c76e8-e454-4ea9-9466-e61c8867335d.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6252,7 +6300,11 @@
         <v>161278</v>
       </c>
       <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>1781968245890</t>
+        </is>
+      </c>
       <c r="O70" t="n">
         <v>0</v>
       </c>
@@ -6273,7 +6325,11 @@
         <v>0</v>
       </c>
       <c r="V70" t="inlineStr"/>
-      <c r="W70" t="inlineStr"/>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6012/656549/91f875e3-6b96-4ec9-9e37-f42877da362f.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -7580,7 +7636,11 @@
         <v>161294</v>
       </c>
       <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>1781968171347</t>
+        </is>
+      </c>
       <c r="O86" t="n">
         <v>0</v>
       </c>
@@ -7601,7 +7661,11 @@
         <v>0</v>
       </c>
       <c r="V86" t="inlineStr"/>
-      <c r="W86" t="inlineStr"/>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6012/656565/be68f725-cb50-44e1-8d5b-977ee4604ace.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -7912,7 +7976,11 @@
         <v>161298</v>
       </c>
       <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>1781970494738</t>
+        </is>
+      </c>
       <c r="O90" t="n">
         <v>0</v>
       </c>
@@ -7933,7 +8001,11 @@
         <v>0</v>
       </c>
       <c r="V90" t="inlineStr"/>
-      <c r="W90" t="inlineStr"/>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6012/656569/b6b0702d-b47a-43e4-8548-13b7f9b59a93.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -10900,7 +10972,11 @@
         <v>161221</v>
       </c>
       <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>1781970122827</t>
+        </is>
+      </c>
       <c r="O126" t="n">
         <v>0</v>
       </c>
@@ -10921,7 +10997,11 @@
         <v>0</v>
       </c>
       <c r="V126" t="inlineStr"/>
-      <c r="W126" t="inlineStr"/>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6004/656587/32afeb4f-de9b-4cba-9212-6cc986e4e636.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -17469,7 +17549,11 @@
         <v>161248</v>
       </c>
       <c r="M205" t="inlineStr"/>
-      <c r="N205" t="inlineStr"/>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>1781968226118</t>
+        </is>
+      </c>
       <c r="O205" t="n">
         <v>0</v>
       </c>
@@ -17490,7 +17574,11 @@
         <v>0</v>
       </c>
       <c r="V205" t="inlineStr"/>
-      <c r="W205" t="inlineStr"/>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6009/656634/0e076a02-b761-4c9b-a261-0d40f73f6f4e.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -26267,7 +26355,11 @@
         <v>87246</v>
       </c>
       <c r="M311" t="inlineStr"/>
-      <c r="N311" t="inlineStr"/>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>1781970500433</t>
+        </is>
+      </c>
       <c r="O311" t="n">
         <v>0</v>
       </c>
@@ -26288,7 +26380,11 @@
         <v>0</v>
       </c>
       <c r="V311" t="inlineStr"/>
-      <c r="W311" t="inlineStr"/>
+      <c r="W311" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6112/86157/42497fe2-317d-4ef9-9c7a-7ab5b5bbe9aa.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -29172,7 +29268,11 @@
         <v>87218</v>
       </c>
       <c r="M346" t="inlineStr"/>
-      <c r="N346" t="inlineStr"/>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>1781968509699</t>
+        </is>
+      </c>
       <c r="O346" t="n">
         <v>0</v>
       </c>
@@ -29193,7 +29293,11 @@
         <v>0</v>
       </c>
       <c r="V346" t="inlineStr"/>
-      <c r="W346" t="inlineStr"/>
+      <c r="W346" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6109/86129/220574d4-dd1f-4551-ae28-3cb2edbcc1e3.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -33322,7 +33426,11 @@
         <v>162598</v>
       </c>
       <c r="M396" t="inlineStr"/>
-      <c r="N396" t="inlineStr"/>
+      <c r="N396" t="inlineStr">
+        <is>
+          <t>1781968315573</t>
+        </is>
+      </c>
       <c r="O396" t="n">
         <v>0</v>
       </c>
@@ -33343,7 +33451,11 @@
         <v>0</v>
       </c>
       <c r="V396" t="inlineStr"/>
-      <c r="W396" t="inlineStr"/>
+      <c r="W396" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6105/657959/cfa5863c-3c18-4f85-9a8e-2cb3fb81ec73.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -36559,7 +36671,11 @@
         <v>162629</v>
       </c>
       <c r="M435" t="inlineStr"/>
-      <c r="N435" t="inlineStr"/>
+      <c r="N435" t="inlineStr">
+        <is>
+          <t>1781970498294</t>
+        </is>
+      </c>
       <c r="O435" t="n">
         <v>0</v>
       </c>
@@ -36580,7 +36696,11 @@
         <v>0</v>
       </c>
       <c r="V435" t="inlineStr"/>
-      <c r="W435" t="inlineStr"/>
+      <c r="W435" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6108/657980/6843e8d9-5598-4ec2-86d5-3e19fcafa8af.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -37804,7 +37924,11 @@
         <v>162672</v>
       </c>
       <c r="M450" t="inlineStr"/>
-      <c r="N450" t="inlineStr"/>
+      <c r="N450" t="inlineStr">
+        <is>
+          <t>1781968869947</t>
+        </is>
+      </c>
       <c r="O450" t="n">
         <v>0</v>
       </c>
@@ -37825,7 +37949,11 @@
         <v>0</v>
       </c>
       <c r="V450" t="inlineStr"/>
-      <c r="W450" t="inlineStr"/>
+      <c r="W450" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6115/657986/c7202e99-ff20-4006-8cb4-d999e70705e0.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -47764,7 +47892,11 @@
         <v>162945</v>
       </c>
       <c r="M570" t="inlineStr"/>
-      <c r="N570" t="inlineStr"/>
+      <c r="N570" t="inlineStr">
+        <is>
+          <t>1781970490034</t>
+        </is>
+      </c>
       <c r="O570" t="n">
         <v>0</v>
       </c>
@@ -47785,7 +47917,11 @@
         <v>0</v>
       </c>
       <c r="V570" t="inlineStr"/>
-      <c r="W570" t="inlineStr"/>
+      <c r="W570" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6147/658253/db2462de-c7dc-49d4-8591-a6378ce6053d.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">

--- a/output/Nasarawa/results.xlsx
+++ b/output/Nasarawa/results.xlsx
@@ -4766,7 +4766,11 @@
         <v>161334</v>
       </c>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>1781971564044</t>
+        </is>
+      </c>
       <c r="O52" t="n">
         <v>0</v>
       </c>
@@ -4787,7 +4791,11 @@
         <v>0</v>
       </c>
       <c r="V52" t="inlineStr"/>
-      <c r="W52" t="inlineStr"/>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6013/656540/02dffaf6-88c7-4d63-ae15-e4cccaaee476.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5695,7 +5703,11 @@
         <v>161271</v>
       </c>
       <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>1781971386613</t>
+        </is>
+      </c>
       <c r="O63" t="n">
         <v>0</v>
       </c>
@@ -5716,7 +5728,11 @@
         <v>0</v>
       </c>
       <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr"/>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6012/656542/e1a3106b-e81a-4a07-a9a3-0e3d78733a24.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -8399,7 +8415,11 @@
         <v>161303</v>
       </c>
       <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>1781971024325</t>
+        </is>
+      </c>
       <c r="O95" t="n">
         <v>0</v>
       </c>
@@ -8420,7 +8440,11 @@
         <v>0</v>
       </c>
       <c r="V95" t="inlineStr"/>
-      <c r="W95" t="inlineStr"/>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6012/656574/7a8ec192-0bb1-4921-8549-4e686be22032.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -10889,7 +10913,11 @@
         <v>161220</v>
       </c>
       <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>1781971926166</t>
+        </is>
+      </c>
       <c r="O125" t="n">
         <v>0</v>
       </c>
@@ -10910,7 +10938,11 @@
         <v>0</v>
       </c>
       <c r="V125" t="inlineStr"/>
-      <c r="W125" t="inlineStr"/>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6004/656586/276d3d9a-40f2-4b34-9d2c-23179e1af277.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -38098,7 +38130,11 @@
         <v>162674</v>
       </c>
       <c r="M452" t="inlineStr"/>
-      <c r="N452" t="inlineStr"/>
+      <c r="N452" t="inlineStr">
+        <is>
+          <t>1781971564757</t>
+        </is>
+      </c>
       <c r="O452" t="n">
         <v>0</v>
       </c>
@@ -38119,7 +38155,11 @@
         <v>0</v>
       </c>
       <c r="V452" t="inlineStr"/>
-      <c r="W452" t="inlineStr"/>
+      <c r="W452" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6115/657988/0a3b4ef0-24be-4875-b6d1-adde5ee5440a.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">

--- a/output/Nasarawa/results.xlsx
+++ b/output/Nasarawa/results.xlsx
@@ -2766,7 +2766,11 @@
         <v>161310</v>
       </c>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>1781972825205</t>
+        </is>
+      </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
@@ -2787,7 +2791,11 @@
         <v>0</v>
       </c>
       <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6013/656516/fbf2fc19-f3ad-4c87-9bdd-52ad5166f3fc.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3015,7 +3023,11 @@
         <v>161313</v>
       </c>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>1781972464449</t>
+        </is>
+      </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
@@ -3036,7 +3048,11 @@
         <v>0</v>
       </c>
       <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6013/656519/02a8662a-88a3-4db7-800a-70e278a814c0.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3770,7 +3786,11 @@
         <v>161322</v>
       </c>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>1781971930635</t>
+        </is>
+      </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
@@ -3791,7 +3811,11 @@
         <v>0</v>
       </c>
       <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6013/656528/76381a77-1346-4ecc-94bd-82ccbe795d5c.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5197,7 +5221,11 @@
         <v>86137</v>
       </c>
       <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>1781973254769</t>
+        </is>
+      </c>
       <c r="O57" t="n">
         <v>0</v>
       </c>
@@ -5218,7 +5246,11 @@
         <v>0</v>
       </c>
       <c r="V57" t="inlineStr"/>
-      <c r="W57" t="inlineStr"/>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6012/85073/23c1a755-d81d-44e4-92e4-72a5742a0af4.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6656,7 +6688,11 @@
         <v>161282</v>
       </c>
       <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>1781973401809</t>
+        </is>
+      </c>
       <c r="O74" t="n">
         <v>0</v>
       </c>
@@ -6677,7 +6713,11 @@
         <v>0</v>
       </c>
       <c r="V74" t="inlineStr"/>
-      <c r="W74" t="inlineStr"/>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6012/656553/0209c501-5905-4676-9e36-3ede60af1c72.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6739,7 +6779,11 @@
         <v>161283</v>
       </c>
       <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>1781973368325</t>
+        </is>
+      </c>
       <c r="O75" t="n">
         <v>0</v>
       </c>
@@ -6760,7 +6804,11 @@
         <v>0</v>
       </c>
       <c r="V75" t="inlineStr"/>
-      <c r="W75" t="inlineStr"/>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6012/656554/e80ffba2-9ad5-4dbb-b29f-fa4071d90c31.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6905,7 +6953,11 @@
         <v>161285</v>
       </c>
       <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>1781972646621</t>
+        </is>
+      </c>
       <c r="O77" t="n">
         <v>0</v>
       </c>
@@ -6926,7 +6978,11 @@
         <v>0</v>
       </c>
       <c r="V77" t="inlineStr"/>
-      <c r="W77" t="inlineStr"/>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6012/656556/738353e8-435d-443a-be16-86a0c41bdd40.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -7320,7 +7376,11 @@
         <v>161290</v>
       </c>
       <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>1781973377527</t>
+        </is>
+      </c>
       <c r="O82" t="n">
         <v>0</v>
       </c>
@@ -7341,7 +7401,11 @@
         <v>0</v>
       </c>
       <c r="V82" t="inlineStr"/>
-      <c r="W82" t="inlineStr"/>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6012/656561/92f064e3-c8df-4f20-bd85-9aa5dab709e2.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -7403,7 +7467,11 @@
         <v>161291</v>
       </c>
       <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>1781973219894</t>
+        </is>
+      </c>
       <c r="O83" t="n">
         <v>0</v>
       </c>
@@ -7424,7 +7492,11 @@
         <v>0</v>
       </c>
       <c r="V83" t="inlineStr"/>
-      <c r="W83" t="inlineStr"/>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6012/656562/ce439005-8bb7-4c1d-ad32-2632ceb943b6.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -8506,7 +8578,11 @@
         <v>161304</v>
       </c>
       <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>1781973399391</t>
+        </is>
+      </c>
       <c r="O96" t="n">
         <v>0</v>
       </c>
@@ -8527,7 +8603,11 @@
         <v>0</v>
       </c>
       <c r="V96" t="inlineStr"/>
-      <c r="W96" t="inlineStr"/>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6012/656575/27aa0457-31ba-4cab-877a-671b79cad90e.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -13170,7 +13250,11 @@
         <v>161258</v>
       </c>
       <c r="M152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>1781972470309</t>
+        </is>
+      </c>
       <c r="O152" t="n">
         <v>0</v>
       </c>
@@ -13191,7 +13275,11 @@
         <v>0</v>
       </c>
       <c r="V152" t="inlineStr"/>
-      <c r="W152" t="inlineStr"/>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6010/656609/46a98bbf-9f8b-410c-820d-e8e6876713f5.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -15589,7 +15677,11 @@
         <v>161268</v>
       </c>
       <c r="M181" t="inlineStr"/>
-      <c r="N181" t="inlineStr"/>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>1781973006233</t>
+        </is>
+      </c>
       <c r="O181" t="n">
         <v>0</v>
       </c>
@@ -15610,7 +15702,11 @@
         <v>0</v>
       </c>
       <c r="V181" t="inlineStr"/>
-      <c r="W181" t="inlineStr"/>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6011/656627/85f9aeba-3809-4fd7-803f-fc0ba706a460.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -16336,7 +16432,11 @@
         <v>161337</v>
       </c>
       <c r="M190" t="inlineStr"/>
-      <c r="N190" t="inlineStr"/>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>1781972645318</t>
+        </is>
+      </c>
       <c r="O190" t="n">
         <v>0</v>
       </c>
@@ -16357,7 +16457,11 @@
         <v>0</v>
       </c>
       <c r="V190" t="inlineStr"/>
-      <c r="W190" t="inlineStr"/>
+      <c r="W190" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6014/656502/33fdf1d7-b3c8-440a-a172-545390a6fe20.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -18917,7 +19021,11 @@
         <v>87275</v>
       </c>
       <c r="M221" t="inlineStr"/>
-      <c r="N221" t="inlineStr"/>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>1781972648269</t>
+        </is>
+      </c>
       <c r="O221" t="n">
         <v>0</v>
       </c>
@@ -18938,7 +19046,11 @@
         <v>0</v>
       </c>
       <c r="V221" t="inlineStr"/>
-      <c r="W221" t="inlineStr"/>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6116/86186/e85bd5b8-e8f0-4211-ad53-befdb4b77c28.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -46189,7 +46301,11 @@
         <v>162951</v>
       </c>
       <c r="M549" t="inlineStr"/>
-      <c r="N549" t="inlineStr"/>
+      <c r="N549" t="inlineStr">
+        <is>
+          <t>1781973195520</t>
+        </is>
+      </c>
       <c r="O549" t="n">
         <v>0</v>
       </c>
@@ -46210,7 +46326,11 @@
         <v>0</v>
       </c>
       <c r="V549" t="inlineStr"/>
-      <c r="W549" t="inlineStr"/>
+      <c r="W549" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6148/658240/9c803a88-761e-493e-93ac-287ac46e56eb.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -47766,7 +47886,11 @@
         <v>162943</v>
       </c>
       <c r="M568" t="inlineStr"/>
-      <c r="N568" t="inlineStr"/>
+      <c r="N568" t="inlineStr">
+        <is>
+          <t>1781973008256</t>
+        </is>
+      </c>
       <c r="O568" t="n">
         <v>0</v>
       </c>
@@ -47787,7 +47911,11 @@
         <v>0</v>
       </c>
       <c r="V568" t="inlineStr"/>
-      <c r="W568" t="inlineStr"/>
+      <c r="W568" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6147/658251/3a0206a9-0cd8-47fa-b769-eb516aec3fb6.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">

--- a/output/Nasarawa/results.xlsx
+++ b/output/Nasarawa/results.xlsx
@@ -1770,7 +1770,11 @@
         <v>86145</v>
       </c>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>1781973548774</t>
+        </is>
+      </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
@@ -1791,7 +1795,11 @@
         <v>0</v>
       </c>
       <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6013/85081/96021811-da76-4645-a50f-ed516983b832.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3114,7 +3122,11 @@
         <v>161314</v>
       </c>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>1781973370815</t>
+        </is>
+      </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
@@ -3135,7 +3147,11 @@
         <v>0</v>
       </c>
       <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6013/656520/c264ab22-2d7b-4429-a4d8-14452db991bf.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">

--- a/output/Nasarawa/results.xlsx
+++ b/output/Nasarawa/results.xlsx
@@ -1861,7 +1861,11 @@
         <v>86146</v>
       </c>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>1781973669731</t>
+        </is>
+      </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
@@ -1882,7 +1886,11 @@
         <v>0</v>
       </c>
       <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6013/85082/0f2fb75d-a61e-47ce-8bd1-a564dfded26b.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3304,7 +3312,11 @@
         <v>161316</v>
       </c>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>1781973753760</t>
+        </is>
+      </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
@@ -3325,7 +3337,11 @@
         <v>0</v>
       </c>
       <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6013/656522/807b7798-f150-4bae-a77e-dda251c98015.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3719,7 +3735,11 @@
         <v>161321</v>
       </c>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>1781973751454</t>
+        </is>
+      </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
@@ -3740,7 +3760,11 @@
         <v>0</v>
       </c>
       <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6013/656527/8d00afd0-88ce-4f44-bfae-2c85244672b8.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -7831,7 +7855,11 @@
         <v>161295</v>
       </c>
       <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>1781973663954</t>
+        </is>
+      </c>
       <c r="O87" t="n">
         <v>0</v>
       </c>
@@ -7852,7 +7880,11 @@
         <v>0</v>
       </c>
       <c r="V87" t="inlineStr"/>
-      <c r="W87" t="inlineStr"/>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6012/656566/f663d9c9-64f4-4dae-88ad-984118b714c6.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -13440,7 +13472,11 @@
         <v>161260</v>
       </c>
       <c r="M154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>1781973745923</t>
+        </is>
+      </c>
       <c r="O154" t="n">
         <v>0</v>
       </c>
@@ -13461,7 +13497,11 @@
         <v>0</v>
       </c>
       <c r="V154" t="inlineStr"/>
-      <c r="W154" t="inlineStr"/>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6010/656611/f6a5f4e5-f76d-408c-a9dc-9b033f53f964.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">

--- a/output/Nasarawa/results.xlsx
+++ b/output/Nasarawa/results.xlsx
@@ -8369,7 +8369,11 @@
         <v>161301</v>
       </c>
       <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>1781974268302</t>
+        </is>
+      </c>
       <c r="O93" t="n">
         <v>0</v>
       </c>
@@ -8390,7 +8394,11 @@
         <v>0</v>
       </c>
       <c r="V93" t="inlineStr"/>
-      <c r="W93" t="inlineStr"/>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6012/656572/0722d11d-c6bf-4f84-8ab3-f71af6a1bd26.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -8883,7 +8891,11 @@
         <v>161307</v>
       </c>
       <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>1781973905143</t>
+        </is>
+      </c>
       <c r="O99" t="n">
         <v>0</v>
       </c>
@@ -8904,7 +8916,11 @@
         <v>0</v>
       </c>
       <c r="V99" t="inlineStr"/>
-      <c r="W99" t="inlineStr"/>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6012/656578/6b212c3e-ab73-41c9-9a72-7ef6114d4255.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -12966,7 +12982,11 @@
         <v>161254</v>
       </c>
       <c r="M148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>1781974267207</t>
+        </is>
+      </c>
       <c r="O148" t="n">
         <v>0</v>
       </c>
@@ -12987,7 +13007,11 @@
         <v>0</v>
       </c>
       <c r="V148" t="inlineStr"/>
-      <c r="W148" t="inlineStr"/>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6010/656605/01ecfdc3-d4ae-4355-a837-3fa73a88abec.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -16579,7 +16603,11 @@
         <v>161338</v>
       </c>
       <c r="M191" t="inlineStr"/>
-      <c r="N191" t="inlineStr"/>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>1781974447753</t>
+        </is>
+      </c>
       <c r="O191" t="n">
         <v>0</v>
       </c>
@@ -16600,7 +16628,11 @@
         <v>0</v>
       </c>
       <c r="V191" t="inlineStr"/>
-      <c r="W191" t="inlineStr"/>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6014/656503/5b2aba42-dd1c-4273-ba35-62605c6cdaca.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -16994,7 +17026,11 @@
         <v>86118</v>
       </c>
       <c r="M196" t="inlineStr"/>
-      <c r="N196" t="inlineStr"/>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>1781974632489</t>
+        </is>
+      </c>
       <c r="O196" t="n">
         <v>0</v>
       </c>
@@ -17015,7 +17051,11 @@
         <v>0</v>
       </c>
       <c r="V196" t="inlineStr"/>
-      <c r="W196" t="inlineStr"/>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6009/85054/916c0066-2a32-44fd-be54-68a91cf52b75.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -37045,7 +37085,11 @@
         <v>162631</v>
       </c>
       <c r="M437" t="inlineStr"/>
-      <c r="N437" t="inlineStr"/>
+      <c r="N437" t="inlineStr">
+        <is>
+          <t>1781974265492</t>
+        </is>
+      </c>
       <c r="O437" t="n">
         <v>0</v>
       </c>
@@ -37066,7 +37110,11 @@
         <v>0</v>
       </c>
       <c r="V437" t="inlineStr"/>
-      <c r="W437" t="inlineStr"/>
+      <c r="W437" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6108/657982/4f82ddf2-8a08-4858-8f71-8d11c34038a6.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -37875,7 +37923,11 @@
         <v>87269</v>
       </c>
       <c r="M447" t="inlineStr"/>
-      <c r="N447" t="inlineStr"/>
+      <c r="N447" t="inlineStr">
+        <is>
+          <t>1781973931156</t>
+        </is>
+      </c>
       <c r="O447" t="n">
         <v>0</v>
       </c>
@@ -37896,7 +37948,11 @@
         <v>0</v>
       </c>
       <c r="V447" t="inlineStr"/>
-      <c r="W447" t="inlineStr"/>
+      <c r="W447" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6115/86180/bcca6203-82b5-42bf-9093-c401808fbc26.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -39551,7 +39607,11 @@
         <v>87555</v>
       </c>
       <c r="M467" t="inlineStr"/>
-      <c r="N467" t="inlineStr"/>
+      <c r="N467" t="inlineStr">
+        <is>
+          <t>1781974804559</t>
+        </is>
+      </c>
       <c r="O467" t="n">
         <v>0</v>
       </c>
@@ -39572,7 +39632,11 @@
         <v>0</v>
       </c>
       <c r="V467" t="inlineStr"/>
-      <c r="W467" t="inlineStr"/>
+      <c r="W467" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6141/86466/8d53058b-acf2-40ee-9172-99cddaaed9f0.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">

--- a/output/Nasarawa/results.xlsx
+++ b/output/Nasarawa/results.xlsx
@@ -39226,7 +39226,11 @@
         <v>162662</v>
       </c>
       <c r="M258" t="inlineStr"/>
-      <c r="N258" t="inlineStr"/>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>1781975887367</t>
+        </is>
+      </c>
       <c r="O258" t="n">
         <v>0</v>
       </c>
@@ -39247,7 +39251,11 @@
         <v>0</v>
       </c>
       <c r="V258" t="inlineStr"/>
-      <c r="W258" t="inlineStr"/>
+      <c r="W258" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6114/657904/4614aee7-2bc7-4990-b4f5-b03dba06e2cd.jpg</t>
+        </is>
+      </c>
       <c r="X258" t="n">
         <v>0</v>
       </c>
@@ -39375,7 +39383,11 @@
         <v>162663</v>
       </c>
       <c r="M259" t="inlineStr"/>
-      <c r="N259" t="inlineStr"/>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>1781975882659</t>
+        </is>
+      </c>
       <c r="O259" t="n">
         <v>0</v>
       </c>
@@ -39396,7 +39408,11 @@
         <v>0</v>
       </c>
       <c r="V259" t="inlineStr"/>
-      <c r="W259" t="inlineStr"/>
+      <c r="W259" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6114/657905/db61b287-4d67-4509-83db-873d99bcd661.jpg</t>
+        </is>
+      </c>
       <c r="X259" t="n">
         <v>0</v>
       </c>

--- a/output/Nasarawa/results.xlsx
+++ b/output/Nasarawa/results.xlsx
@@ -3118,7 +3118,11 @@
         <v>86147</v>
       </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>1781976941429</t>
+        </is>
+      </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
@@ -3139,7 +3143,11 @@
         <v>0</v>
       </c>
       <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6013/85083/9e400b32-df39-4927-b48f-dc5f0bd11a6d.jpg</t>
+        </is>
+      </c>
       <c r="X18" t="n">
         <v>0</v>
       </c>
@@ -4310,7 +4318,11 @@
         <v>161308</v>
       </c>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>1781976781719</t>
+        </is>
+      </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
@@ -4331,7 +4343,11 @@
         <v>0</v>
       </c>
       <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6013/656514/5e7e1f5c-60c0-4981-bb5d-c27cb8ee871e.jpg</t>
+        </is>
+      </c>
       <c r="X26" t="n">
         <v>0</v>
       </c>
@@ -4459,7 +4475,11 @@
         <v>161309</v>
       </c>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>1781976806734</t>
+        </is>
+      </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
@@ -4480,7 +4500,11 @@
         <v>0</v>
       </c>
       <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6013/656515/98ec0e21-5780-43d2-95d0-ae2d7d22f7bb.jpg</t>
+        </is>
+      </c>
       <c r="X27" t="n">
         <v>0</v>
       </c>
@@ -5840,7 +5864,11 @@
         <v>161318</v>
       </c>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>1781976755996</t>
+        </is>
+      </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
@@ -5861,7 +5889,11 @@
         <v>0</v>
       </c>
       <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6013/656524/77a929ad-790d-4985-acc6-3425ec63b913.jpg</t>
+        </is>
+      </c>
       <c r="X36" t="n">
         <v>0</v>
       </c>
@@ -6138,7 +6170,11 @@
         <v>161320</v>
       </c>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>1781977041449</t>
+        </is>
+      </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
@@ -6159,7 +6195,11 @@
         <v>0</v>
       </c>
       <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6013/656526/eeb3a2cb-2b5c-4c23-98b1-ada3f11f2389.jpg</t>
+        </is>
+      </c>
       <c r="X38" t="n">
         <v>0</v>
       </c>
@@ -6601,7 +6641,11 @@
         <v>161323</v>
       </c>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>1781976822034</t>
+        </is>
+      </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
@@ -6622,7 +6666,11 @@
         <v>0</v>
       </c>
       <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6013/656529/96816b7e-b664-469a-9de2-d271ad74b60c.jpg</t>
+        </is>
+      </c>
       <c r="X41" t="n">
         <v>0</v>
       </c>
@@ -6750,7 +6798,11 @@
         <v>161324</v>
       </c>
       <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>1781976812690</t>
+        </is>
+      </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
@@ -6771,7 +6823,11 @@
         <v>0</v>
       </c>
       <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6013/656530/fff71fcd-bbaf-4193-951a-2b6a6f40f227.jpg</t>
+        </is>
+      </c>
       <c r="X42" t="n">
         <v>0</v>
       </c>
@@ -6899,7 +6955,11 @@
         <v>161325</v>
       </c>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>1781976430273</t>
+        </is>
+      </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
@@ -6920,7 +6980,11 @@
         <v>0</v>
       </c>
       <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6013/656531/0bc9b14b-c81d-463c-ab87-267225a6d25f.jpg</t>
+        </is>
+      </c>
       <c r="X43" t="n">
         <v>0</v>
       </c>
@@ -7048,7 +7112,11 @@
         <v>161326</v>
       </c>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>1781976819816</t>
+        </is>
+      </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
@@ -7069,7 +7137,11 @@
         <v>0</v>
       </c>
       <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6013/656532/70221a29-c503-44f9-8f2d-ad23d2338d47.jpg</t>
+        </is>
+      </c>
       <c r="X44" t="n">
         <v>0</v>
       </c>
@@ -8397,7 +8469,11 @@
         <v>161335</v>
       </c>
       <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>1781976905273</t>
+        </is>
+      </c>
       <c r="O53" t="n">
         <v>0</v>
       </c>
@@ -8418,7 +8494,11 @@
         <v>0</v>
       </c>
       <c r="V53" t="inlineStr"/>
-      <c r="W53" t="inlineStr"/>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6013/656541/c768aed9-1b45-41e8-8432-985b37053715.jpg</t>
+        </is>
+      </c>
       <c r="X53" t="n">
         <v>0</v>
       </c>
@@ -8703,7 +8783,11 @@
         <v>86135</v>
       </c>
       <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>1781976898771</t>
+        </is>
+      </c>
       <c r="O55" t="n">
         <v>0</v>
       </c>
@@ -8724,7 +8808,11 @@
         <v>0</v>
       </c>
       <c r="V55" t="inlineStr"/>
-      <c r="W55" t="inlineStr"/>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6012/85071/03895c8f-5f94-49bc-b3ba-39d93b1f125c.jpg</t>
+        </is>
+      </c>
       <c r="X55" t="n">
         <v>0</v>
       </c>
@@ -8852,7 +8940,11 @@
         <v>86136</v>
       </c>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>1781976836321</t>
+        </is>
+      </c>
       <c r="O56" t="n">
         <v>0</v>
       </c>
@@ -8873,7 +8965,11 @@
         <v>0</v>
       </c>
       <c r="V56" t="inlineStr"/>
-      <c r="W56" t="inlineStr"/>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6012/85072/26371d65-9138-4638-b88e-359c0e92b082.jpg</t>
+        </is>
+      </c>
       <c r="X56" t="n">
         <v>0</v>
       </c>
@@ -9307,7 +9403,11 @@
         <v>86139</v>
       </c>
       <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>1781977023096</t>
+        </is>
+      </c>
       <c r="O59" t="n">
         <v>0</v>
       </c>
@@ -9328,7 +9428,11 @@
         <v>0</v>
       </c>
       <c r="V59" t="inlineStr"/>
-      <c r="W59" t="inlineStr"/>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6012/85075/8f64fd8e-ecf5-4d26-81c3-1840adc60252.jpg</t>
+        </is>
+      </c>
       <c r="X59" t="n">
         <v>0</v>
       </c>
@@ -9456,7 +9560,11 @@
         <v>86140</v>
       </c>
       <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>1781977060853</t>
+        </is>
+      </c>
       <c r="O60" t="n">
         <v>0</v>
       </c>
@@ -9477,7 +9585,11 @@
         <v>0</v>
       </c>
       <c r="V60" t="inlineStr"/>
-      <c r="W60" t="inlineStr"/>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6012/85076/b054785e-bcbe-4cc9-b0ff-2f29ec6027d5.jpg</t>
+        </is>
+      </c>
       <c r="X60" t="n">
         <v>0</v>
       </c>
@@ -10531,7 +10643,11 @@
         <v>161275</v>
       </c>
       <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>1781976790738</t>
+        </is>
+      </c>
       <c r="O67" t="n">
         <v>0</v>
       </c>
@@ -10552,7 +10668,11 @@
         <v>0</v>
       </c>
       <c r="V67" t="inlineStr"/>
-      <c r="W67" t="inlineStr"/>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6012/656546/a650435c-1d99-4c56-beec-827f151ab291.jpg</t>
+        </is>
+      </c>
       <c r="X67" t="n">
         <v>0</v>
       </c>
@@ -10680,7 +10800,11 @@
         <v>161276</v>
       </c>
       <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>1781976857206</t>
+        </is>
+      </c>
       <c r="O68" t="n">
         <v>0</v>
       </c>
@@ -10701,7 +10825,11 @@
         <v>0</v>
       </c>
       <c r="V68" t="inlineStr"/>
-      <c r="W68" t="inlineStr"/>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6012/656547/e2927061-0bf6-4666-aeb8-b39593516e98.jpg</t>
+        </is>
+      </c>
       <c r="X68" t="n">
         <v>0</v>
       </c>
@@ -11904,7 +12032,11 @@
         <v>161284</v>
       </c>
       <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>1781976842333</t>
+        </is>
+      </c>
       <c r="O76" t="n">
         <v>0</v>
       </c>
@@ -11925,7 +12057,11 @@
         <v>0</v>
       </c>
       <c r="V76" t="inlineStr"/>
-      <c r="W76" t="inlineStr"/>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6012/656555/eaf1d5dd-c662-4cf6-a049-f7f71a13350b.jpg</t>
+        </is>
+      </c>
       <c r="X76" t="n">
         <v>0</v>
       </c>
@@ -12210,7 +12346,11 @@
         <v>161286</v>
       </c>
       <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>1781976811550</t>
+        </is>
+      </c>
       <c r="O78" t="n">
         <v>0</v>
       </c>
@@ -12231,7 +12371,11 @@
         <v>0</v>
       </c>
       <c r="V78" t="inlineStr"/>
-      <c r="W78" t="inlineStr"/>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6012/656557/9f3e0463-0c6c-49f3-a120-6fb2b12ac348.jpg</t>
+        </is>
+      </c>
       <c r="X78" t="n">
         <v>0</v>
       </c>
@@ -12359,7 +12503,11 @@
         <v>161287</v>
       </c>
       <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>1781976969260</t>
+        </is>
+      </c>
       <c r="O79" t="n">
         <v>0</v>
       </c>
@@ -12380,7 +12528,11 @@
         <v>0</v>
       </c>
       <c r="V79" t="inlineStr"/>
-      <c r="W79" t="inlineStr"/>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6012/656558/b43359a1-3df0-4019-9987-4ab24fe308f8.jpg</t>
+        </is>
+      </c>
       <c r="X79" t="n">
         <v>0</v>
       </c>
@@ -12657,7 +12809,11 @@
         <v>161289</v>
       </c>
       <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>1781976929846</t>
+        </is>
+      </c>
       <c r="O81" t="n">
         <v>0</v>
       </c>
@@ -12678,7 +12834,11 @@
         <v>0</v>
       </c>
       <c r="V81" t="inlineStr"/>
-      <c r="W81" t="inlineStr"/>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6012/656560/8e8532c3-92eb-426b-843a-1fcb0f818475.jpg</t>
+        </is>
+      </c>
       <c r="X81" t="n">
         <v>0</v>
       </c>
@@ -13120,7 +13280,11 @@
         <v>161292</v>
       </c>
       <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>1781976796486</t>
+        </is>
+      </c>
       <c r="O84" t="n">
         <v>0</v>
       </c>
@@ -13141,7 +13305,11 @@
         <v>0</v>
       </c>
       <c r="V84" t="inlineStr"/>
-      <c r="W84" t="inlineStr"/>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6012/656563/d2f0b8ce-4fda-4422-abe2-268bdba9eeed.jpg</t>
+        </is>
+      </c>
       <c r="X84" t="n">
         <v>0</v>
       </c>
@@ -14642,7 +14810,11 @@
         <v>161302</v>
       </c>
       <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>1781976859447</t>
+        </is>
+      </c>
       <c r="O94" t="n">
         <v>0</v>
       </c>
@@ -14663,7 +14835,11 @@
         <v>0</v>
       </c>
       <c r="V94" t="inlineStr"/>
-      <c r="W94" t="inlineStr"/>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6012/656573/b9aad7b6-0948-438e-ac66-73ab77d6330a.jpg</t>
+        </is>
+      </c>
       <c r="X94" t="n">
         <v>0</v>
       </c>
@@ -15560,7 +15736,11 @@
         <v>86108</v>
       </c>
       <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>1781976806660</t>
+        </is>
+      </c>
       <c r="O100" t="n">
         <v>0</v>
       </c>
@@ -15581,7 +15761,11 @@
         <v>0</v>
       </c>
       <c r="V100" t="inlineStr"/>
-      <c r="W100" t="inlineStr"/>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6007/85044/232e4550-75e0-4e7c-8822-e7bbcfc21193.jpg</t>
+        </is>
+      </c>
       <c r="X100" t="n">
         <v>0</v>
       </c>
@@ -16313,7 +16497,11 @@
         <v>161231</v>
       </c>
       <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>1781977101895</t>
+        </is>
+      </c>
       <c r="O105" t="n">
         <v>0</v>
       </c>
@@ -16334,7 +16522,11 @@
         <v>0</v>
       </c>
       <c r="V105" t="inlineStr"/>
-      <c r="W105" t="inlineStr"/>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6007/656588/11aeeca7-6536-41e2-bc2e-c88006493463.jpg</t>
+        </is>
+      </c>
       <c r="X105" t="n">
         <v>0</v>
       </c>
@@ -17215,7 +17407,11 @@
         <v>86091</v>
       </c>
       <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>1781976969571</t>
+        </is>
+      </c>
       <c r="O111" t="n">
         <v>0</v>
       </c>
@@ -17236,7 +17432,11 @@
         <v>0</v>
       </c>
       <c r="V111" t="inlineStr"/>
-      <c r="W111" t="inlineStr"/>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6004/85027/d43d3ead-f3f8-4445-8b65-c91d40875310.jpg</t>
+        </is>
+      </c>
       <c r="X111" t="n">
         <v>0</v>
       </c>
@@ -17513,7 +17713,11 @@
         <v>86093</v>
       </c>
       <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>1781977059158</t>
+        </is>
+      </c>
       <c r="O113" t="n">
         <v>0</v>
       </c>
@@ -17534,7 +17738,11 @@
         <v>0</v>
       </c>
       <c r="V113" t="inlineStr"/>
-      <c r="W113" t="inlineStr"/>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6004/85029/910568f1-f034-4b73-843c-1a5f52d66bb3.jpg</t>
+        </is>
+      </c>
       <c r="X113" t="n">
         <v>0</v>
       </c>
@@ -18109,7 +18317,11 @@
         <v>86097</v>
       </c>
       <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>1781976996378</t>
+        </is>
+      </c>
       <c r="O117" t="n">
         <v>0</v>
       </c>
@@ -18130,7 +18342,11 @@
         <v>0</v>
       </c>
       <c r="V117" t="inlineStr"/>
-      <c r="W117" t="inlineStr"/>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6004/85033/b87876f6-97d4-4fd0-b3a9-cad2d21e83fc.jpg</t>
+        </is>
+      </c>
       <c r="X117" t="n">
         <v>0</v>
       </c>
@@ -21552,7 +21768,11 @@
         <v>161243</v>
       </c>
       <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>1781977084585</t>
+        </is>
+      </c>
       <c r="O140" t="n">
         <v>0</v>
       </c>
@@ -21573,7 +21793,11 @@
         <v>0</v>
       </c>
       <c r="V140" t="inlineStr"/>
-      <c r="W140" t="inlineStr"/>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6008/656601/3b55c1b2-50a2-42e4-afbe-bcd6f90739a3.jpg</t>
+        </is>
+      </c>
       <c r="X140" t="n">
         <v>0</v>
       </c>
@@ -21701,7 +21925,11 @@
         <v>86123</v>
       </c>
       <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>1781976816449</t>
+        </is>
+      </c>
       <c r="O141" t="n">
         <v>0</v>
       </c>
@@ -21722,7 +21950,11 @@
         <v>0</v>
       </c>
       <c r="V141" t="inlineStr"/>
-      <c r="W141" t="inlineStr"/>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6010/85059/f016a4c2-b8d6-4f56-b458-6c654ea13e43.jpg</t>
+        </is>
+      </c>
       <c r="X141" t="n">
         <v>0</v>
       </c>
@@ -21999,7 +22231,11 @@
         <v>86125</v>
       </c>
       <c r="M143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>1781976850959</t>
+        </is>
+      </c>
       <c r="O143" t="n">
         <v>0</v>
       </c>
@@ -22020,7 +22256,11 @@
         <v>0</v>
       </c>
       <c r="V143" t="inlineStr"/>
-      <c r="W143" t="inlineStr"/>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6010/85061/884ccee8-099d-4bd8-8442-f8910ef12ad7.jpg</t>
+        </is>
+      </c>
       <c r="X143" t="n">
         <v>0</v>
       </c>
@@ -22297,7 +22537,11 @@
         <v>161251</v>
       </c>
       <c r="M145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>1781976754835</t>
+        </is>
+      </c>
       <c r="O145" t="n">
         <v>0</v>
       </c>
@@ -22318,7 +22562,11 @@
         <v>0</v>
       </c>
       <c r="V145" t="inlineStr"/>
-      <c r="W145" t="inlineStr"/>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6010/656602/24f60fc0-dd5f-4654-be83-8dfdaa136c75.jpg</t>
+        </is>
+      </c>
       <c r="X145" t="n">
         <v>0</v>
       </c>
@@ -22446,7 +22694,11 @@
         <v>161252</v>
       </c>
       <c r="M146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>1781977071603</t>
+        </is>
+      </c>
       <c r="O146" t="n">
         <v>0</v>
       </c>
@@ -22467,7 +22719,11 @@
         <v>0</v>
       </c>
       <c r="V146" t="inlineStr"/>
-      <c r="W146" t="inlineStr"/>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6010/656603/1d763519-c099-4506-86a7-c626a8cae77d.jpg</t>
+        </is>
+      </c>
       <c r="X146" t="n">
         <v>0</v>
       </c>
@@ -23505,7 +23761,11 @@
         <v>161259</v>
       </c>
       <c r="M153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>1781976788014</t>
+        </is>
+      </c>
       <c r="O153" t="n">
         <v>0</v>
       </c>
@@ -23526,7 +23786,11 @@
         <v>0</v>
       </c>
       <c r="V153" t="inlineStr"/>
-      <c r="W153" t="inlineStr"/>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6010/656610/95578735-dfbc-47ca-b504-40cee9cdb3e0.jpg</t>
+        </is>
+      </c>
       <c r="X153" t="n">
         <v>0</v>
       </c>
@@ -23812,7 +24076,11 @@
         <v>86104</v>
       </c>
       <c r="M155" t="inlineStr"/>
-      <c r="N155" t="inlineStr"/>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>1781977110161</t>
+        </is>
+      </c>
       <c r="O155" t="n">
         <v>0</v>
       </c>
@@ -23833,7 +24101,11 @@
         <v>0</v>
       </c>
       <c r="V155" t="inlineStr"/>
-      <c r="W155" t="inlineStr"/>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6006/85040/0ac95b45-7f54-4222-ab5c-bb0a146551e1.jpg</t>
+        </is>
+      </c>
       <c r="X155" t="n">
         <v>0</v>
       </c>
@@ -24562,7 +24834,11 @@
         <v>161223</v>
       </c>
       <c r="M160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>1781977127136</t>
+        </is>
+      </c>
       <c r="O160" t="n">
         <v>0</v>
       </c>
@@ -24583,7 +24859,11 @@
         <v>0</v>
       </c>
       <c r="V160" t="inlineStr"/>
-      <c r="W160" t="inlineStr"/>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6006/656619/1fe4e584-2415-4b0c-bfec-9a2a4e9376dd.jpg</t>
+        </is>
+      </c>
       <c r="X160" t="n">
         <v>0</v>
       </c>
@@ -30121,7 +30401,11 @@
         <v>86119</v>
       </c>
       <c r="M197" t="inlineStr"/>
-      <c r="N197" t="inlineStr"/>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>1781976819067</t>
+        </is>
+      </c>
       <c r="O197" t="n">
         <v>0</v>
       </c>
@@ -30142,7 +30426,11 @@
         <v>0</v>
       </c>
       <c r="V197" t="inlineStr"/>
-      <c r="W197" t="inlineStr"/>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6009/85055/63fb9f30-cfbc-479c-a52c-842c60dc572f.jpg</t>
+        </is>
+      </c>
       <c r="X197" t="n">
         <v>0</v>
       </c>
@@ -30419,7 +30707,11 @@
         <v>86121</v>
       </c>
       <c r="M199" t="inlineStr"/>
-      <c r="N199" t="inlineStr"/>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>1781977083969</t>
+        </is>
+      </c>
       <c r="O199" t="n">
         <v>0</v>
       </c>
@@ -30440,7 +30732,11 @@
         <v>0</v>
       </c>
       <c r="V199" t="inlineStr"/>
-      <c r="W199" t="inlineStr"/>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6009/85057/5744402b-4af8-40a6-a71c-924713abdc28.jpg</t>
+        </is>
+      </c>
       <c r="X199" t="n">
         <v>0</v>
       </c>
@@ -30866,7 +31162,11 @@
         <v>161245</v>
       </c>
       <c r="M202" t="inlineStr"/>
-      <c r="N202" t="inlineStr"/>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>1781976846575</t>
+        </is>
+      </c>
       <c r="O202" t="n">
         <v>0</v>
       </c>
@@ -30887,7 +31187,11 @@
         <v>0</v>
       </c>
       <c r="V202" t="inlineStr"/>
-      <c r="W202" t="inlineStr"/>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6009/656631/61b7f63a-98e5-413b-a1f0-86a23d9aba8e.jpg</t>
+        </is>
+      </c>
       <c r="X202" t="n">
         <v>0</v>
       </c>
@@ -31470,7 +31774,11 @@
         <v>161249</v>
       </c>
       <c r="M206" t="inlineStr"/>
-      <c r="N206" t="inlineStr"/>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>1781976998864</t>
+        </is>
+      </c>
       <c r="O206" t="n">
         <v>0</v>
       </c>
@@ -31491,7 +31799,11 @@
         <v>0</v>
       </c>
       <c r="V206" t="inlineStr"/>
-      <c r="W206" t="inlineStr"/>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6009/656635/bdeba4b6-1127-45c1-81eb-b4ab55b22fdf.jpg</t>
+        </is>
+      </c>
       <c r="X206" t="n">
         <v>0</v>
       </c>
@@ -31917,7 +32229,11 @@
         <v>87291</v>
       </c>
       <c r="M209" t="inlineStr"/>
-      <c r="N209" t="inlineStr"/>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>1781977273219</t>
+        </is>
+      </c>
       <c r="O209" t="n">
         <v>0</v>
       </c>
@@ -31938,7 +32254,11 @@
         <v>0</v>
       </c>
       <c r="V209" t="inlineStr"/>
-      <c r="W209" t="inlineStr"/>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6118/86202/c3ccd7ac-ae96-442a-90f7-1b9343f37c5b.jpg</t>
+        </is>
+      </c>
       <c r="X209" t="n">
         <v>0</v>
       </c>
@@ -32960,7 +33280,11 @@
         <v>162703</v>
       </c>
       <c r="M216" t="inlineStr"/>
-      <c r="N216" t="inlineStr"/>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>1781976897625</t>
+        </is>
+      </c>
       <c r="O216" t="n">
         <v>0</v>
       </c>
@@ -32981,7 +33305,11 @@
         <v>0</v>
       </c>
       <c r="V216" t="inlineStr"/>
-      <c r="W216" t="inlineStr"/>
+      <c r="W216" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6118/657885/a942c581-09fc-4883-8880-f3d42a09ab03.jpg</t>
+        </is>
+      </c>
       <c r="X216" t="n">
         <v>0</v>
       </c>
@@ -33407,7 +33735,11 @@
         <v>87273</v>
       </c>
       <c r="M219" t="inlineStr"/>
-      <c r="N219" t="inlineStr"/>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>1781976874063</t>
+        </is>
+      </c>
       <c r="O219" t="n">
         <v>0</v>
       </c>
@@ -33428,7 +33760,11 @@
         <v>0</v>
       </c>
       <c r="V219" t="inlineStr"/>
-      <c r="W219" t="inlineStr"/>
+      <c r="W219" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6116/86184/0751ba35-7770-4ed4-b3ce-2ba58b653a3a.jpg</t>
+        </is>
+      </c>
       <c r="X219" t="n">
         <v>0</v>
       </c>
@@ -39540,7 +39876,11 @@
         <v>162664</v>
       </c>
       <c r="M260" t="inlineStr"/>
-      <c r="N260" t="inlineStr"/>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>1781976758644</t>
+        </is>
+      </c>
       <c r="O260" t="n">
         <v>0</v>
       </c>
@@ -39561,7 +39901,11 @@
         <v>0</v>
       </c>
       <c r="V260" t="inlineStr"/>
-      <c r="W260" t="inlineStr"/>
+      <c r="W260" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6114/657906/50a412ad-22eb-421a-aea0-ce6b4fd6d99a.jpg</t>
+        </is>
+      </c>
       <c r="X260" t="n">
         <v>0</v>
       </c>
@@ -39838,7 +40182,11 @@
         <v>162666</v>
       </c>
       <c r="M262" t="inlineStr"/>
-      <c r="N262" t="inlineStr"/>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>1781976946122</t>
+        </is>
+      </c>
       <c r="O262" t="n">
         <v>0</v>
       </c>
@@ -39859,7 +40207,11 @@
         <v>0</v>
       </c>
       <c r="V262" t="inlineStr"/>
-      <c r="W262" t="inlineStr"/>
+      <c r="W262" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6114/657908/68cfc488-204e-4391-8489-01f6292a5400.jpg</t>
+        </is>
+      </c>
       <c r="X262" t="n">
         <v>0</v>
       </c>
@@ -40136,7 +40488,11 @@
         <v>162668</v>
       </c>
       <c r="M264" t="inlineStr"/>
-      <c r="N264" t="inlineStr"/>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>1781977134986</t>
+        </is>
+      </c>
       <c r="O264" t="n">
         <v>0</v>
       </c>
@@ -40157,7 +40513,11 @@
         <v>0</v>
       </c>
       <c r="V264" t="inlineStr"/>
-      <c r="W264" t="inlineStr"/>
+      <c r="W264" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6114/657910/6e013e7e-b894-437c-9ec7-d22bad3c912d.jpg</t>
+        </is>
+      </c>
       <c r="X264" t="n">
         <v>0</v>
       </c>
@@ -45657,7 +46017,11 @@
         <v>162659</v>
       </c>
       <c r="M301" t="inlineStr"/>
-      <c r="N301" t="inlineStr"/>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>1781976778712</t>
+        </is>
+      </c>
       <c r="O301" t="n">
         <v>0</v>
       </c>
@@ -45678,7 +46042,11 @@
         <v>0</v>
       </c>
       <c r="V301" t="inlineStr"/>
-      <c r="W301" t="inlineStr"/>
+      <c r="W301" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6113/657919/f9cb4f67-03e5-4e68-80ed-dd211b3dc2a1.jpg</t>
+        </is>
+      </c>
       <c r="X301" t="n">
         <v>0</v>
       </c>
@@ -46700,7 +47068,11 @@
         <v>87243</v>
       </c>
       <c r="M308" t="inlineStr"/>
-      <c r="N308" t="inlineStr"/>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>1781977069190</t>
+        </is>
+      </c>
       <c r="O308" t="n">
         <v>0</v>
       </c>
@@ -46721,7 +47093,11 @@
         <v>0</v>
       </c>
       <c r="V308" t="inlineStr"/>
-      <c r="W308" t="inlineStr"/>
+      <c r="W308" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6112/86154/2d9f2828-be0c-4d12-a184-27e7e711fc41.jpg</t>
+        </is>
+      </c>
       <c r="X308" t="n">
         <v>0</v>
       </c>
@@ -47900,7 +48276,11 @@
         <v>162652</v>
       </c>
       <c r="M316" t="inlineStr"/>
-      <c r="N316" t="inlineStr"/>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>1781976919192</t>
+        </is>
+      </c>
       <c r="O316" t="n">
         <v>0</v>
       </c>
@@ -47921,7 +48301,11 @@
         <v>0</v>
       </c>
       <c r="V316" t="inlineStr"/>
-      <c r="W316" t="inlineStr"/>
+      <c r="W316" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6112/657881/d82119ef-db47-48e8-afc3-4721f910e0b0.jpg</t>
+        </is>
+      </c>
       <c r="X316" t="n">
         <v>0</v>
       </c>
@@ -48049,7 +48433,11 @@
         <v>162653</v>
       </c>
       <c r="M317" t="inlineStr"/>
-      <c r="N317" t="inlineStr"/>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>1781977005245</t>
+        </is>
+      </c>
       <c r="O317" t="n">
         <v>0</v>
       </c>
@@ -48070,7 +48458,11 @@
         <v>0</v>
       </c>
       <c r="V317" t="inlineStr"/>
-      <c r="W317" t="inlineStr"/>
+      <c r="W317" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6112/657882/4a79b1a2-a2c6-49d3-a6c6-3a8c8401b7e0.jpg</t>
+        </is>
+      </c>
       <c r="X317" t="n">
         <v>0</v>
       </c>
@@ -48347,7 +48739,11 @@
         <v>87234</v>
       </c>
       <c r="M319" t="inlineStr"/>
-      <c r="N319" t="inlineStr"/>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>1781976776415</t>
+        </is>
+      </c>
       <c r="O319" t="n">
         <v>0</v>
       </c>
@@ -48368,7 +48764,11 @@
         <v>0</v>
       </c>
       <c r="V319" t="inlineStr"/>
-      <c r="W319" t="inlineStr"/>
+      <c r="W319" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6111/86145/ec4324b1-4979-43fe-a3a3-d58bf2ba2531.jpg</t>
+        </is>
+      </c>
       <c r="X319" t="n">
         <v>0</v>
       </c>
@@ -51178,7 +51578,11 @@
         <v>162644</v>
       </c>
       <c r="M338" t="inlineStr"/>
-      <c r="N338" t="inlineStr"/>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>1781976821655</t>
+        </is>
+      </c>
       <c r="O338" t="n">
         <v>0</v>
       </c>
@@ -51199,7 +51603,11 @@
         <v>0</v>
       </c>
       <c r="V338" t="inlineStr"/>
-      <c r="W338" t="inlineStr"/>
+      <c r="W338" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6110/657927/23f3afc1-1c67-46e3-8a40-f2fe16d46768.jpg</t>
+        </is>
+      </c>
       <c r="X338" t="n">
         <v>0</v>
       </c>
@@ -52684,7 +53092,11 @@
         <v>87220</v>
       </c>
       <c r="M348" t="inlineStr"/>
-      <c r="N348" t="inlineStr"/>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>1781976971651</t>
+        </is>
+      </c>
       <c r="O348" t="n">
         <v>0</v>
       </c>
@@ -52705,7 +53117,11 @@
         <v>0</v>
       </c>
       <c r="V348" t="inlineStr"/>
-      <c r="W348" t="inlineStr"/>
+      <c r="W348" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6109/86131/334e28d0-28f7-4963-8c0f-c94c4b284ba2.jpg</t>
+        </is>
+      </c>
       <c r="X348" t="n">
         <v>0</v>
       </c>
@@ -53578,7 +53994,11 @@
         <v>162637</v>
       </c>
       <c r="M354" t="inlineStr"/>
-      <c r="N354" t="inlineStr"/>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>1781977029382</t>
+        </is>
+      </c>
       <c r="O354" t="n">
         <v>0</v>
       </c>
@@ -53599,7 +54019,11 @@
         <v>0</v>
       </c>
       <c r="V354" t="inlineStr"/>
-      <c r="W354" t="inlineStr"/>
+      <c r="W354" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6109/657932/6844b5c2-dae6-4dbb-8d89-3f12847fa103.jpg</t>
+        </is>
+      </c>
       <c r="X354" t="n">
         <v>0</v>
       </c>
@@ -61795,7 +62219,11 @@
         <v>87187</v>
       </c>
       <c r="M409" t="inlineStr"/>
-      <c r="N409" t="inlineStr"/>
+      <c r="N409" t="inlineStr">
+        <is>
+          <t>1781976906694</t>
+        </is>
+      </c>
       <c r="O409" t="n">
         <v>0</v>
       </c>
@@ -61816,7 +62244,11 @@
         <v>0</v>
       </c>
       <c r="V409" t="inlineStr"/>
-      <c r="W409" t="inlineStr"/>
+      <c r="W409" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6106/86098/b40e3fd5-0981-42e6-a183-9b33d32268fc.jpg</t>
+        </is>
+      </c>
       <c r="X409" t="n">
         <v>0</v>
       </c>
@@ -62391,7 +62823,11 @@
         <v>162610</v>
       </c>
       <c r="M413" t="inlineStr"/>
-      <c r="N413" t="inlineStr"/>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>1781976911815</t>
+        </is>
+      </c>
       <c r="O413" t="n">
         <v>0</v>
       </c>
@@ -62412,7 +62848,11 @@
         <v>0</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" t="inlineStr"/>
+      <c r="W413" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6106/657971/e07aac2d-e6ce-49db-b0a2-b4f4822719b4.jpg</t>
+        </is>
+      </c>
       <c r="X413" t="n">
         <v>0</v>
       </c>
@@ -62540,7 +62980,11 @@
         <v>162611</v>
       </c>
       <c r="M414" t="inlineStr"/>
-      <c r="N414" t="inlineStr"/>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>1781977081069</t>
+        </is>
+      </c>
       <c r="O414" t="n">
         <v>0</v>
       </c>
@@ -62561,7 +63005,11 @@
         <v>0</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" t="inlineStr"/>
+      <c r="W414" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6106/657972/fbe92ca7-3282-4d66-bc40-2670727194b1.jpg</t>
+        </is>
+      </c>
       <c r="X414" t="n">
         <v>0</v>
       </c>
@@ -62689,7 +63137,11 @@
         <v>162612</v>
       </c>
       <c r="M415" t="inlineStr"/>
-      <c r="N415" t="inlineStr"/>
+      <c r="N415" t="inlineStr">
+        <is>
+          <t>1781976817697</t>
+        </is>
+      </c>
       <c r="O415" t="n">
         <v>0</v>
       </c>
@@ -62710,7 +63162,11 @@
         <v>0</v>
       </c>
       <c r="V415" t="inlineStr"/>
-      <c r="W415" t="inlineStr"/>
+      <c r="W415" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6106/657973/e6f87565-1fa1-4db7-b3ac-dfae5cdfa267.jpg</t>
+        </is>
+      </c>
       <c r="X415" t="n">
         <v>0</v>
       </c>
@@ -62838,7 +63294,11 @@
         <v>162613</v>
       </c>
       <c r="M416" t="inlineStr"/>
-      <c r="N416" t="inlineStr"/>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>1781976795416</t>
+        </is>
+      </c>
       <c r="O416" t="n">
         <v>0</v>
       </c>
@@ -62859,7 +63319,11 @@
         <v>0</v>
       </c>
       <c r="V416" t="inlineStr"/>
-      <c r="W416" t="inlineStr"/>
+      <c r="W416" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6106/657974/5aa3820d-446a-455f-9af1-38d4aecf13f3.jpg</t>
+        </is>
+      </c>
       <c r="X416" t="n">
         <v>0</v>
       </c>
@@ -62987,7 +63451,11 @@
         <v>162614</v>
       </c>
       <c r="M417" t="inlineStr"/>
-      <c r="N417" t="inlineStr"/>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>1781976875351</t>
+        </is>
+      </c>
       <c r="O417" t="n">
         <v>0</v>
       </c>
@@ -63008,7 +63476,11 @@
         <v>0</v>
       </c>
       <c r="V417" t="inlineStr"/>
-      <c r="W417" t="inlineStr"/>
+      <c r="W417" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6106/657975/11d1605c-c263-4de3-a932-f1c93fe55dfe.jpg</t>
+        </is>
+      </c>
       <c r="X417" t="n">
         <v>0</v>
       </c>
@@ -63136,7 +63608,11 @@
         <v>162615</v>
       </c>
       <c r="M418" t="inlineStr"/>
-      <c r="N418" t="inlineStr"/>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>1781976904432</t>
+        </is>
+      </c>
       <c r="O418" t="n">
         <v>0</v>
       </c>
@@ -63157,7 +63633,11 @@
         <v>0</v>
       </c>
       <c r="V418" t="inlineStr"/>
-      <c r="W418" t="inlineStr"/>
+      <c r="W418" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6106/657976/2d63680b-fa7e-4b0b-be5c-b317637d9588.jpg</t>
+        </is>
+      </c>
       <c r="X418" t="n">
         <v>0</v>
       </c>
@@ -63583,7 +64063,11 @@
         <v>162618</v>
       </c>
       <c r="M421" t="inlineStr"/>
-      <c r="N421" t="inlineStr"/>
+      <c r="N421" t="inlineStr">
+        <is>
+          <t>1781977144953</t>
+        </is>
+      </c>
       <c r="O421" t="n">
         <v>0</v>
       </c>
@@ -63604,7 +64088,11 @@
         <v>0</v>
       </c>
       <c r="V421" t="inlineStr"/>
-      <c r="W421" t="inlineStr"/>
+      <c r="W421" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6106/657979/ec33a669-591c-4560-beba-a262b44318ab.jpg</t>
+        </is>
+      </c>
       <c r="X421" t="n">
         <v>0</v>
       </c>
@@ -66430,7 +66918,11 @@
         <v>162634</v>
       </c>
       <c r="M440" t="inlineStr"/>
-      <c r="N440" t="inlineStr"/>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>1781976787159</t>
+        </is>
+      </c>
       <c r="O440" t="n">
         <v>0</v>
       </c>
@@ -66451,7 +66943,11 @@
         <v>0</v>
       </c>
       <c r="V440" t="inlineStr"/>
-      <c r="W440" t="inlineStr"/>
+      <c r="W440" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6108/657985/8418658b-b366-45cd-bdf4-0970695c8a92.jpg</t>
+        </is>
+      </c>
       <c r="X440" t="n">
         <v>0</v>
       </c>
@@ -66877,7 +67373,11 @@
         <v>87265</v>
       </c>
       <c r="M443" t="inlineStr"/>
-      <c r="N443" t="inlineStr"/>
+      <c r="N443" t="inlineStr">
+        <is>
+          <t>1781976908917</t>
+        </is>
+      </c>
       <c r="O443" t="n">
         <v>0</v>
       </c>
@@ -66898,7 +67398,11 @@
         <v>0</v>
       </c>
       <c r="V443" t="inlineStr"/>
-      <c r="W443" t="inlineStr"/>
+      <c r="W443" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6115/86176/ef3c82cb-927b-4d95-9df7-b712c67157d9.jpg</t>
+        </is>
+      </c>
       <c r="X443" t="n">
         <v>0</v>
       </c>
@@ -67026,7 +67530,11 @@
         <v>87266</v>
       </c>
       <c r="M444" t="inlineStr"/>
-      <c r="N444" t="inlineStr"/>
+      <c r="N444" t="inlineStr">
+        <is>
+          <t>1781976868417</t>
+        </is>
+      </c>
       <c r="O444" t="n">
         <v>0</v>
       </c>
@@ -67047,7 +67555,11 @@
         <v>0</v>
       </c>
       <c r="V444" t="inlineStr"/>
-      <c r="W444" t="inlineStr"/>
+      <c r="W444" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6115/86177/1271a7c9-78df-4a8f-8fc2-1f7a4dda7a12.jpg</t>
+        </is>
+      </c>
       <c r="X444" t="n">
         <v>0</v>
       </c>
@@ -67630,7 +68142,11 @@
         <v>87270</v>
       </c>
       <c r="M448" t="inlineStr"/>
-      <c r="N448" t="inlineStr"/>
+      <c r="N448" t="inlineStr">
+        <is>
+          <t>1781976940198</t>
+        </is>
+      </c>
       <c r="O448" t="n">
         <v>0</v>
       </c>
@@ -67651,7 +68167,11 @@
         <v>0</v>
       </c>
       <c r="V448" t="inlineStr"/>
-      <c r="W448" t="inlineStr"/>
+      <c r="W448" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6115/86181/2bd2bbf4-94a0-45a3-97d7-e729a6ac8f41.jpg</t>
+        </is>
+      </c>
       <c r="X448" t="n">
         <v>0</v>
       </c>
@@ -67779,7 +68299,11 @@
         <v>87271</v>
       </c>
       <c r="M449" t="inlineStr"/>
-      <c r="N449" t="inlineStr"/>
+      <c r="N449" t="inlineStr">
+        <is>
+          <t>1781976868210</t>
+        </is>
+      </c>
       <c r="O449" t="n">
         <v>0</v>
       </c>
@@ -67800,7 +68324,11 @@
         <v>0</v>
       </c>
       <c r="V449" t="inlineStr"/>
-      <c r="W449" t="inlineStr"/>
+      <c r="W449" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6115/86182/4cddbd00-15f8-4a86-928d-5e9ccbd2ea35.jpg</t>
+        </is>
+      </c>
       <c r="X449" t="n">
         <v>0</v>
       </c>
@@ -68391,7 +68919,11 @@
         <v>162675</v>
       </c>
       <c r="M453" t="inlineStr"/>
-      <c r="N453" t="inlineStr"/>
+      <c r="N453" t="inlineStr">
+        <is>
+          <t>1781976789149</t>
+        </is>
+      </c>
       <c r="O453" t="n">
         <v>0</v>
       </c>
@@ -68412,7 +68944,11 @@
         <v>0</v>
       </c>
       <c r="V453" t="inlineStr"/>
-      <c r="W453" t="inlineStr"/>
+      <c r="W453" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6115/657989/fc38acc1-f0f0-480e-ade1-39c3f658f32b.jpg</t>
+        </is>
+      </c>
       <c r="X453" t="n">
         <v>0</v>
       </c>
@@ -68540,7 +69076,11 @@
         <v>162676</v>
       </c>
       <c r="M454" t="inlineStr"/>
-      <c r="N454" t="inlineStr"/>
+      <c r="N454" t="inlineStr">
+        <is>
+          <t>1781976778124</t>
+        </is>
+      </c>
       <c r="O454" t="n">
         <v>0</v>
       </c>
@@ -68561,7 +69101,11 @@
         <v>0</v>
       </c>
       <c r="V454" t="inlineStr"/>
-      <c r="W454" t="inlineStr"/>
+      <c r="W454" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6115/657990/7b1fefb7-cdb7-406b-b31f-b94fb2b7e021.jpg</t>
+        </is>
+      </c>
       <c r="X454" t="n">
         <v>0</v>
       </c>
@@ -68689,7 +69233,11 @@
         <v>162677</v>
       </c>
       <c r="M455" t="inlineStr"/>
-      <c r="N455" t="inlineStr"/>
+      <c r="N455" t="inlineStr">
+        <is>
+          <t>1781976846941</t>
+        </is>
+      </c>
       <c r="O455" t="n">
         <v>0</v>
       </c>
@@ -68710,7 +69258,11 @@
         <v>0</v>
       </c>
       <c r="V455" t="inlineStr"/>
-      <c r="W455" t="inlineStr"/>
+      <c r="W455" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6115/657991/82145c95-0032-45ae-a48c-2eb62dbbfa91.jpg</t>
+        </is>
+      </c>
       <c r="X455" t="n">
         <v>0</v>
       </c>
@@ -69136,7 +69688,11 @@
         <v>162680</v>
       </c>
       <c r="M458" t="inlineStr"/>
-      <c r="N458" t="inlineStr"/>
+      <c r="N458" t="inlineStr">
+        <is>
+          <t>1781977119083</t>
+        </is>
+      </c>
       <c r="O458" t="n">
         <v>0</v>
       </c>
@@ -69157,7 +69713,11 @@
         <v>0</v>
       </c>
       <c r="V458" t="inlineStr"/>
-      <c r="W458" t="inlineStr"/>
+      <c r="W458" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6115/657994/22074394-244f-45be-99eb-58e2c4030a17.jpg</t>
+        </is>
+      </c>
       <c r="X458" t="n">
         <v>0</v>
       </c>
@@ -69583,7 +70143,11 @@
         <v>162683</v>
       </c>
       <c r="M461" t="inlineStr"/>
-      <c r="N461" t="inlineStr"/>
+      <c r="N461" t="inlineStr">
+        <is>
+          <t>1781976768279</t>
+        </is>
+      </c>
       <c r="O461" t="n">
         <v>0</v>
       </c>
@@ -69604,7 +70168,11 @@
         <v>0</v>
       </c>
       <c r="V461" t="inlineStr"/>
-      <c r="W461" t="inlineStr"/>
+      <c r="W461" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6115/657997/df9213ef-8896-4e6f-9266-e4d34f586628.jpg</t>
+        </is>
+      </c>
       <c r="X461" t="n">
         <v>0</v>
       </c>
@@ -69732,7 +70300,11 @@
         <v>162684</v>
       </c>
       <c r="M462" t="inlineStr"/>
-      <c r="N462" t="inlineStr"/>
+      <c r="N462" t="inlineStr">
+        <is>
+          <t>1781977168710</t>
+        </is>
+      </c>
       <c r="O462" t="n">
         <v>0</v>
       </c>
@@ -69753,7 +70325,11 @@
         <v>0</v>
       </c>
       <c r="V462" t="inlineStr"/>
-      <c r="W462" t="inlineStr"/>
+      <c r="W462" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6115/657998/ba498545-40b3-4911-b8f5-fe28fc45a353.jpg</t>
+        </is>
+      </c>
       <c r="X462" t="n">
         <v>0</v>
       </c>
@@ -71975,7 +72551,11 @@
         <v>162913</v>
       </c>
       <c r="M477" t="inlineStr"/>
-      <c r="N477" t="inlineStr"/>
+      <c r="N477" t="inlineStr">
+        <is>
+          <t>1781977116740</t>
+        </is>
+      </c>
       <c r="O477" t="n">
         <v>0</v>
       </c>
@@ -71996,7 +72576,11 @@
         <v>0</v>
       </c>
       <c r="V477" t="inlineStr"/>
-      <c r="W477" t="inlineStr"/>
+      <c r="W477" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6143/658203/556fdd23-179d-43b5-b1bb-261357acd5a7.jpg</t>
+        </is>
+      </c>
       <c r="X477" t="n">
         <v>0</v>
       </c>
@@ -72720,7 +73304,11 @@
         <v>162918</v>
       </c>
       <c r="M482" t="inlineStr"/>
-      <c r="N482" t="inlineStr"/>
+      <c r="N482" t="inlineStr">
+        <is>
+          <t>1781976830439</t>
+        </is>
+      </c>
       <c r="O482" t="n">
         <v>0</v>
       </c>
@@ -72741,7 +73329,11 @@
         <v>0</v>
       </c>
       <c r="V482" t="inlineStr"/>
-      <c r="W482" t="inlineStr"/>
+      <c r="W482" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6143/658208/d42c0483-acd0-4ebb-a63a-18c81bd6968c.jpg</t>
+        </is>
+      </c>
       <c r="X482" t="n">
         <v>0</v>
       </c>
@@ -79127,7 +79719,11 @@
         <v>87569</v>
       </c>
       <c r="M525" t="inlineStr"/>
-      <c r="N525" t="inlineStr"/>
+      <c r="N525" t="inlineStr">
+        <is>
+          <t>1781976763087</t>
+        </is>
+      </c>
       <c r="O525" t="n">
         <v>0</v>
       </c>
@@ -79148,7 +79744,11 @@
         <v>0</v>
       </c>
       <c r="V525" t="inlineStr"/>
-      <c r="W525" t="inlineStr"/>
+      <c r="W525" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6144/86480/99e48b10-9c58-48b6-a1cb-28eca45010df.jpg</t>
+        </is>
+      </c>
       <c r="X525" t="n">
         <v>0</v>
       </c>
@@ -79276,7 +79876,11 @@
         <v>87570</v>
       </c>
       <c r="M526" t="inlineStr"/>
-      <c r="N526" t="inlineStr"/>
+      <c r="N526" t="inlineStr">
+        <is>
+          <t>1781977001362</t>
+        </is>
+      </c>
       <c r="O526" t="n">
         <v>0</v>
       </c>
@@ -79297,7 +79901,11 @@
         <v>0</v>
       </c>
       <c r="V526" t="inlineStr"/>
-      <c r="W526" t="inlineStr"/>
+      <c r="W526" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6144/86481/403a6d31-2b6d-4d5e-863b-2eec90c83f90.jpg</t>
+        </is>
+      </c>
       <c r="X526" t="n">
         <v>0</v>
       </c>
@@ -79425,7 +80033,11 @@
         <v>87571</v>
       </c>
       <c r="M527" t="inlineStr"/>
-      <c r="N527" t="inlineStr"/>
+      <c r="N527" t="inlineStr">
+        <is>
+          <t>1781976786859</t>
+        </is>
+      </c>
       <c r="O527" t="n">
         <v>0</v>
       </c>
@@ -79446,7 +80058,11 @@
         <v>0</v>
       </c>
       <c r="V527" t="inlineStr"/>
-      <c r="W527" t="inlineStr"/>
+      <c r="W527" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6144/86482/5d62e81f-5bc5-48ff-bb22-7837f043972f.jpg</t>
+        </is>
+      </c>
       <c r="X527" t="n">
         <v>0</v>
       </c>
@@ -80021,7 +80637,11 @@
         <v>162921</v>
       </c>
       <c r="M531" t="inlineStr"/>
-      <c r="N531" t="inlineStr"/>
+      <c r="N531" t="inlineStr">
+        <is>
+          <t>1781976913469</t>
+        </is>
+      </c>
       <c r="O531" t="n">
         <v>0</v>
       </c>
@@ -80042,7 +80662,11 @@
         <v>0</v>
       </c>
       <c r="V531" t="inlineStr"/>
-      <c r="W531" t="inlineStr"/>
+      <c r="W531" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6144/658231/4451a8c5-622b-43ad-bd3a-d1d123071958.jpg</t>
+        </is>
+      </c>
       <c r="X531" t="n">
         <v>0</v>
       </c>
@@ -80170,7 +80794,11 @@
         <v>162922</v>
       </c>
       <c r="M532" t="inlineStr"/>
-      <c r="N532" t="inlineStr"/>
+      <c r="N532" t="inlineStr">
+        <is>
+          <t>1781976953311</t>
+        </is>
+      </c>
       <c r="O532" t="n">
         <v>0</v>
       </c>
@@ -80191,7 +80819,11 @@
         <v>0</v>
       </c>
       <c r="V532" t="inlineStr"/>
-      <c r="W532" t="inlineStr"/>
+      <c r="W532" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6144/658232/b099803e-f7ff-4997-9e06-3c96ef44393f.jpg</t>
+        </is>
+      </c>
       <c r="X532" t="n">
         <v>0</v>
       </c>
@@ -80766,7 +81398,11 @@
         <v>87591</v>
       </c>
       <c r="M536" t="inlineStr"/>
-      <c r="N536" t="inlineStr"/>
+      <c r="N536" t="inlineStr">
+        <is>
+          <t>1781976941095</t>
+        </is>
+      </c>
       <c r="O536" t="n">
         <v>0</v>
       </c>
@@ -80787,7 +81423,11 @@
         <v>0</v>
       </c>
       <c r="V536" t="inlineStr"/>
-      <c r="W536" t="inlineStr"/>
+      <c r="W536" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6148/86502/ef516ab3-0b0a-40c2-b96d-cfb9284c191d.jpg</t>
+        </is>
+      </c>
       <c r="X536" t="n">
         <v>0</v>
       </c>
@@ -81668,7 +82308,11 @@
         <v>87597</v>
       </c>
       <c r="M542" t="inlineStr"/>
-      <c r="N542" t="inlineStr"/>
+      <c r="N542" t="inlineStr">
+        <is>
+          <t>1781976857796</t>
+        </is>
+      </c>
       <c r="O542" t="n">
         <v>0</v>
       </c>
@@ -81689,7 +82333,11 @@
         <v>0</v>
       </c>
       <c r="V542" t="inlineStr"/>
-      <c r="W542" t="inlineStr"/>
+      <c r="W542" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6148/86508/a43a28ec-5656-4808-a9bf-56d053663b83.jpg</t>
+        </is>
+      </c>
       <c r="X542" t="n">
         <v>0</v>
       </c>
@@ -81817,7 +82465,11 @@
         <v>87598</v>
       </c>
       <c r="M543" t="inlineStr"/>
-      <c r="N543" t="inlineStr"/>
+      <c r="N543" t="inlineStr">
+        <is>
+          <t>1781976993591</t>
+        </is>
+      </c>
       <c r="O543" t="n">
         <v>0</v>
       </c>
@@ -81838,7 +82490,11 @@
         <v>0</v>
       </c>
       <c r="V543" t="inlineStr"/>
-      <c r="W543" t="inlineStr"/>
+      <c r="W543" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6148/86509/48855ddd-c356-4830-bed0-ec163a5afc29.jpg</t>
+        </is>
+      </c>
       <c r="X543" t="n">
         <v>0</v>
       </c>
@@ -82115,7 +82771,11 @@
         <v>162947</v>
       </c>
       <c r="M545" t="inlineStr"/>
-      <c r="N545" t="inlineStr"/>
+      <c r="N545" t="inlineStr">
+        <is>
+          <t>1781977103721</t>
+        </is>
+      </c>
       <c r="O545" t="n">
         <v>0</v>
       </c>
@@ -82136,7 +82796,11 @@
         <v>0</v>
       </c>
       <c r="V545" t="inlineStr"/>
-      <c r="W545" t="inlineStr"/>
+      <c r="W545" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6148/658236/c503d0f1-cedf-4544-beed-1abfbbb9a0ce.jpg</t>
+        </is>
+      </c>
       <c r="X545" t="n">
         <v>0</v>
       </c>
@@ -82264,7 +82928,11 @@
         <v>162948</v>
       </c>
       <c r="M546" t="inlineStr"/>
-      <c r="N546" t="inlineStr"/>
+      <c r="N546" t="inlineStr">
+        <is>
+          <t>1781976977554</t>
+        </is>
+      </c>
       <c r="O546" t="n">
         <v>0</v>
       </c>
@@ -82285,7 +82953,11 @@
         <v>0</v>
       </c>
       <c r="V546" t="inlineStr"/>
-      <c r="W546" t="inlineStr"/>
+      <c r="W546" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6148/658237/060e18ec-89f1-4afd-acc7-d1baa7ea3c05.jpg</t>
+        </is>
+      </c>
       <c r="X546" t="n">
         <v>0</v>
       </c>
@@ -82413,7 +83085,11 @@
         <v>162949</v>
       </c>
       <c r="M547" t="inlineStr"/>
-      <c r="N547" t="inlineStr"/>
+      <c r="N547" t="inlineStr">
+        <is>
+          <t>1781977159473</t>
+        </is>
+      </c>
       <c r="O547" t="n">
         <v>0</v>
       </c>
@@ -82434,7 +83110,11 @@
         <v>0</v>
       </c>
       <c r="V547" t="inlineStr"/>
-      <c r="W547" t="inlineStr"/>
+      <c r="W547" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6148/658238/8c1b501c-3e37-46fa-b0e4-a4e4c5ace0f4.jpg</t>
+        </is>
+      </c>
       <c r="X547" t="n">
         <v>0</v>
       </c>
@@ -82868,7 +83548,11 @@
         <v>162952</v>
       </c>
       <c r="M550" t="inlineStr"/>
-      <c r="N550" t="inlineStr"/>
+      <c r="N550" t="inlineStr">
+        <is>
+          <t>1781977125359</t>
+        </is>
+      </c>
       <c r="O550" t="n">
         <v>0</v>
       </c>
@@ -82889,7 +83573,11 @@
         <v>0</v>
       </c>
       <c r="V550" t="inlineStr"/>
-      <c r="W550" t="inlineStr"/>
+      <c r="W550" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6148/658241/40ac234b-04a5-4486-8cb3-a88a981b5a21.jpg</t>
+        </is>
+      </c>
       <c r="X550" t="n">
         <v>0</v>
       </c>
@@ -83017,7 +83705,11 @@
         <v>162953</v>
       </c>
       <c r="M551" t="inlineStr"/>
-      <c r="N551" t="inlineStr"/>
+      <c r="N551" t="inlineStr">
+        <is>
+          <t>1781976816515</t>
+        </is>
+      </c>
       <c r="O551" t="n">
         <v>0</v>
       </c>
@@ -83038,7 +83730,11 @@
         <v>0</v>
       </c>
       <c r="V551" t="inlineStr"/>
-      <c r="W551" t="inlineStr"/>
+      <c r="W551" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6148/658242/11ac5d01-bf0e-42f8-bc1e-589dfd904743.jpg</t>
+        </is>
+      </c>
       <c r="X551" t="n">
         <v>0</v>
       </c>
@@ -83166,7 +83862,11 @@
         <v>162954</v>
       </c>
       <c r="M552" t="inlineStr"/>
-      <c r="N552" t="inlineStr"/>
+      <c r="N552" t="inlineStr">
+        <is>
+          <t>1781976867493</t>
+        </is>
+      </c>
       <c r="O552" t="n">
         <v>0</v>
       </c>
@@ -83187,7 +83887,11 @@
         <v>0</v>
       </c>
       <c r="V552" t="inlineStr"/>
-      <c r="W552" t="inlineStr"/>
+      <c r="W552" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6148/658243/923694a9-4f86-41ff-a3b1-8a0c2aa09007.jpg</t>
+        </is>
+      </c>
       <c r="X552" t="n">
         <v>0</v>
       </c>
@@ -83613,7 +84317,11 @@
         <v>87585</v>
       </c>
       <c r="M555" t="inlineStr"/>
-      <c r="N555" t="inlineStr"/>
+      <c r="N555" t="inlineStr">
+        <is>
+          <t>1781977013600</t>
+        </is>
+      </c>
       <c r="O555" t="n">
         <v>0</v>
       </c>
@@ -83634,7 +84342,11 @@
         <v>0</v>
       </c>
       <c r="V555" t="inlineStr"/>
-      <c r="W555" t="inlineStr"/>
+      <c r="W555" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6147/86496/9b352749-6800-4cf5-9977-198cc1bb0878.jpg</t>
+        </is>
+      </c>
       <c r="X555" t="n">
         <v>0</v>
       </c>
@@ -83762,7 +84474,11 @@
         <v>87586</v>
       </c>
       <c r="M556" t="inlineStr"/>
-      <c r="N556" t="inlineStr"/>
+      <c r="N556" t="inlineStr">
+        <is>
+          <t>1781976847496</t>
+        </is>
+      </c>
       <c r="O556" t="n">
         <v>0</v>
       </c>
@@ -83783,7 +84499,11 @@
         <v>0</v>
       </c>
       <c r="V556" t="inlineStr"/>
-      <c r="W556" t="inlineStr"/>
+      <c r="W556" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6147/86497/d2b9dc62-a97c-4ade-be8a-84f77b2df463.jpg</t>
+        </is>
+      </c>
       <c r="X556" t="n">
         <v>0</v>
       </c>
@@ -84060,7 +84780,11 @@
         <v>87588</v>
       </c>
       <c r="M558" t="inlineStr"/>
-      <c r="N558" t="inlineStr"/>
+      <c r="N558" t="inlineStr">
+        <is>
+          <t>1781977003068</t>
+        </is>
+      </c>
       <c r="O558" t="n">
         <v>0</v>
       </c>
@@ -84081,7 +84805,11 @@
         <v>0</v>
       </c>
       <c r="V558" t="inlineStr"/>
-      <c r="W558" t="inlineStr"/>
+      <c r="W558" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6147/86499/a918deaf-f493-49a2-92f2-9928ecd25a78.jpg</t>
+        </is>
+      </c>
       <c r="X558" t="n">
         <v>0</v>
       </c>
@@ -84507,7 +85235,11 @@
         <v>162936</v>
       </c>
       <c r="M561" t="inlineStr"/>
-      <c r="N561" t="inlineStr"/>
+      <c r="N561" t="inlineStr">
+        <is>
+          <t>1781977022209</t>
+        </is>
+      </c>
       <c r="O561" t="n">
         <v>0</v>
       </c>
@@ -84528,7 +85260,11 @@
         <v>0</v>
       </c>
       <c r="V561" t="inlineStr"/>
-      <c r="W561" t="inlineStr"/>
+      <c r="W561" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6147/658244/7c885488-ed18-443c-a24f-8a56ef8071e1.jpg</t>
+        </is>
+      </c>
       <c r="X561" t="n">
         <v>0</v>
       </c>
@@ -84656,7 +85392,11 @@
         <v>162937</v>
       </c>
       <c r="M562" t="inlineStr"/>
-      <c r="N562" t="inlineStr"/>
+      <c r="N562" t="inlineStr">
+        <is>
+          <t>1781976802148</t>
+        </is>
+      </c>
       <c r="O562" t="n">
         <v>0</v>
       </c>
@@ -84677,7 +85417,11 @@
         <v>0</v>
       </c>
       <c r="V562" t="inlineStr"/>
-      <c r="W562" t="inlineStr"/>
+      <c r="W562" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6147/658245/ad7d2849-69b6-450e-93bb-3932a7aa93cb.jpg</t>
+        </is>
+      </c>
       <c r="X562" t="n">
         <v>0</v>
       </c>
@@ -84954,7 +85698,11 @@
         <v>162939</v>
       </c>
       <c r="M564" t="inlineStr"/>
-      <c r="N564" t="inlineStr"/>
+      <c r="N564" t="inlineStr">
+        <is>
+          <t>1781976795608</t>
+        </is>
+      </c>
       <c r="O564" t="n">
         <v>0</v>
       </c>
@@ -84975,7 +85723,11 @@
         <v>0</v>
       </c>
       <c r="V564" t="inlineStr"/>
-      <c r="W564" t="inlineStr"/>
+      <c r="W564" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6147/658247/a770a222-5758-49bf-aa66-e3141c7534b7.jpg</t>
+        </is>
+      </c>
       <c r="X564" t="n">
         <v>0</v>
       </c>
@@ -85103,7 +85855,11 @@
         <v>162940</v>
       </c>
       <c r="M565" t="inlineStr"/>
-      <c r="N565" t="inlineStr"/>
+      <c r="N565" t="inlineStr">
+        <is>
+          <t>1781977034237</t>
+        </is>
+      </c>
       <c r="O565" t="n">
         <v>0</v>
       </c>
@@ -85124,7 +85880,11 @@
         <v>0</v>
       </c>
       <c r="V565" t="inlineStr"/>
-      <c r="W565" t="inlineStr"/>
+      <c r="W565" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6147/658248/ec519bf4-41aa-4de5-8b31-4ab2d059e479.jpg</t>
+        </is>
+      </c>
       <c r="X565" t="n">
         <v>0</v>
       </c>
@@ -85252,7 +86012,11 @@
         <v>162941</v>
       </c>
       <c r="M566" t="inlineStr"/>
-      <c r="N566" t="inlineStr"/>
+      <c r="N566" t="inlineStr">
+        <is>
+          <t>1781976803790</t>
+        </is>
+      </c>
       <c r="O566" t="n">
         <v>0</v>
       </c>
@@ -85273,7 +86037,11 @@
         <v>0</v>
       </c>
       <c r="V566" t="inlineStr"/>
-      <c r="W566" t="inlineStr"/>
+      <c r="W566" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6147/658249/f0759e6e-2390-40fa-918b-870425e838df.jpg</t>
+        </is>
+      </c>
       <c r="X566" t="n">
         <v>0</v>
       </c>
@@ -85707,7 +86475,11 @@
         <v>162944</v>
       </c>
       <c r="M569" t="inlineStr"/>
-      <c r="N569" t="inlineStr"/>
+      <c r="N569" t="inlineStr">
+        <is>
+          <t>1781976751620</t>
+        </is>
+      </c>
       <c r="O569" t="n">
         <v>0</v>
       </c>
@@ -85728,7 +86500,11 @@
         <v>0</v>
       </c>
       <c r="V569" t="inlineStr"/>
-      <c r="W569" t="inlineStr"/>
+      <c r="W569" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6147/658252/654323de-df29-4a5c-93d1-6a4ed735b145.jpg</t>
+        </is>
+      </c>
       <c r="X569" t="n">
         <v>0</v>
       </c>
@@ -86162,7 +86938,11 @@
         <v>87577</v>
       </c>
       <c r="M572" t="inlineStr"/>
-      <c r="N572" t="inlineStr"/>
+      <c r="N572" t="inlineStr">
+        <is>
+          <t>1781976804945</t>
+        </is>
+      </c>
       <c r="O572" t="n">
         <v>0</v>
       </c>
@@ -86183,7 +86963,11 @@
         <v>0</v>
       </c>
       <c r="V572" t="inlineStr"/>
-      <c r="W572" t="inlineStr"/>
+      <c r="W572" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6146/86488/f6e8ce1f-ba51-4ac4-b696-94e168cf1ce4.jpg</t>
+        </is>
+      </c>
       <c r="X572" t="n">
         <v>0</v>
       </c>

--- a/output/Nasarawa/results.xlsx
+++ b/output/Nasarawa/results.xlsx
@@ -20,16 +20,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,227 +420,227 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>LGA</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Election ID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Election Name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Election Date</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Ward</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Ward Code</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Ward ID</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Polling Unit</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>PU Code</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>PU ID</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Polling Unit ID</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Result Updated Time</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Session</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Result Info PU</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Image File</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Image URL</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
@@ -2506,7 +2494,11 @@
         <v>86143</v>
       </c>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>1781977351091</t>
+        </is>
+      </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
@@ -2527,7 +2519,11 @@
         <v>0</v>
       </c>
       <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6013/85079/230225f8-52c9-4707-acf4-030957aca280.jpg</t>
+        </is>
+      </c>
       <c r="X14" t="n">
         <v>0</v>
       </c>
@@ -4169,7 +4165,11 @@
         <v>86154</v>
       </c>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>1781977165720</t>
+        </is>
+      </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
@@ -4190,7 +4190,11 @@
         <v>0</v>
       </c>
       <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6013/85090/a66c6095-c3fa-4ccd-80ad-846ca4c412f3.jpg</t>
+        </is>
+      </c>
       <c r="X25" t="n">
         <v>0</v>
       </c>
@@ -27083,7 +27087,11 @@
         <v>161262</v>
       </c>
       <c r="M175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>1781977864067</t>
+        </is>
+      </c>
       <c r="O175" t="n">
         <v>0</v>
       </c>
@@ -27104,7 +27112,11 @@
         <v>0</v>
       </c>
       <c r="V175" t="inlineStr"/>
-      <c r="W175" t="inlineStr"/>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6011/656621/6b598095-9fba-4be1-a8be-db2f1d57481b.jpg</t>
+        </is>
+      </c>
       <c r="X175" t="n">
         <v>0</v>
       </c>
@@ -31468,7 +31480,11 @@
         <v>161247</v>
       </c>
       <c r="M204" t="inlineStr"/>
-      <c r="N204" t="inlineStr"/>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>1781977863605</t>
+        </is>
+      </c>
       <c r="O204" t="n">
         <v>0</v>
       </c>
@@ -31489,7 +31505,11 @@
         <v>0</v>
       </c>
       <c r="V204" t="inlineStr"/>
-      <c r="W204" t="inlineStr"/>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6009/656633/54d46b25-86c8-4b56-8519-d3920f42d18d.jpg</t>
+        </is>
+      </c>
       <c r="X204" t="n">
         <v>0</v>
       </c>
@@ -32386,7 +32406,11 @@
         <v>87292</v>
       </c>
       <c r="M210" t="inlineStr"/>
-      <c r="N210" t="inlineStr"/>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>1781977864626</t>
+        </is>
+      </c>
       <c r="O210" t="n">
         <v>0</v>
       </c>
@@ -32407,7 +32431,11 @@
         <v>0</v>
       </c>
       <c r="V210" t="inlineStr"/>
-      <c r="W210" t="inlineStr"/>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6118/86203/5bbf496e-1ef2-4233-be8a-16b2babac543.jpg</t>
+        </is>
+      </c>
       <c r="X210" t="n">
         <v>0</v>
       </c>
@@ -32833,7 +32861,11 @@
         <v>87295</v>
       </c>
       <c r="M213" t="inlineStr"/>
-      <c r="N213" t="inlineStr"/>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>1781977355482</t>
+        </is>
+      </c>
       <c r="O213" t="n">
         <v>0</v>
       </c>
@@ -32854,7 +32886,11 @@
         <v>0</v>
       </c>
       <c r="V213" t="inlineStr"/>
-      <c r="W213" t="inlineStr"/>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6118/86206/fcaed5a0-2775-46f8-b326-fabd65133616.jpg</t>
+        </is>
+      </c>
       <c r="X213" t="n">
         <v>0</v>
       </c>
@@ -46323,7 +46359,11 @@
         <v>87238</v>
       </c>
       <c r="M303" t="inlineStr"/>
-      <c r="N303" t="inlineStr"/>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>1781978225709</t>
+        </is>
+      </c>
       <c r="O303" t="n">
         <v>0</v>
       </c>
@@ -46344,7 +46384,11 @@
         <v>0</v>
       </c>
       <c r="V303" t="inlineStr"/>
-      <c r="W303" t="inlineStr"/>
+      <c r="W303" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6112/86149/bd70473f-4f01-40b2-870c-2c7f3b263365.jpg</t>
+        </is>
+      </c>
       <c r="X303" t="n">
         <v>0</v>
       </c>
@@ -47978,7 +48022,11 @@
         <v>162650</v>
       </c>
       <c r="M314" t="inlineStr"/>
-      <c r="N314" t="inlineStr"/>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>1781977408341</t>
+        </is>
+      </c>
       <c r="O314" t="n">
         <v>0</v>
       </c>
@@ -47999,7 +48047,11 @@
         <v>0</v>
       </c>
       <c r="V314" t="inlineStr"/>
-      <c r="W314" t="inlineStr"/>
+      <c r="W314" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6112/657879/d3204712-2885-45b4-861f-529eea9e7e93.jpg</t>
+        </is>
+      </c>
       <c r="X314" t="n">
         <v>0</v>
       </c>
@@ -67687,7 +67739,11 @@
         <v>87267</v>
       </c>
       <c r="M445" t="inlineStr"/>
-      <c r="N445" t="inlineStr"/>
+      <c r="N445" t="inlineStr">
+        <is>
+          <t>1781977404261</t>
+        </is>
+      </c>
       <c r="O445" t="n">
         <v>0</v>
       </c>
@@ -67708,7 +67764,11 @@
         <v>0</v>
       </c>
       <c r="V445" t="inlineStr"/>
-      <c r="W445" t="inlineStr"/>
+      <c r="W445" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6115/86178/560ed8c7-0f37-4467-b32b-f5c67dbf7753.jpg</t>
+        </is>
+      </c>
       <c r="X445" t="n">
         <v>0</v>
       </c>
@@ -79570,7 +79630,11 @@
         <v>87568</v>
       </c>
       <c r="M524" t="inlineStr"/>
-      <c r="N524" t="inlineStr"/>
+      <c r="N524" t="inlineStr">
+        <is>
+          <t>1781977157437</t>
+        </is>
+      </c>
       <c r="O524" t="n">
         <v>0</v>
       </c>
@@ -79591,7 +79655,11 @@
         <v>0</v>
       </c>
       <c r="V524" t="inlineStr"/>
-      <c r="W524" t="inlineStr"/>
+      <c r="W524" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6144/86479/ee00a374-1e2d-434b-bb36-a3b5ffec3511.jpg</t>
+        </is>
+      </c>
       <c r="X524" t="n">
         <v>0</v>
       </c>
@@ -80339,7 +80407,11 @@
         <v>162919</v>
       </c>
       <c r="M529" t="inlineStr"/>
-      <c r="N529" t="inlineStr"/>
+      <c r="N529" t="inlineStr">
+        <is>
+          <t>1781977151683</t>
+        </is>
+      </c>
       <c r="O529" t="n">
         <v>0</v>
       </c>
@@ -80360,7 +80432,11 @@
         <v>0</v>
       </c>
       <c r="V529" t="inlineStr"/>
-      <c r="W529" t="inlineStr"/>
+      <c r="W529" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6144/658229/6d88b90d-b339-408e-9f2d-e80e90346d9b.jpg</t>
+        </is>
+      </c>
       <c r="X529" t="n">
         <v>0</v>
       </c>
@@ -80488,7 +80564,11 @@
         <v>162920</v>
       </c>
       <c r="M530" t="inlineStr"/>
-      <c r="N530" t="inlineStr"/>
+      <c r="N530" t="inlineStr">
+        <is>
+          <t>1781977230584</t>
+        </is>
+      </c>
       <c r="O530" t="n">
         <v>0</v>
       </c>
@@ -80509,7 +80589,11 @@
         <v>0</v>
       </c>
       <c r="V530" t="inlineStr"/>
-      <c r="W530" t="inlineStr"/>
+      <c r="W530" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6144/658230/32c7f048-36e9-4782-9526-c51c72ea513f.jpg</t>
+        </is>
+      </c>
       <c r="X530" t="n">
         <v>0</v>
       </c>
@@ -81249,7 +81333,11 @@
         <v>162925</v>
       </c>
       <c r="M535" t="inlineStr"/>
-      <c r="N535" t="inlineStr"/>
+      <c r="N535" t="inlineStr">
+        <is>
+          <t>1781977172212</t>
+        </is>
+      </c>
       <c r="O535" t="n">
         <v>0</v>
       </c>
@@ -81270,7 +81358,11 @@
         <v>0</v>
       </c>
       <c r="V535" t="inlineStr"/>
-      <c r="W535" t="inlineStr"/>
+      <c r="W535" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6144/658235/7aa11d85-1d53-44d0-8411-092ab982eb87.jpg</t>
+        </is>
+      </c>
       <c r="X535" t="n">
         <v>0</v>
       </c>
@@ -85549,7 +85641,11 @@
         <v>162938</v>
       </c>
       <c r="M563" t="inlineStr"/>
-      <c r="N563" t="inlineStr"/>
+      <c r="N563" t="inlineStr">
+        <is>
+          <t>1781977116582</t>
+        </is>
+      </c>
       <c r="O563" t="n">
         <v>0</v>
       </c>
@@ -85570,7 +85666,11 @@
         <v>0</v>
       </c>
       <c r="V563" t="inlineStr"/>
-      <c r="W563" t="inlineStr"/>
+      <c r="W563" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6147/658246/925b9efc-c146-4982-9cc3-2b7bf43d92fe.jpg</t>
+        </is>
+      </c>
       <c r="X563" t="n">
         <v>0</v>
       </c>
@@ -88838,162 +88938,162 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>LGA</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Ward</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Polling Units</t>
         </is>
@@ -92655,157 +92755,157 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>LGA</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Polling Units</t>
         </is>
@@ -93123,152 +93223,152 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Polling Units</t>
         </is>

--- a/output/Nasarawa/results.xlsx
+++ b/output/Nasarawa/results.xlsx
@@ -20,13 +20,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,227 +432,227 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>LGA</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Election ID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Election Name</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Election Date</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Ward</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Ward Code</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Ward ID</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Polling Unit</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>PU Code</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>PU ID</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Polling Unit ID</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Result Updated Time</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Session</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Result Info PU</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Image File</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Image URL</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
@@ -3271,7 +3283,11 @@
         <v>86148</v>
       </c>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>1781981824607</t>
+        </is>
+      </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
@@ -3292,7 +3308,11 @@
         <v>0</v>
       </c>
       <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6013/85084/272fd0de-d293-462d-89f3-68c364e3fec5.jpg</t>
+        </is>
+      </c>
       <c r="X19" t="n">
         <v>0</v>
       </c>
@@ -3420,7 +3440,11 @@
         <v>86149</v>
       </c>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1781982364790</t>
+        </is>
+      </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
@@ -3441,7 +3465,11 @@
         <v>0</v>
       </c>
       <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6013/85085/7caee4cc-e108-4d16-99fd-a11696ddefb3.jpg</t>
+        </is>
+      </c>
       <c r="X20" t="n">
         <v>0</v>
       </c>
@@ -6025,7 +6053,11 @@
         <v>161319</v>
       </c>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>1781980621809</t>
+        </is>
+      </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
@@ -6046,7 +6078,11 @@
         <v>0</v>
       </c>
       <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6013/656525/3226c78e-1874-4d5a-8c34-eeeba5371c73.jpg</t>
+        </is>
+      </c>
       <c r="X37" t="n">
         <v>0</v>
       </c>
@@ -7571,7 +7607,11 @@
         <v>161329</v>
       </c>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>1781979665213</t>
+        </is>
+      </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
@@ -7592,7 +7632,11 @@
         <v>0</v>
       </c>
       <c r="V47" t="inlineStr"/>
-      <c r="W47" t="inlineStr"/>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6013/656535/964ee4cd-aea3-4dbd-8fdb-75f5c9f09be1.jpg</t>
+        </is>
+      </c>
       <c r="X47" t="n">
         <v>0</v>
       </c>
@@ -15897,7 +15941,11 @@
         <v>86109</v>
       </c>
       <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>1781981102798</t>
+        </is>
+      </c>
       <c r="O101" t="n">
         <v>0</v>
       </c>
@@ -15918,7 +15966,11 @@
         <v>0</v>
       </c>
       <c r="V101" t="inlineStr"/>
-      <c r="W101" t="inlineStr"/>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6007/85045/811070f6-acb5-4907-a168-cc3ff130a99a.jpg</t>
+        </is>
+      </c>
       <c r="X101" t="n">
         <v>0</v>
       </c>
@@ -16807,7 +16859,11 @@
         <v>161233</v>
       </c>
       <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>1781979672325</t>
+        </is>
+      </c>
       <c r="O107" t="n">
         <v>0</v>
       </c>
@@ -16828,7 +16884,11 @@
         <v>0</v>
       </c>
       <c r="V107" t="inlineStr"/>
-      <c r="W107" t="inlineStr"/>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6007/656590/21069eaa-61ab-425e-b2d4-0b9c5b37ee1e.jpg</t>
+        </is>
+      </c>
       <c r="X107" t="n">
         <v>0</v>
       </c>
@@ -17568,7 +17628,11 @@
         <v>86092</v>
       </c>
       <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>1781980026192</t>
+        </is>
+      </c>
       <c r="O112" t="n">
         <v>0</v>
       </c>
@@ -17589,7 +17653,11 @@
         <v>0</v>
       </c>
       <c r="V112" t="inlineStr"/>
-      <c r="W112" t="inlineStr"/>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6004/85028/368c33b7-9c55-4202-9554-bb50ac192c91.jpg</t>
+        </is>
+      </c>
       <c r="X112" t="n">
         <v>0</v>
       </c>
@@ -18776,7 +18844,11 @@
         <v>161215</v>
       </c>
       <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>1781978225627</t>
+        </is>
+      </c>
       <c r="O120" t="n">
         <v>0</v>
       </c>
@@ -18797,7 +18869,11 @@
         <v>0</v>
       </c>
       <c r="V120" t="inlineStr"/>
-      <c r="W120" t="inlineStr"/>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6004/656581/2cd74c0c-6fd9-43d3-96dd-aabdfdc5a351.jpg</t>
+        </is>
+      </c>
       <c r="X120" t="n">
         <v>0</v>
       </c>
@@ -20282,7 +20358,11 @@
         <v>86115</v>
       </c>
       <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>1781981828160</t>
+        </is>
+      </c>
       <c r="O130" t="n">
         <v>0</v>
       </c>
@@ -20303,7 +20383,11 @@
         <v>0</v>
       </c>
       <c r="V130" t="inlineStr"/>
-      <c r="W130" t="inlineStr"/>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6008/85051/71024317-ca4e-4a28-b3bd-4e8d16d7e1f0.jpg</t>
+        </is>
+      </c>
       <c r="X130" t="n">
         <v>0</v>
       </c>
@@ -20729,7 +20813,11 @@
         <v>161236</v>
       </c>
       <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>1781982369636</t>
+        </is>
+      </c>
       <c r="O133" t="n">
         <v>0</v>
       </c>
@@ -20750,7 +20838,11 @@
         <v>0</v>
       </c>
       <c r="V133" t="inlineStr"/>
-      <c r="W133" t="inlineStr"/>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6008/656594/bd14fe89-efe2-4067-8b42-0c4c42d79f7f.jpg</t>
+        </is>
+      </c>
       <c r="X133" t="n">
         <v>0</v>
       </c>
@@ -21027,7 +21119,11 @@
         <v>161238</v>
       </c>
       <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>1781979663243</t>
+        </is>
+      </c>
       <c r="O135" t="n">
         <v>0</v>
       </c>
@@ -21048,7 +21144,11 @@
         <v>0</v>
       </c>
       <c r="V135" t="inlineStr"/>
-      <c r="W135" t="inlineStr"/>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6008/656596/41601533-e270-4957-867a-d9fb843f79a4.jpg</t>
+        </is>
+      </c>
       <c r="X135" t="n">
         <v>0</v>
       </c>
@@ -21623,7 +21723,11 @@
         <v>161242</v>
       </c>
       <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>1781982185545</t>
+        </is>
+      </c>
       <c r="O139" t="n">
         <v>0</v>
       </c>
@@ -21644,7 +21748,11 @@
         <v>0</v>
       </c>
       <c r="V139" t="inlineStr"/>
-      <c r="W139" t="inlineStr"/>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6008/656600/f29a43c6-81b1-49cd-bb45-06240e4dc51d.jpg</t>
+        </is>
+      </c>
       <c r="X139" t="n">
         <v>0</v>
       </c>
@@ -22392,7 +22500,11 @@
         <v>86126</v>
       </c>
       <c r="M144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>1781983632507</t>
+        </is>
+      </c>
       <c r="O144" t="n">
         <v>0</v>
       </c>
@@ -22413,7 +22525,11 @@
         <v>0</v>
       </c>
       <c r="V144" t="inlineStr"/>
-      <c r="W144" t="inlineStr"/>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6010/85062/933081d1-915d-4743-ba24-ae4b3f8917ef.jpg</t>
+        </is>
+      </c>
       <c r="X144" t="n">
         <v>0</v>
       </c>
@@ -22855,7 +22971,11 @@
         <v>161253</v>
       </c>
       <c r="M147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>1781978766067</t>
+        </is>
+      </c>
       <c r="O147" t="n">
         <v>0</v>
       </c>
@@ -22876,7 +22996,11 @@
         <v>0</v>
       </c>
       <c r="V147" t="inlineStr"/>
-      <c r="W147" t="inlineStr"/>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6010/656604/6b47dc1d-41f8-4b75-bcbd-eb5a95becd4d.jpg</t>
+        </is>
+      </c>
       <c r="X147" t="n">
         <v>0</v>
       </c>
@@ -23310,7 +23434,11 @@
         <v>161256</v>
       </c>
       <c r="M150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>1781982005324</t>
+        </is>
+      </c>
       <c r="O150" t="n">
         <v>0</v>
       </c>
@@ -23331,7 +23459,11 @@
         <v>0</v>
       </c>
       <c r="V150" t="inlineStr"/>
-      <c r="W150" t="inlineStr"/>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6010/656607/e70f9abf-38fa-4e87-8c9f-3c4ddb70d83e.jpg</t>
+        </is>
+      </c>
       <c r="X150" t="n">
         <v>0</v>
       </c>
@@ -24688,7 +24820,11 @@
         <v>161222</v>
       </c>
       <c r="M159" t="inlineStr"/>
-      <c r="N159" t="inlineStr"/>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>1781979673530</t>
+        </is>
+      </c>
       <c r="O159" t="n">
         <v>0</v>
       </c>
@@ -24709,7 +24845,11 @@
         <v>0</v>
       </c>
       <c r="V159" t="inlineStr"/>
-      <c r="W159" t="inlineStr"/>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6006/656612/256dfa61-a855-4a4f-9c20-d7fc100ab30b.jpg</t>
+        </is>
+      </c>
       <c r="X159" t="n">
         <v>0</v>
       </c>
@@ -25296,7 +25436,11 @@
         <v>161226</v>
       </c>
       <c r="M163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>1781979668676</t>
+        </is>
+      </c>
       <c r="O163" t="n">
         <v>0</v>
       </c>
@@ -25317,7 +25461,11 @@
         <v>0</v>
       </c>
       <c r="V163" t="inlineStr"/>
-      <c r="W163" t="inlineStr"/>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6006/656615/3026b3fa-7f9e-4589-863d-2e89c69c9778.jpg</t>
+        </is>
+      </c>
       <c r="X163" t="n">
         <v>0</v>
       </c>
@@ -27840,7 +27988,11 @@
         <v>161267</v>
       </c>
       <c r="M180" t="inlineStr"/>
-      <c r="N180" t="inlineStr"/>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>1781981286579</t>
+        </is>
+      </c>
       <c r="O180" t="n">
         <v>0</v>
       </c>
@@ -27861,7 +28013,11 @@
         <v>0</v>
       </c>
       <c r="V180" t="inlineStr"/>
-      <c r="W180" t="inlineStr"/>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6011/656626/45c09456-b6be-497d-9b01-c0a808752179.jpg</t>
+        </is>
+      </c>
       <c r="X180" t="n">
         <v>0</v>
       </c>
@@ -33167,7 +33323,11 @@
         <v>162702</v>
       </c>
       <c r="M215" t="inlineStr"/>
-      <c r="N215" t="inlineStr"/>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>1781982722756</t>
+        </is>
+      </c>
       <c r="O215" t="n">
         <v>0</v>
       </c>
@@ -33188,7 +33348,11 @@
         <v>0</v>
       </c>
       <c r="V215" t="inlineStr"/>
-      <c r="W215" t="inlineStr"/>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6118/657884/9dc092b4-9e86-4f54-81ba-2569216fb9ff.jpg</t>
+        </is>
+      </c>
       <c r="X215" t="n">
         <v>0</v>
       </c>
@@ -35724,7 +35888,11 @@
         <v>87280</v>
       </c>
       <c r="M232" t="inlineStr"/>
-      <c r="N232" t="inlineStr"/>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>1781983634455</t>
+        </is>
+      </c>
       <c r="O232" t="n">
         <v>0</v>
       </c>
@@ -35745,7 +35913,11 @@
         <v>0</v>
       </c>
       <c r="V232" t="inlineStr"/>
-      <c r="W232" t="inlineStr"/>
+      <c r="W232" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6117/86191/9a3b7e0e-7d6a-4d84-bd00-71bcade754c0.jpg</t>
+        </is>
+      </c>
       <c r="X232" t="n">
         <v>0</v>
       </c>
@@ -37363,7 +37535,11 @@
         <v>162692</v>
       </c>
       <c r="M243" t="inlineStr"/>
-      <c r="N243" t="inlineStr"/>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>1781978586343</t>
+        </is>
+      </c>
       <c r="O243" t="n">
         <v>0</v>
       </c>
@@ -37384,7 +37560,11 @@
         <v>0</v>
       </c>
       <c r="V243" t="inlineStr"/>
-      <c r="W243" t="inlineStr"/>
+      <c r="W243" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6117/657894/1a6beebd-1524-468e-b075-c741e87d0bf2.jpg</t>
+        </is>
+      </c>
       <c r="X243" t="n">
         <v>0</v>
       </c>
@@ -40375,7 +40555,11 @@
         <v>162667</v>
       </c>
       <c r="M263" t="inlineStr"/>
-      <c r="N263" t="inlineStr"/>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>1781979664839</t>
+        </is>
+      </c>
       <c r="O263" t="n">
         <v>0</v>
       </c>
@@ -40396,7 +40580,11 @@
         <v>0</v>
       </c>
       <c r="V263" t="inlineStr"/>
-      <c r="W263" t="inlineStr"/>
+      <c r="W263" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6114/657909/a85094ec-2f43-4a75-98bc-30312e8b9efc.jpg</t>
+        </is>
+      </c>
       <c r="X263" t="n">
         <v>0</v>
       </c>
@@ -40681,7 +40869,11 @@
         <v>162669</v>
       </c>
       <c r="M265" t="inlineStr"/>
-      <c r="N265" t="inlineStr"/>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>1781980024482</t>
+        </is>
+      </c>
       <c r="O265" t="n">
         <v>0</v>
       </c>
@@ -40702,7 +40894,11 @@
         <v>0</v>
       </c>
       <c r="V265" t="inlineStr"/>
-      <c r="W265" t="inlineStr"/>
+      <c r="W265" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6114/657911/725d8a91-ab9a-4f35-814c-ef8ddf878c5c.jpg</t>
+        </is>
+      </c>
       <c r="X265" t="n">
         <v>0</v>
       </c>
@@ -42767,7 +42963,11 @@
         <v>162621</v>
       </c>
       <c r="M279" t="inlineStr"/>
-      <c r="N279" t="inlineStr"/>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>1781980926348</t>
+        </is>
+      </c>
       <c r="O279" t="n">
         <v>0</v>
       </c>
@@ -42788,7 +42988,11 @@
         <v>0</v>
       </c>
       <c r="V279" t="inlineStr"/>
-      <c r="W279" t="inlineStr"/>
+      <c r="W279" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6107/657871/9c783fde-0214-4580-9379-d2f7bcb2c995.jpg</t>
+        </is>
+      </c>
       <c r="X279" t="n">
         <v>0</v>
       </c>
@@ -45457,7 +45661,11 @@
         <v>162655</v>
       </c>
       <c r="M297" t="inlineStr"/>
-      <c r="N297" t="inlineStr"/>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>1781978762793</t>
+        </is>
+      </c>
       <c r="O297" t="n">
         <v>0</v>
       </c>
@@ -45478,7 +45686,11 @@
         <v>0</v>
       </c>
       <c r="V297" t="inlineStr"/>
-      <c r="W297" t="inlineStr"/>
+      <c r="W297" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6113/657915/8d25ee75-479d-4c68-a859-89a7c1399eab.jpg</t>
+        </is>
+      </c>
       <c r="X297" t="n">
         <v>0</v>
       </c>
@@ -47873,7 +48085,11 @@
         <v>87248</v>
       </c>
       <c r="M313" t="inlineStr"/>
-      <c r="N313" t="inlineStr"/>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>1781981644832</t>
+        </is>
+      </c>
       <c r="O313" t="n">
         <v>0</v>
       </c>
@@ -47894,7 +48110,11 @@
         <v>0</v>
       </c>
       <c r="V313" t="inlineStr"/>
-      <c r="W313" t="inlineStr"/>
+      <c r="W313" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6112/86159/20001914-7215-45ab-8551-a0560f2fdbc9.jpg</t>
+        </is>
+      </c>
       <c r="X313" t="n">
         <v>0</v>
       </c>
@@ -62122,7 +62342,11 @@
         <v>87186</v>
       </c>
       <c r="M408" t="inlineStr"/>
-      <c r="N408" t="inlineStr"/>
+      <c r="N408" t="inlineStr">
+        <is>
+          <t>1781981284033</t>
+        </is>
+      </c>
       <c r="O408" t="n">
         <v>0</v>
       </c>
@@ -62143,7 +62367,11 @@
         <v>0</v>
       </c>
       <c r="V408" t="inlineStr"/>
-      <c r="W408" t="inlineStr"/>
+      <c r="W408" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6106/86097/430f1900-7279-4f52-866e-0d133e7971b1.jpg</t>
+        </is>
+      </c>
       <c r="X408" t="n">
         <v>0</v>
       </c>
@@ -62428,7 +62656,11 @@
         <v>87188</v>
       </c>
       <c r="M410" t="inlineStr"/>
-      <c r="N410" t="inlineStr"/>
+      <c r="N410" t="inlineStr">
+        <is>
+          <t>1781981105893</t>
+        </is>
+      </c>
       <c r="O410" t="n">
         <v>0</v>
       </c>
@@ -62449,7 +62681,11 @@
         <v>0</v>
       </c>
       <c r="V410" t="inlineStr"/>
-      <c r="W410" t="inlineStr"/>
+      <c r="W410" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6106/86099/cdd40037-04ed-4d49-9e3d-0eee3e73db02.jpg</t>
+        </is>
+      </c>
       <c r="X410" t="n">
         <v>0</v>
       </c>
@@ -62726,7 +62962,11 @@
         <v>87190</v>
       </c>
       <c r="M412" t="inlineStr"/>
-      <c r="N412" t="inlineStr"/>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>1781983637572</t>
+        </is>
+      </c>
       <c r="O412" t="n">
         <v>0</v>
       </c>
@@ -62747,7 +62987,11 @@
         <v>0</v>
       </c>
       <c r="V412" t="inlineStr"/>
-      <c r="W412" t="inlineStr"/>
+      <c r="W412" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6106/86101/71e45562-e10d-4988-9245-f271dab418f6.jpg</t>
+        </is>
+      </c>
       <c r="X412" t="n">
         <v>0</v>
       </c>
@@ -63817,7 +64061,11 @@
         <v>162616</v>
       </c>
       <c r="M419" t="inlineStr"/>
-      <c r="N419" t="inlineStr"/>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>1781981464384</t>
+        </is>
+      </c>
       <c r="O419" t="n">
         <v>0</v>
       </c>
@@ -63838,7 +64086,11 @@
         <v>0</v>
       </c>
       <c r="V419" t="inlineStr"/>
-      <c r="W419" t="inlineStr"/>
+      <c r="W419" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6106/657977/7ff55c6f-5cdb-42e1-a3b0-d4ec080efe88.jpg</t>
+        </is>
+      </c>
       <c r="X419" t="n">
         <v>0</v>
       </c>
@@ -63966,7 +64218,11 @@
         <v>162617</v>
       </c>
       <c r="M420" t="inlineStr"/>
-      <c r="N420" t="inlineStr"/>
+      <c r="N420" t="inlineStr">
+        <is>
+          <t>1781981105270</t>
+        </is>
+      </c>
       <c r="O420" t="n">
         <v>0</v>
       </c>
@@ -63987,7 +64243,11 @@
         <v>0</v>
       </c>
       <c r="V420" t="inlineStr"/>
-      <c r="W420" t="inlineStr"/>
+      <c r="W420" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6106/657978/2e2da2c9-cf12-4667-b799-4ebc16623c90.jpg</t>
+        </is>
+      </c>
       <c r="X420" t="n">
         <v>0</v>
       </c>
@@ -66821,7 +67081,11 @@
         <v>162633</v>
       </c>
       <c r="M439" t="inlineStr"/>
-      <c r="N439" t="inlineStr"/>
+      <c r="N439" t="inlineStr">
+        <is>
+          <t>1781982183681</t>
+        </is>
+      </c>
       <c r="O439" t="n">
         <v>0</v>
       </c>
@@ -66842,7 +67106,11 @@
         <v>0</v>
       </c>
       <c r="V439" t="inlineStr"/>
-      <c r="W439" t="inlineStr"/>
+      <c r="W439" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6108/657984/b02a7b91-d1a4-41fb-b945-eeafb7591d93.jpg</t>
+        </is>
+      </c>
       <c r="X439" t="n">
         <v>0</v>
       </c>
@@ -71717,7 +71985,11 @@
         <v>87563</v>
       </c>
       <c r="M471" t="inlineStr"/>
-      <c r="N471" t="inlineStr"/>
+      <c r="N471" t="inlineStr">
+        <is>
+          <t>1781982007410</t>
+        </is>
+      </c>
       <c r="O471" t="n">
         <v>0</v>
       </c>
@@ -71738,7 +72010,11 @@
         <v>0</v>
       </c>
       <c r="V471" t="inlineStr"/>
-      <c r="W471" t="inlineStr"/>
+      <c r="W471" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6143/86474/ba0e6720-71ad-452b-8a17-62bd76e924d9.jpg</t>
+        </is>
+      </c>
       <c r="X471" t="n">
         <v>0</v>
       </c>
@@ -71866,7 +72142,11 @@
         <v>87564</v>
       </c>
       <c r="M472" t="inlineStr"/>
-      <c r="N472" t="inlineStr"/>
+      <c r="N472" t="inlineStr">
+        <is>
+          <t>1781980026988</t>
+        </is>
+      </c>
       <c r="O472" t="n">
         <v>0</v>
       </c>
@@ -71887,7 +72167,11 @@
         <v>0</v>
       </c>
       <c r="V472" t="inlineStr"/>
-      <c r="W472" t="inlineStr"/>
+      <c r="W472" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6143/86475/31020fa9-64f1-4348-b672-fe4c746eb976.jpg</t>
+        </is>
+      </c>
       <c r="X472" t="n">
         <v>0</v>
       </c>
@@ -72313,7 +72597,11 @@
         <v>87567</v>
       </c>
       <c r="M475" t="inlineStr"/>
-      <c r="N475" t="inlineStr"/>
+      <c r="N475" t="inlineStr">
+        <is>
+          <t>1781981109700</t>
+        </is>
+      </c>
       <c r="O475" t="n">
         <v>0</v>
       </c>
@@ -72334,7 +72622,11 @@
         <v>0</v>
       </c>
       <c r="V475" t="inlineStr"/>
-      <c r="W475" t="inlineStr"/>
+      <c r="W475" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6143/86478/72aeeeb5-f673-4f68-ad8e-91d29531c923.jpg</t>
+        </is>
+      </c>
       <c r="X475" t="n">
         <v>0</v>
       </c>
@@ -72917,7 +73209,11 @@
         <v>162915</v>
       </c>
       <c r="M479" t="inlineStr"/>
-      <c r="N479" t="inlineStr"/>
+      <c r="N479" t="inlineStr">
+        <is>
+          <t>1781980025799</t>
+        </is>
+      </c>
       <c r="O479" t="n">
         <v>0</v>
       </c>
@@ -72938,7 +73234,11 @@
         <v>0</v>
       </c>
       <c r="V479" t="inlineStr"/>
-      <c r="W479" t="inlineStr"/>
+      <c r="W479" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6143/658205/2c84e67b-d771-4e1d-b79b-e2a651938197.jpg</t>
+        </is>
+      </c>
       <c r="X479" t="n">
         <v>0</v>
       </c>
@@ -74861,29 +75161,43 @@
       <c r="L492" t="n">
         <v>87573</v>
       </c>
-      <c r="M492" t="inlineStr"/>
-      <c r="N492" t="inlineStr"/>
+      <c r="M492" t="n">
+        <v>1781983634949</v>
+      </c>
+      <c r="N492" t="inlineStr">
+        <is>
+          <t>1781983634443</t>
+        </is>
+      </c>
       <c r="O492" t="n">
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="P492" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="Q492" t="n">
-        <v>0</v>
-      </c>
-      <c r="R492" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="R492" t="inlineStr">
+        <is>
+          <t>6a36e992c89f29392f333ef6</t>
+        </is>
+      </c>
       <c r="S492" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="T492" t="n">
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="U492" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="V492" t="inlineStr"/>
-      <c r="W492" t="inlineStr"/>
+      <c r="W492" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6145/86484/704cf1a0-a1de-47e2-8bfc-111cbdb34210.jpg</t>
+        </is>
+      </c>
       <c r="X492" t="n">
         <v>0</v>
       </c>
@@ -74894,13 +75208,13 @@
         <v>0</v>
       </c>
       <c r="AA492" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AB492" t="n">
         <v>0</v>
       </c>
       <c r="AC492" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="AD492" t="n">
         <v>0</v>
@@ -74918,22 +75232,22 @@
         <v>0</v>
       </c>
       <c r="AI492" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AJ492" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK492" t="n">
         <v>0</v>
       </c>
       <c r="AL492" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM492" t="n">
         <v>0</v>
       </c>
       <c r="AN492" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AO492" t="n">
         <v>0</v>
@@ -75011,7 +75325,11 @@
         <v>87574</v>
       </c>
       <c r="M493" t="inlineStr"/>
-      <c r="N493" t="inlineStr"/>
+      <c r="N493" t="inlineStr">
+        <is>
+          <t>1781983922934</t>
+        </is>
+      </c>
       <c r="O493" t="n">
         <v>0</v>
       </c>
@@ -75032,7 +75350,11 @@
         <v>0</v>
       </c>
       <c r="V493" t="inlineStr"/>
-      <c r="W493" t="inlineStr"/>
+      <c r="W493" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6145/86485/4fa2bc72-ef06-4272-b178-0afe749a5242.jpg</t>
+        </is>
+      </c>
       <c r="X493" t="n">
         <v>0</v>
       </c>
@@ -81035,7 +81357,11 @@
         <v>162923</v>
       </c>
       <c r="M533" t="inlineStr"/>
-      <c r="N533" t="inlineStr"/>
+      <c r="N533" t="inlineStr">
+        <is>
+          <t>1781978588211</t>
+        </is>
+      </c>
       <c r="O533" t="n">
         <v>0</v>
       </c>
@@ -81056,7 +81382,11 @@
         <v>0</v>
       </c>
       <c r="V533" t="inlineStr"/>
-      <c r="W533" t="inlineStr"/>
+      <c r="W533" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6144/658233/dc66e67d-1edb-437a-abd7-41848674807d.jpg</t>
+        </is>
+      </c>
       <c r="X533" t="n">
         <v>0</v>
       </c>
@@ -81184,7 +81514,11 @@
         <v>162924</v>
       </c>
       <c r="M534" t="inlineStr"/>
-      <c r="N534" t="inlineStr"/>
+      <c r="N534" t="inlineStr">
+        <is>
+          <t>1781978588795</t>
+        </is>
+      </c>
       <c r="O534" t="n">
         <v>0</v>
       </c>
@@ -81205,7 +81539,11 @@
         <v>0</v>
       </c>
       <c r="V534" t="inlineStr"/>
-      <c r="W534" t="inlineStr"/>
+      <c r="W534" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6144/658234/e6dd838d-b10a-4d1a-b7b3-b3570214165b.jpg</t>
+        </is>
+      </c>
       <c r="X534" t="n">
         <v>0</v>
       </c>
@@ -81796,7 +82134,11 @@
         <v>87593</v>
       </c>
       <c r="M538" t="inlineStr"/>
-      <c r="N538" t="inlineStr"/>
+      <c r="N538" t="inlineStr">
+        <is>
+          <t>1781983755259</t>
+        </is>
+      </c>
       <c r="O538" t="n">
         <v>0</v>
       </c>
@@ -81817,7 +82159,11 @@
         <v>0</v>
       </c>
       <c r="V538" t="inlineStr"/>
-      <c r="W538" t="inlineStr"/>
+      <c r="W538" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6148/86504/5f408fe7-3968-4a55-b59c-eebdbc41fdf8.jpg</t>
+        </is>
+      </c>
       <c r="X538" t="n">
         <v>0</v>
       </c>
@@ -84111,7 +84457,11 @@
         <v>87583</v>
       </c>
       <c r="M553" t="inlineStr"/>
-      <c r="N553" t="inlineStr"/>
+      <c r="N553" t="inlineStr">
+        <is>
+          <t>1781980391313</t>
+        </is>
+      </c>
       <c r="O553" t="n">
         <v>0</v>
       </c>
@@ -84132,7 +84482,11 @@
         <v>0</v>
       </c>
       <c r="V553" t="inlineStr"/>
-      <c r="W553" t="inlineStr"/>
+      <c r="W553" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6147/86494/b3002622-4e1a-4d55-85a3-c6c1a84ae533.jpg</t>
+        </is>
+      </c>
       <c r="X553" t="n">
         <v>0</v>
       </c>
@@ -85177,29 +85531,43 @@
       <c r="L560" t="n">
         <v>87590</v>
       </c>
-      <c r="M560" t="inlineStr"/>
-      <c r="N560" t="inlineStr"/>
+      <c r="M560" t="n">
+        <v>1781982547383</v>
+      </c>
+      <c r="N560" t="inlineStr">
+        <is>
+          <t>1781982546791</t>
+        </is>
+      </c>
       <c r="O560" t="n">
-        <v>0</v>
+        <v>824</v>
       </c>
       <c r="P560" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="Q560" t="n">
-        <v>0</v>
-      </c>
-      <c r="R560" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="R560" t="inlineStr">
+        <is>
+          <t>6a36e552c89f29392f333e54</t>
+        </is>
+      </c>
       <c r="S560" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="T560" t="n">
-        <v>0</v>
+        <v>823</v>
       </c>
       <c r="U560" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="V560" t="inlineStr"/>
-      <c r="W560" t="inlineStr"/>
+      <c r="W560" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6147/86501/9592c459-03f8-4136-b8a4-83b94f7ddb8b.jpg</t>
+        </is>
+      </c>
       <c r="X560" t="n">
         <v>0</v>
       </c>
@@ -85210,13 +85578,13 @@
         <v>0</v>
       </c>
       <c r="AA560" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB560" t="n">
         <v>0</v>
       </c>
       <c r="AC560" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AD560" t="n">
         <v>0</v>
@@ -85234,10 +85602,10 @@
         <v>0</v>
       </c>
       <c r="AI560" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ560" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AK560" t="n">
         <v>0</v>
@@ -85249,7 +85617,7 @@
         <v>0</v>
       </c>
       <c r="AN560" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AO560" t="n">
         <v>0</v>
@@ -86269,7 +86637,11 @@
         <v>162942</v>
       </c>
       <c r="M567" t="inlineStr"/>
-      <c r="N567" t="inlineStr"/>
+      <c r="N567" t="inlineStr">
+        <is>
+          <t>1781980744281</t>
+        </is>
+      </c>
       <c r="O567" t="n">
         <v>0</v>
       </c>
@@ -86290,7 +86662,11 @@
         <v>0</v>
       </c>
       <c r="V567" t="inlineStr"/>
-      <c r="W567" t="inlineStr"/>
+      <c r="W567" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6147/658250/98ff9de7-6ee8-4362-925c-69c15591d66e.jpg</t>
+        </is>
+      </c>
       <c r="X567" t="n">
         <v>0</v>
       </c>
@@ -86889,7 +87265,11 @@
         <v>162946</v>
       </c>
       <c r="M571" t="inlineStr"/>
-      <c r="N571" t="inlineStr"/>
+      <c r="N571" t="inlineStr">
+        <is>
+          <t>1781979676396</t>
+        </is>
+      </c>
       <c r="O571" t="n">
         <v>0</v>
       </c>
@@ -86910,7 +87290,11 @@
         <v>0</v>
       </c>
       <c r="V571" t="inlineStr"/>
-      <c r="W571" t="inlineStr"/>
+      <c r="W571" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6147/658254/bcea42de-8312-47cd-b130-de4a302eafbe.jpg</t>
+        </is>
+      </c>
       <c r="X571" t="n">
         <v>0</v>
       </c>
@@ -88934,168 +89318,178 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF36"/>
+  <dimension ref="A1:AH36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>LGA</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Ward</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Polling Units</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>INEC Uploaded Results</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>INEC Upload Percent</t>
         </is>
       </c>
     </row>
@@ -89202,6 +89596,12 @@
       <c r="AF2" t="n">
         <v>12</v>
       </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -89306,6 +89706,12 @@
       <c r="AF3" t="n">
         <v>40</v>
       </c>
+      <c r="AG3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -89410,6 +89816,12 @@
       <c r="AF4" t="n">
         <v>46</v>
       </c>
+      <c r="AG4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>69.59999999999999</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -89514,6 +89926,12 @@
       <c r="AF5" t="n">
         <v>10</v>
       </c>
+      <c r="AG5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -89618,6 +90036,12 @@
       <c r="AF6" t="n">
         <v>17</v>
       </c>
+      <c r="AG6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>41.2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -89722,6 +90146,12 @@
       <c r="AF7" t="n">
         <v>14</v>
       </c>
+      <c r="AG7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>35.7</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -89826,6 +90256,12 @@
       <c r="AF8" t="n">
         <v>14</v>
       </c>
+      <c r="AG8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>78.59999999999999</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -89931,6 +90367,12 @@
       <c r="AF9" t="n">
         <v>12</v>
       </c>
+      <c r="AG9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>33.3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -90035,6 +90477,12 @@
       <c r="AF10" t="n">
         <v>17</v>
       </c>
+      <c r="AG10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>17.6</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -90139,6 +90587,12 @@
       <c r="AF11" t="n">
         <v>12</v>
       </c>
+      <c r="AG11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -90243,6 +90697,12 @@
       <c r="AF12" t="n">
         <v>12</v>
       </c>
+      <c r="AG12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>58.3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -90347,6 +90807,12 @@
       <c r="AF13" t="n">
         <v>10</v>
       </c>
+      <c r="AG13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -90451,6 +90917,12 @@
       <c r="AF14" t="n">
         <v>12</v>
       </c>
+      <c r="AG14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>16.7</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -90555,6 +91027,12 @@
       <c r="AF15" t="n">
         <v>22</v>
       </c>
+      <c r="AG15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>9.1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -90659,6 +91137,12 @@
       <c r="AF16" t="n">
         <v>16</v>
       </c>
+      <c r="AG16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>43.8</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -90763,6 +91247,12 @@
       <c r="AF17" t="n">
         <v>19</v>
       </c>
+      <c r="AG17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>10.5</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -90867,6 +91357,12 @@
       <c r="AF18" t="n">
         <v>16</v>
       </c>
+      <c r="AG18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>12.5</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -90971,6 +91467,12 @@
       <c r="AF19" t="n">
         <v>15</v>
       </c>
+      <c r="AG19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>46.7</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -91075,6 +91577,12 @@
       <c r="AF20" t="n">
         <v>8</v>
       </c>
+      <c r="AG20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>12.5</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -91179,6 +91687,12 @@
       <c r="AF21" t="n">
         <v>15</v>
       </c>
+      <c r="AG21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>6.7</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -91283,6 +91797,12 @@
       <c r="AF22" t="n">
         <v>17</v>
       </c>
+      <c r="AG22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>29.4</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -91387,6 +91907,12 @@
       <c r="AF23" t="n">
         <v>50</v>
       </c>
+      <c r="AG23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -91491,6 +92017,12 @@
       <c r="AF24" t="n">
         <v>14</v>
       </c>
+      <c r="AG24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>92.90000000000001</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -91595,6 +92127,12 @@
       <c r="AF25" t="n">
         <v>19</v>
       </c>
+      <c r="AG25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>21.1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -91699,6 +92237,12 @@
       <c r="AF26" t="n">
         <v>22</v>
       </c>
+      <c r="AG26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>63.6</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -91803,6 +92347,12 @@
       <c r="AF27" t="n">
         <v>8</v>
       </c>
+      <c r="AG27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>12.5</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -91907,6 +92457,12 @@
       <c r="AF28" t="n">
         <v>12</v>
       </c>
+      <c r="AG28" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -92011,6 +92567,12 @@
       <c r="AF29" t="n">
         <v>9</v>
       </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -92029,22 +92591,22 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -92056,13 +92618,13 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
@@ -92080,22 +92642,22 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W30" t="n">
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y30" t="n">
         <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -92114,6 +92676,12 @@
       </c>
       <c r="AF30" t="n">
         <v>7</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>28.6</v>
       </c>
     </row>
     <row r="31">
@@ -92219,6 +92787,12 @@
       <c r="AF31" t="n">
         <v>14</v>
       </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -92323,6 +92897,12 @@
       <c r="AF32" t="n">
         <v>11</v>
       </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -92427,6 +93007,12 @@
       <c r="AF33" t="n">
         <v>12</v>
       </c>
+      <c r="AG33" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>91.7</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -92531,6 +93117,12 @@
       <c r="AF34" t="n">
         <v>17</v>
       </c>
+      <c r="AG34" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>70.59999999999999</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -92549,22 +93141,22 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>824</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>823</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -92576,13 +93168,13 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -92600,10 +93192,10 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W35" t="n">
         <v>0</v>
@@ -92615,7 +93207,7 @@
         <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -92634,6 +93226,12 @@
       </c>
       <c r="AF35" t="n">
         <v>19</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>84.2</v>
       </c>
     </row>
     <row r="36">
@@ -92738,6 +93336,12 @@
       </c>
       <c r="AF36" t="n">
         <v>13</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -92751,163 +93355,173 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE4"/>
+  <dimension ref="A1:AG4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>LGA</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Polling Units</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>INEC Uploaded Results</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>INEC Upload Percent</t>
         </is>
       </c>
     </row>
@@ -93009,6 +93623,12 @@
       <c r="AE2" t="n">
         <v>206</v>
       </c>
+      <c r="AF2" t="n">
+        <v>104</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>50.5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -93108,6 +93728,12 @@
       <c r="AE3" t="n">
         <v>255</v>
       </c>
+      <c r="AF3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>25.9</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -93121,22 +93747,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1574</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1573</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>209</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -93148,13 +93774,13 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -93172,22 +93798,22 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -93206,6 +93832,12 @@
       </c>
       <c r="AE4" t="n">
         <v>122</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>49</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>40.2</v>
       </c>
     </row>
   </sheetData>
@@ -93219,158 +93851,173 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD2"/>
+  <dimension ref="A1:AG2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Polling Units</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>INEC Uploaded Results</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>INEC Expected Results</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>INEC Upload Percent</t>
         </is>
       </c>
     </row>
@@ -93381,22 +94028,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>176</v>
+        <v>1750</v>
       </c>
       <c r="C2" t="n">
-        <v>87</v>
+        <v>302</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>83</v>
+        <v>298</v>
       </c>
       <c r="F2" t="n">
-        <v>176</v>
+        <v>1749</v>
       </c>
       <c r="G2" t="n">
-        <v>83</v>
+        <v>292</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -93408,13 +94055,13 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>55</v>
+        <v>187</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -93432,22 +94079,22 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
+        <v>36</v>
+      </c>
+      <c r="T2" t="n">
         <v>14</v>
       </c>
-      <c r="T2" t="n">
-        <v>1</v>
-      </c>
       <c r="U2" t="n">
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -93466,6 +94113,15 @@
       </c>
       <c r="AD2" t="n">
         <v>583</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>219</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>583</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>37.6</v>
       </c>
     </row>
   </sheetData>

--- a/output/Nasarawa/results.xlsx
+++ b/output/Nasarawa/results.xlsx
@@ -20664,7 +20664,11 @@
         <v>86117</v>
       </c>
       <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>1781985243008</t>
+        </is>
+      </c>
       <c r="O132" t="n">
         <v>0</v>
       </c>
@@ -20685,7 +20689,11 @@
         <v>0</v>
       </c>
       <c r="V132" t="inlineStr"/>
-      <c r="W132" t="inlineStr"/>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6008/85053/f14edfb4-9d79-4b46-a80d-bac4d2ff237f.jpg</t>
+        </is>
+      </c>
       <c r="X132" t="n">
         <v>0</v>
       </c>
@@ -41175,7 +41183,11 @@
         <v>162671</v>
       </c>
       <c r="M267" t="inlineStr"/>
-      <c r="N267" t="inlineStr"/>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>1781985422478</t>
+        </is>
+      </c>
       <c r="O267" t="n">
         <v>0</v>
       </c>
@@ -41196,7 +41208,11 @@
         <v>0</v>
       </c>
       <c r="V267" t="inlineStr"/>
-      <c r="W267" t="inlineStr"/>
+      <c r="W267" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6114/657913/4ee608dd-fbc3-4130-941c-4a86fc3c2b4b.jpg</t>
+        </is>
+      </c>
       <c r="X267" t="n">
         <v>0</v>
       </c>
@@ -73515,7 +73531,11 @@
         <v>162917</v>
       </c>
       <c r="M481" t="inlineStr"/>
-      <c r="N481" t="inlineStr"/>
+      <c r="N481" t="inlineStr">
+        <is>
+          <t>1781984883117</t>
+        </is>
+      </c>
       <c r="O481" t="n">
         <v>0</v>
       </c>
@@ -73536,7 +73556,11 @@
         <v>0</v>
       </c>
       <c r="V481" t="inlineStr"/>
-      <c r="W481" t="inlineStr"/>
+      <c r="W481" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6143/658207/eabfb1ad-f7d4-4f20-9893-3e9e87fa3d75.jpg</t>
+        </is>
+      </c>
       <c r="X481" t="n">
         <v>0</v>
       </c>
@@ -90147,10 +90171,10 @@
         <v>14</v>
       </c>
       <c r="AG7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH7" t="n">
-        <v>35.7</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="8">
@@ -91138,10 +91162,10 @@
         <v>16</v>
       </c>
       <c r="AG16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH16" t="n">
-        <v>43.8</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -92458,10 +92482,10 @@
         <v>12</v>
       </c>
       <c r="AG28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH28" t="n">
-        <v>50</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="29">
@@ -93624,10 +93648,10 @@
         <v>206</v>
       </c>
       <c r="AF2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG2" t="n">
-        <v>50.5</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3">
@@ -93729,10 +93753,10 @@
         <v>255</v>
       </c>
       <c r="AF3" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AG3" t="n">
-        <v>25.9</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="4">
@@ -93834,10 +93858,10 @@
         <v>122</v>
       </c>
       <c r="AF4" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AG4" t="n">
-        <v>40.2</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -94115,13 +94139,13 @@
         <v>583</v>
       </c>
       <c r="AE2" t="n">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="AF2" t="n">
         <v>583</v>
       </c>
       <c r="AG2" t="n">
-        <v>37.6</v>
+        <v>38.1</v>
       </c>
     </row>
   </sheetData>

--- a/output/Nasarawa/results.xlsx
+++ b/output/Nasarawa/results.xlsx
@@ -93648,10 +93648,10 @@
         <v>206</v>
       </c>
       <c r="AF2" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -93753,10 +93753,10 @@
         <v>255</v>
       </c>
       <c r="AF3" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>26.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -93858,10 +93858,10 @@
         <v>122</v>
       </c>
       <c r="AF4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -94139,13 +94139,13 @@
         <v>583</v>
       </c>
       <c r="AE2" t="n">
-        <v>222</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
         <v>583</v>
       </c>
       <c r="AG2" t="n">
-        <v>38.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/Nasarawa/results.xlsx
+++ b/output/Nasarawa/results.xlsx
@@ -93648,10 +93648,10 @@
         <v>206</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3">
@@ -93753,10 +93753,10 @@
         <v>255</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="4">
@@ -93858,10 +93858,10 @@
         <v>122</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -94139,13 +94139,13 @@
         <v>583</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="AF2" t="n">
         <v>583</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>38.1</v>
       </c>
     </row>
   </sheetData>

--- a/output/Nasarawa/results.xlsx
+++ b/output/Nasarawa/results.xlsx
@@ -20,16 +20,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,227 +420,227 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>LGA</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Election ID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Election Name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Election Date</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Ward</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Ward Code</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Ward ID</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Polling Unit</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>PU Code</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>PU ID</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Polling Unit ID</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Result Updated Time</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Session</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Result Info PU</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Image File</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Image URL</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
@@ -3746,7 +3734,11 @@
         <v>86151</v>
       </c>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>1781989195413</t>
+        </is>
+      </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
@@ -3767,7 +3759,11 @@
         <v>0</v>
       </c>
       <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6013/85087/d752697f-d3ea-419b-81b8-1fc998062fe2.jpg</t>
+        </is>
+      </c>
       <c r="X22" t="n">
         <v>0</v>
       </c>
@@ -7309,7 +7305,11 @@
         <v>161327</v>
       </c>
       <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>1781989199034</t>
+        </is>
+      </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
@@ -7330,7 +7330,11 @@
         <v>0</v>
       </c>
       <c r="V45" t="inlineStr"/>
-      <c r="W45" t="inlineStr"/>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6013/656533/75b96c02-f5ed-4a51-b566-b6e3f6cf5260.jpg</t>
+        </is>
+      </c>
       <c r="X45" t="n">
         <v>0</v>
       </c>
@@ -16404,7 +16408,11 @@
         <v>161230</v>
       </c>
       <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>1781989159605</t>
+        </is>
+      </c>
       <c r="O104" t="n">
         <v>0</v>
       </c>
@@ -16425,7 +16433,11 @@
         <v>0</v>
       </c>
       <c r="V104" t="inlineStr"/>
-      <c r="W104" t="inlineStr"/>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6007/656593/6cf290cb-5d2f-4d5f-be45-0c3b6c1d6b5a.jpg</t>
+        </is>
+      </c>
       <c r="X104" t="n">
         <v>0</v>
       </c>
@@ -19299,7 +19311,11 @@
         <v>161218</v>
       </c>
       <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>1781989184964</t>
+        </is>
+      </c>
       <c r="O123" t="n">
         <v>0</v>
       </c>
@@ -19320,7 +19336,11 @@
         <v>0</v>
       </c>
       <c r="V123" t="inlineStr"/>
-      <c r="W123" t="inlineStr"/>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6004/656584/33cd2004-b12c-4924-9ee4-55b4cc7e0e81.jpg</t>
+        </is>
+      </c>
       <c r="X123" t="n">
         <v>0</v>
       </c>
@@ -19911,7 +19931,11 @@
         <v>86112</v>
       </c>
       <c r="M127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>1781989126433</t>
+        </is>
+      </c>
       <c r="O127" t="n">
         <v>0</v>
       </c>
@@ -19932,7 +19956,11 @@
         <v>0</v>
       </c>
       <c r="V127" t="inlineStr"/>
-      <c r="W127" t="inlineStr"/>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6008/85048/5103cce4-a1d1-47b6-9820-090f14f5a213.jpg</t>
+        </is>
+      </c>
       <c r="X127" t="n">
         <v>0</v>
       </c>
@@ -20060,7 +20088,11 @@
         <v>86113</v>
       </c>
       <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>1781989208984</t>
+        </is>
+      </c>
       <c r="O128" t="n">
         <v>0</v>
       </c>
@@ -20081,7 +20113,11 @@
         <v>0</v>
       </c>
       <c r="V128" t="inlineStr"/>
-      <c r="W128" t="inlineStr"/>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6008/85049/83c63999-71d5-4df0-b52a-ca349ca3b093.jpg</t>
+        </is>
+      </c>
       <c r="X128" t="n">
         <v>0</v>
       </c>
@@ -20209,7 +20245,11 @@
         <v>86114</v>
       </c>
       <c r="M129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>1781989183281</t>
+        </is>
+      </c>
       <c r="O129" t="n">
         <v>0</v>
       </c>
@@ -20230,7 +20270,11 @@
         <v>0</v>
       </c>
       <c r="V129" t="inlineStr"/>
-      <c r="W129" t="inlineStr"/>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6008/85050/00e06398-f150-41b2-8c54-edf9d8a5df91.jpg</t>
+        </is>
+      </c>
       <c r="X129" t="n">
         <v>0</v>
       </c>
@@ -20515,7 +20559,11 @@
         <v>86116</v>
       </c>
       <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>1781989175326</t>
+        </is>
+      </c>
       <c r="O131" t="n">
         <v>0</v>
       </c>
@@ -20536,7 +20584,11 @@
         <v>0</v>
       </c>
       <c r="V131" t="inlineStr"/>
-      <c r="W131" t="inlineStr"/>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6008/85052/f74caea8-7186-432b-8f84-f3a5c118b038.jpg</t>
+        </is>
+      </c>
       <c r="X131" t="n">
         <v>0</v>
       </c>
@@ -21284,7 +21336,11 @@
         <v>161239</v>
       </c>
       <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>1781989154608</t>
+        </is>
+      </c>
       <c r="O136" t="n">
         <v>0</v>
       </c>
@@ -21305,7 +21361,11 @@
         <v>0</v>
       </c>
       <c r="V136" t="inlineStr"/>
-      <c r="W136" t="inlineStr"/>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6008/656597/f7c2eb32-fa4e-4672-885b-b448b6cda981.jpg</t>
+        </is>
+      </c>
       <c r="X136" t="n">
         <v>0</v>
       </c>
@@ -21433,7 +21493,11 @@
         <v>161240</v>
       </c>
       <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>1781989139490</t>
+        </is>
+      </c>
       <c r="O137" t="n">
         <v>0</v>
       </c>
@@ -21454,7 +21518,11 @@
         <v>0</v>
       </c>
       <c r="V137" t="inlineStr"/>
-      <c r="W137" t="inlineStr"/>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6008/656598/d9a56e24-666d-438b-a620-f7023f72b523.jpg</t>
+        </is>
+      </c>
       <c r="X137" t="n">
         <v>0</v>
       </c>
@@ -21582,7 +21650,11 @@
         <v>161241</v>
       </c>
       <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>1781989187423</t>
+        </is>
+      </c>
       <c r="O138" t="n">
         <v>0</v>
       </c>
@@ -21603,7 +21675,11 @@
         <v>0</v>
       </c>
       <c r="V138" t="inlineStr"/>
-      <c r="W138" t="inlineStr"/>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6008/656599/0e248ce5-405d-4367-8ff2-d088c0069d65.jpg</t>
+        </is>
+      </c>
       <c r="X138" t="n">
         <v>0</v>
       </c>
@@ -22202,7 +22278,11 @@
         <v>86124</v>
       </c>
       <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>1781989167915</t>
+        </is>
+      </c>
       <c r="O142" t="n">
         <v>0</v>
       </c>
@@ -22223,7 +22303,11 @@
         <v>0</v>
       </c>
       <c r="V142" t="inlineStr"/>
-      <c r="W142" t="inlineStr"/>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6010/85060/ce1fbd29-c14d-4a4a-9dd4-02ef5913b1aa.jpg</t>
+        </is>
+      </c>
       <c r="X142" t="n">
         <v>0</v>
       </c>
@@ -23293,7 +23377,11 @@
         <v>161255</v>
       </c>
       <c r="M149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>1781989159754</t>
+        </is>
+      </c>
       <c r="O149" t="n">
         <v>0</v>
       </c>
@@ -23314,7 +23402,11 @@
         <v>0</v>
       </c>
       <c r="V149" t="inlineStr"/>
-      <c r="W149" t="inlineStr"/>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6010/656606/89c93f9f-8413-4633-9175-0f81b94e356e.jpg</t>
+        </is>
+      </c>
       <c r="X149" t="n">
         <v>0</v>
       </c>
@@ -23599,7 +23691,11 @@
         <v>161257</v>
       </c>
       <c r="M151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>1781989177144</t>
+        </is>
+      </c>
       <c r="O151" t="n">
         <v>0</v>
       </c>
@@ -23620,7 +23716,11 @@
         <v>0</v>
       </c>
       <c r="V151" t="inlineStr"/>
-      <c r="W151" t="inlineStr"/>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6010/656608/ae502915-6d49-4d9d-bd62-ad34bb5e1f7e.jpg</t>
+        </is>
+      </c>
       <c r="X151" t="n">
         <v>0</v>
       </c>
@@ -24528,7 +24628,11 @@
         <v>86106</v>
       </c>
       <c r="M157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>1781989134235</t>
+        </is>
+      </c>
       <c r="O157" t="n">
         <v>0</v>
       </c>
@@ -24549,7 +24653,11 @@
         <v>0</v>
       </c>
       <c r="V157" t="inlineStr"/>
-      <c r="W157" t="inlineStr"/>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6006/85042/53f00a54-63a3-430c-9831-8ee7e37281d5.jpg</t>
+        </is>
+      </c>
       <c r="X157" t="n">
         <v>0</v>
       </c>
@@ -25144,7 +25252,11 @@
         <v>161224</v>
       </c>
       <c r="M161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>1781989130433</t>
+        </is>
+      </c>
       <c r="O161" t="n">
         <v>0</v>
       </c>
@@ -25165,7 +25277,11 @@
         <v>0</v>
       </c>
       <c r="V161" t="inlineStr"/>
-      <c r="W161" t="inlineStr"/>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6006/656613/e1753a3c-631f-40e2-98d3-b42989715527.jpg</t>
+        </is>
+      </c>
       <c r="X161" t="n">
         <v>0</v>
       </c>
@@ -25294,7 +25410,11 @@
         <v>161225</v>
       </c>
       <c r="M162" t="inlineStr"/>
-      <c r="N162" t="inlineStr"/>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>1781989177732</t>
+        </is>
+      </c>
       <c r="O162" t="n">
         <v>0</v>
       </c>
@@ -25315,7 +25435,11 @@
         <v>0</v>
       </c>
       <c r="V162" t="inlineStr"/>
-      <c r="W162" t="inlineStr"/>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6006/656614/0326bae0-ed39-4cc9-84ee-b5eeb05d992f.jpg</t>
+        </is>
+      </c>
       <c r="X162" t="n">
         <v>0</v>
       </c>
@@ -26051,7 +26175,11 @@
         <v>86127</v>
       </c>
       <c r="M167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>1781989132041</t>
+        </is>
+      </c>
       <c r="O167" t="n">
         <v>0</v>
       </c>
@@ -26072,7 +26200,11 @@
         <v>0</v>
       </c>
       <c r="V167" t="inlineStr"/>
-      <c r="W167" t="inlineStr"/>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6011/85063/40e10822-0cbc-44a9-ba89-fef3c8088fd9.jpg</t>
+        </is>
+      </c>
       <c r="X167" t="n">
         <v>0</v>
       </c>
@@ -26647,7 +26779,11 @@
         <v>86131</v>
       </c>
       <c r="M171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>1781989146259</t>
+        </is>
+      </c>
       <c r="O171" t="n">
         <v>0</v>
       </c>
@@ -26668,7 +26804,11 @@
         <v>0</v>
       </c>
       <c r="V171" t="inlineStr"/>
-      <c r="W171" t="inlineStr"/>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6011/85067/36c1657b-5ed8-4df7-a5fe-ba49d30d124d.jpg</t>
+        </is>
+      </c>
       <c r="X171" t="n">
         <v>0</v>
       </c>
@@ -26796,7 +26936,11 @@
         <v>86132</v>
       </c>
       <c r="M172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>1781988844820</t>
+        </is>
+      </c>
       <c r="O172" t="n">
         <v>0</v>
       </c>
@@ -26817,7 +26961,11 @@
         <v>0</v>
       </c>
       <c r="V172" t="inlineStr"/>
-      <c r="W172" t="inlineStr"/>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6011/85068/84f47fad-79c7-401c-b859-0b03fada2b02.jpg</t>
+        </is>
+      </c>
       <c r="X172" t="n">
         <v>0</v>
       </c>
@@ -26945,7 +27093,11 @@
         <v>86133</v>
       </c>
       <c r="M173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>1781989052179</t>
+        </is>
+      </c>
       <c r="O173" t="n">
         <v>0</v>
       </c>
@@ -26966,7 +27118,11 @@
         <v>0</v>
       </c>
       <c r="V173" t="inlineStr"/>
-      <c r="W173" t="inlineStr"/>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6011/85069/12d9fbf8-7ab6-40c0-ac9d-04b6f96c6d86.jpg</t>
+        </is>
+      </c>
       <c r="X173" t="n">
         <v>0</v>
       </c>
@@ -27400,7 +27556,11 @@
         <v>161263</v>
       </c>
       <c r="M176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>1781989151881</t>
+        </is>
+      </c>
       <c r="O176" t="n">
         <v>0</v>
       </c>
@@ -27421,7 +27581,11 @@
         <v>0</v>
       </c>
       <c r="V176" t="inlineStr"/>
-      <c r="W176" t="inlineStr"/>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6011/656622/c485c251-a5dd-44c3-aecc-833fd585af50.jpg</t>
+        </is>
+      </c>
       <c r="X176" t="n">
         <v>0</v>
       </c>
@@ -27549,7 +27713,11 @@
         <v>161264</v>
       </c>
       <c r="M177" t="inlineStr"/>
-      <c r="N177" t="inlineStr"/>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>1781989200652</t>
+        </is>
+      </c>
       <c r="O177" t="n">
         <v>0</v>
       </c>
@@ -27570,7 +27738,11 @@
         <v>0</v>
       </c>
       <c r="V177" t="inlineStr"/>
-      <c r="W177" t="inlineStr"/>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6011/656623/b8355a8a-5ffa-45bf-baa9-d6e59b8e5066.jpg</t>
+        </is>
+      </c>
       <c r="X177" t="n">
         <v>0</v>
       </c>
@@ -27698,7 +27870,11 @@
         <v>161265</v>
       </c>
       <c r="M178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>1781989194228</t>
+        </is>
+      </c>
       <c r="O178" t="n">
         <v>0</v>
       </c>
@@ -27719,7 +27895,11 @@
         <v>0</v>
       </c>
       <c r="V178" t="inlineStr"/>
-      <c r="W178" t="inlineStr"/>
+      <c r="W178" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6011/656624/26d9ec6b-dae0-40d5-a90a-b1c9033098df.jpg</t>
+        </is>
+      </c>
       <c r="X178" t="n">
         <v>0</v>
       </c>
@@ -30734,7 +30914,11 @@
         <v>86120</v>
       </c>
       <c r="M198" t="inlineStr"/>
-      <c r="N198" t="inlineStr"/>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>1781989127261</t>
+        </is>
+      </c>
       <c r="O198" t="n">
         <v>0</v>
       </c>
@@ -30755,7 +30939,11 @@
         <v>0</v>
       </c>
       <c r="V198" t="inlineStr"/>
-      <c r="W198" t="inlineStr"/>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6009/85056/1c2bf788-86bf-491b-93e0-9bf991a52ad6.jpg</t>
+        </is>
+      </c>
       <c r="X198" t="n">
         <v>0</v>
       </c>
@@ -31040,7 +31228,11 @@
         <v>86122</v>
       </c>
       <c r="M200" t="inlineStr"/>
-      <c r="N200" t="inlineStr"/>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>1781989149522</t>
+        </is>
+      </c>
       <c r="O200" t="n">
         <v>0</v>
       </c>
@@ -31061,7 +31253,11 @@
         <v>0</v>
       </c>
       <c r="V200" t="inlineStr"/>
-      <c r="W200" t="inlineStr"/>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6009/85058/55b68f11-06bb-47a1-b003-0587d0943135.jpg</t>
+        </is>
+      </c>
       <c r="X200" t="n">
         <v>0</v>
       </c>
@@ -36053,7 +36249,11 @@
         <v>87281</v>
       </c>
       <c r="M233" t="inlineStr"/>
-      <c r="N233" t="inlineStr"/>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>1781989189254</t>
+        </is>
+      </c>
       <c r="O233" t="n">
         <v>0</v>
       </c>
@@ -36074,7 +36274,11 @@
         <v>0</v>
       </c>
       <c r="V233" t="inlineStr"/>
-      <c r="W233" t="inlineStr"/>
+      <c r="W233" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6117/86192/dc2ed034-273d-4855-b0fb-0df122626557.jpg</t>
+        </is>
+      </c>
       <c r="X233" t="n">
         <v>0</v>
       </c>
@@ -38892,7 +39096,11 @@
         <v>87258</v>
       </c>
       <c r="M252" t="inlineStr"/>
-      <c r="N252" t="inlineStr"/>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>1781989186833</t>
+        </is>
+      </c>
       <c r="O252" t="n">
         <v>0</v>
       </c>
@@ -38913,7 +39121,11 @@
         <v>0</v>
       </c>
       <c r="V252" t="inlineStr"/>
-      <c r="W252" t="inlineStr"/>
+      <c r="W252" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6114/86169/d381f779-e11e-4ac4-9054-90613813ee05.jpg</t>
+        </is>
+      </c>
       <c r="X252" t="n">
         <v>0</v>
       </c>
@@ -39339,7 +39551,11 @@
         <v>87261</v>
       </c>
       <c r="M255" t="inlineStr"/>
-      <c r="N255" t="inlineStr"/>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>1781989169658</t>
+        </is>
+      </c>
       <c r="O255" t="n">
         <v>0</v>
       </c>
@@ -39360,7 +39576,11 @@
         <v>0</v>
       </c>
       <c r="V255" t="inlineStr"/>
-      <c r="W255" t="inlineStr"/>
+      <c r="W255" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6114/86172/91044d3e-f17a-4199-9aaa-a40d88ec93e2.jpg</t>
+        </is>
+      </c>
       <c r="X255" t="n">
         <v>0</v>
       </c>
@@ -41034,7 +41254,11 @@
         <v>162670</v>
       </c>
       <c r="M266" t="inlineStr"/>
-      <c r="N266" t="inlineStr"/>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>1781987723919</t>
+        </is>
+      </c>
       <c r="O266" t="n">
         <v>0</v>
       </c>
@@ -41055,7 +41279,11 @@
         <v>0</v>
       </c>
       <c r="V266" t="inlineStr"/>
-      <c r="W266" t="inlineStr"/>
+      <c r="W266" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6114/657912/94a6b183-aa9c-413b-baa6-da73f61c0ef4.jpg</t>
+        </is>
+      </c>
       <c r="X266" t="n">
         <v>0</v>
       </c>
@@ -43732,7 +43960,11 @@
         <v>162626</v>
       </c>
       <c r="M284" t="inlineStr"/>
-      <c r="N284" t="inlineStr"/>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>1781992646434</t>
+        </is>
+      </c>
       <c r="O284" t="n">
         <v>0</v>
       </c>
@@ -43753,7 +43985,11 @@
         <v>0</v>
       </c>
       <c r="V284" t="inlineStr"/>
-      <c r="W284" t="inlineStr"/>
+      <c r="W284" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6107/657876/de9197f8-42c5-4c9c-8152-85fc73788653.jpg</t>
+        </is>
+      </c>
       <c r="X284" t="n">
         <v>0</v>
       </c>
@@ -46744,7 +46980,11 @@
         <v>87239</v>
       </c>
       <c r="M304" t="inlineStr"/>
-      <c r="N304" t="inlineStr"/>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>1781989326684</t>
+        </is>
+      </c>
       <c r="O304" t="n">
         <v>0</v>
       </c>
@@ -46765,7 +47005,11 @@
         <v>0</v>
       </c>
       <c r="V304" t="inlineStr"/>
-      <c r="W304" t="inlineStr"/>
+      <c r="W304" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6112/86150/668850f2-9714-4b85-acc5-f53f27897ffb.jpg</t>
+        </is>
+      </c>
       <c r="X304" t="n">
         <v>0</v>
       </c>
@@ -47191,7 +47435,11 @@
         <v>87242</v>
       </c>
       <c r="M307" t="inlineStr"/>
-      <c r="N307" t="inlineStr"/>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>1781989210669</t>
+        </is>
+      </c>
       <c r="O307" t="n">
         <v>0</v>
       </c>
@@ -47212,7 +47460,11 @@
         <v>0</v>
       </c>
       <c r="V307" t="inlineStr"/>
-      <c r="W307" t="inlineStr"/>
+      <c r="W307" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6112/86153/0ecee4ba-938c-4fc0-b301-0b1c74a3ecc6.jpg</t>
+        </is>
+      </c>
       <c r="X307" t="n">
         <v>0</v>
       </c>
@@ -47646,7 +47898,11 @@
         <v>87245</v>
       </c>
       <c r="M310" t="inlineStr"/>
-      <c r="N310" t="inlineStr"/>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>1781989191813</t>
+        </is>
+      </c>
       <c r="O310" t="n">
         <v>0</v>
       </c>
@@ -47667,7 +47923,11 @@
         <v>0</v>
       </c>
       <c r="V310" t="inlineStr"/>
-      <c r="W310" t="inlineStr"/>
+      <c r="W310" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6112/86156/5624c763-39a0-4824-81db-0b9f4a56733b.jpg</t>
+        </is>
+      </c>
       <c r="X310" t="n">
         <v>0</v>
       </c>
@@ -47952,7 +48212,11 @@
         <v>87247</v>
       </c>
       <c r="M312" t="inlineStr"/>
-      <c r="N312" t="inlineStr"/>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>1781989181394</t>
+        </is>
+      </c>
       <c r="O312" t="n">
         <v>0</v>
       </c>
@@ -47973,7 +48237,11 @@
         <v>0</v>
       </c>
       <c r="V312" t="inlineStr"/>
-      <c r="W312" t="inlineStr"/>
+      <c r="W312" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6112/86158/18b6152b-6510-4c30-b6fb-1afac1d8368e.jpg</t>
+        </is>
+      </c>
       <c r="X312" t="n">
         <v>0</v>
       </c>
@@ -48415,7 +48683,11 @@
         <v>162651</v>
       </c>
       <c r="M315" t="inlineStr"/>
-      <c r="N315" t="inlineStr"/>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>1781988978579</t>
+        </is>
+      </c>
       <c r="O315" t="n">
         <v>0</v>
       </c>
@@ -48436,7 +48708,11 @@
         <v>0</v>
       </c>
       <c r="V315" t="inlineStr"/>
-      <c r="W315" t="inlineStr"/>
+      <c r="W315" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6112/657880/496e9e9f-d918-4ae1-9c63-6844be8775b3.jpg</t>
+        </is>
+      </c>
       <c r="X315" t="n">
         <v>0</v>
       </c>
@@ -48878,7 +49154,11 @@
         <v>87233</v>
       </c>
       <c r="M318" t="inlineStr"/>
-      <c r="N318" t="inlineStr"/>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>1781989151558</t>
+        </is>
+      </c>
       <c r="O318" t="n">
         <v>0</v>
       </c>
@@ -48899,7 +49179,11 @@
         <v>0</v>
       </c>
       <c r="V318" t="inlineStr"/>
-      <c r="W318" t="inlineStr"/>
+      <c r="W318" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6111/86144/46e5f08a-9565-42f6-ba1c-1b012e8df44e.jpg</t>
+        </is>
+      </c>
       <c r="X318" t="n">
         <v>0</v>
       </c>
@@ -49184,7 +49468,11 @@
         <v>87235</v>
       </c>
       <c r="M320" t="inlineStr"/>
-      <c r="N320" t="inlineStr"/>
+      <c r="N320" t="inlineStr">
+        <is>
+          <t>1781989169382</t>
+        </is>
+      </c>
       <c r="O320" t="n">
         <v>0</v>
       </c>
@@ -49205,7 +49493,11 @@
         <v>0</v>
       </c>
       <c r="V320" t="inlineStr"/>
-      <c r="W320" t="inlineStr"/>
+      <c r="W320" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6111/86146/2d20aefe-20f6-4636-9961-195da8f07f40.jpg</t>
+        </is>
+      </c>
       <c r="X320" t="n">
         <v>0</v>
       </c>
@@ -49631,7 +49923,11 @@
         <v>162647</v>
       </c>
       <c r="M323" t="inlineStr"/>
-      <c r="N323" t="inlineStr"/>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>1781989129084</t>
+        </is>
+      </c>
       <c r="O323" t="n">
         <v>0</v>
       </c>
@@ -49652,7 +49948,11 @@
         <v>0</v>
       </c>
       <c r="V323" t="inlineStr"/>
-      <c r="W323" t="inlineStr"/>
+      <c r="W323" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6111/657921/e9cd826a-0b4c-402b-80af-98e8f2d3a00c.jpg</t>
+        </is>
+      </c>
       <c r="X323" t="n">
         <v>0</v>
       </c>
@@ -49780,7 +50080,11 @@
         <v>162648</v>
       </c>
       <c r="M324" t="inlineStr"/>
-      <c r="N324" t="inlineStr"/>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>1781989085413</t>
+        </is>
+      </c>
       <c r="O324" t="n">
         <v>0</v>
       </c>
@@ -49801,7 +50105,11 @@
         <v>0</v>
       </c>
       <c r="V324" t="inlineStr"/>
-      <c r="W324" t="inlineStr"/>
+      <c r="W324" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6111/657922/25143312-c5bf-4898-a670-035f8391a078.jpg</t>
+        </is>
+      </c>
       <c r="X324" t="n">
         <v>0</v>
       </c>
@@ -49929,7 +50237,11 @@
         <v>162649</v>
       </c>
       <c r="M325" t="inlineStr"/>
-      <c r="N325" t="inlineStr"/>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>1781991510109</t>
+        </is>
+      </c>
       <c r="O325" t="n">
         <v>0</v>
       </c>
@@ -49950,7 +50262,11 @@
         <v>0</v>
       </c>
       <c r="V325" t="inlineStr"/>
-      <c r="W325" t="inlineStr"/>
+      <c r="W325" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6111/657923/9304f6e4-d504-4928-9787-521b4d32a2fd.jpg</t>
+        </is>
+      </c>
       <c r="X325" t="n">
         <v>0</v>
       </c>
@@ -51717,7 +52033,11 @@
         <v>162643</v>
       </c>
       <c r="M337" t="inlineStr"/>
-      <c r="N337" t="inlineStr"/>
+      <c r="N337" t="inlineStr">
+        <is>
+          <t>1781989923190</t>
+        </is>
+      </c>
       <c r="O337" t="n">
         <v>0</v>
       </c>
@@ -51738,7 +52058,11 @@
         <v>0</v>
       </c>
       <c r="V337" t="inlineStr"/>
-      <c r="W337" t="inlineStr"/>
+      <c r="W337" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6110/657926/b342f69e-93f4-462a-8982-766d6eb03c03.jpg</t>
+        </is>
+      </c>
       <c r="X337" t="n">
         <v>0</v>
       </c>
@@ -62829,7 +63153,11 @@
         <v>87189</v>
       </c>
       <c r="M411" t="inlineStr"/>
-      <c r="N411" t="inlineStr"/>
+      <c r="N411" t="inlineStr">
+        <is>
+          <t>1781989194231</t>
+        </is>
+      </c>
       <c r="O411" t="n">
         <v>0</v>
       </c>
@@ -62850,7 +63178,11 @@
         <v>0</v>
       </c>
       <c r="V411" t="inlineStr"/>
-      <c r="W411" t="inlineStr"/>
+      <c r="W411" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6106/86100/917a0806-ba9e-4be6-8538-54269588ccba.jpg</t>
+        </is>
+      </c>
       <c r="X411" t="n">
         <v>0</v>
       </c>
@@ -67411,7 +67743,11 @@
         <v>87263</v>
       </c>
       <c r="M441" t="inlineStr"/>
-      <c r="N441" t="inlineStr"/>
+      <c r="N441" t="inlineStr">
+        <is>
+          <t>1781989182577</t>
+        </is>
+      </c>
       <c r="O441" t="n">
         <v>0</v>
       </c>
@@ -67432,7 +67768,11 @@
         <v>0</v>
       </c>
       <c r="V441" t="inlineStr"/>
-      <c r="W441" t="inlineStr"/>
+      <c r="W441" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6115/86174/7fbb1bd0-4de9-4d68-a6b5-4e5d4d597322.jpg</t>
+        </is>
+      </c>
       <c r="X441" t="n">
         <v>0</v>
       </c>
@@ -67560,7 +67900,11 @@
         <v>87264</v>
       </c>
       <c r="M442" t="inlineStr"/>
-      <c r="N442" t="inlineStr"/>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>1781989143770</t>
+        </is>
+      </c>
       <c r="O442" t="n">
         <v>0</v>
       </c>
@@ -67581,7 +67925,11 @@
         <v>0</v>
       </c>
       <c r="V442" t="inlineStr"/>
-      <c r="W442" t="inlineStr"/>
+      <c r="W442" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6115/86175/432e89d9-7f09-42e3-9339-21370b2f9225.jpg</t>
+        </is>
+      </c>
       <c r="X442" t="n">
         <v>0</v>
       </c>
@@ -68180,7 +68528,11 @@
         <v>87268</v>
       </c>
       <c r="M446" t="inlineStr"/>
-      <c r="N446" t="inlineStr"/>
+      <c r="N446" t="inlineStr">
+        <is>
+          <t>1781989164028</t>
+        </is>
+      </c>
       <c r="O446" t="n">
         <v>0</v>
       </c>
@@ -68201,7 +68553,11 @@
         <v>0</v>
       </c>
       <c r="V446" t="inlineStr"/>
-      <c r="W446" t="inlineStr"/>
+      <c r="W446" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6115/86179/ad6d2799-f00f-4432-9c21-714179b72816.jpg</t>
+        </is>
+      </c>
       <c r="X446" t="n">
         <v>0</v>
       </c>
@@ -68957,7 +69313,11 @@
         <v>162673</v>
       </c>
       <c r="M451" t="inlineStr"/>
-      <c r="N451" t="inlineStr"/>
+      <c r="N451" t="inlineStr">
+        <is>
+          <t>1781989210145</t>
+        </is>
+      </c>
       <c r="O451" t="n">
         <v>0</v>
       </c>
@@ -68978,7 +69338,11 @@
         <v>0</v>
       </c>
       <c r="V451" t="inlineStr"/>
-      <c r="W451" t="inlineStr"/>
+      <c r="W451" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6115/657987/0e30b823-c797-497a-b015-b3a141e527ab.jpg</t>
+        </is>
+      </c>
       <c r="X451" t="n">
         <v>0</v>
       </c>
@@ -69883,7 +70247,11 @@
         <v>162679</v>
       </c>
       <c r="M457" t="inlineStr"/>
-      <c r="N457" t="inlineStr"/>
+      <c r="N457" t="inlineStr">
+        <is>
+          <t>1781989205540</t>
+        </is>
+      </c>
       <c r="O457" t="n">
         <v>0</v>
       </c>
@@ -69904,7 +70272,11 @@
         <v>0</v>
       </c>
       <c r="V457" t="inlineStr"/>
-      <c r="W457" t="inlineStr"/>
+      <c r="W457" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6115/657993/97e9413b-a5a3-44d1-bd28-12aca29b88c7.jpg</t>
+        </is>
+      </c>
       <c r="X457" t="n">
         <v>0</v>
       </c>
@@ -70338,7 +70710,11 @@
         <v>162682</v>
       </c>
       <c r="M460" t="inlineStr"/>
-      <c r="N460" t="inlineStr"/>
+      <c r="N460" t="inlineStr">
+        <is>
+          <t>1781989176554</t>
+        </is>
+      </c>
       <c r="O460" t="n">
         <v>0</v>
       </c>
@@ -70359,7 +70735,11 @@
         <v>0</v>
       </c>
       <c r="V460" t="inlineStr"/>
-      <c r="W460" t="inlineStr"/>
+      <c r="W460" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6115/657996/37fff2f6-e837-4bfd-a300-d489f5fdcc68.jpg</t>
+        </is>
+      </c>
       <c r="X460" t="n">
         <v>0</v>
       </c>
@@ -70801,7 +71181,11 @@
         <v>87551</v>
       </c>
       <c r="M463" t="inlineStr"/>
-      <c r="N463" t="inlineStr"/>
+      <c r="N463" t="inlineStr">
+        <is>
+          <t>1781990105339</t>
+        </is>
+      </c>
       <c r="O463" t="n">
         <v>0</v>
       </c>
@@ -70822,7 +71206,11 @@
         <v>0</v>
       </c>
       <c r="V463" t="inlineStr"/>
-      <c r="W463" t="inlineStr"/>
+      <c r="W463" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6141/86462/761d8a00-83a7-46c0-8e11-010af0949be5.jpg</t>
+        </is>
+      </c>
       <c r="X463" t="n">
         <v>0</v>
       </c>
@@ -70950,7 +71338,11 @@
         <v>87552</v>
       </c>
       <c r="M464" t="inlineStr"/>
-      <c r="N464" t="inlineStr"/>
+      <c r="N464" t="inlineStr">
+        <is>
+          <t>1781989327681</t>
+        </is>
+      </c>
       <c r="O464" t="n">
         <v>0</v>
       </c>
@@ -70971,7 +71363,11 @@
         <v>0</v>
       </c>
       <c r="V464" t="inlineStr"/>
-      <c r="W464" t="inlineStr"/>
+      <c r="W464" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6141/86463/68885d5e-f253-4b70-8412-ae3c206f0bc5.jpg</t>
+        </is>
+      </c>
       <c r="X464" t="n">
         <v>0</v>
       </c>
@@ -71099,7 +71495,11 @@
         <v>87553</v>
       </c>
       <c r="M465" t="inlineStr"/>
-      <c r="N465" t="inlineStr"/>
+      <c r="N465" t="inlineStr">
+        <is>
+          <t>1781990284814</t>
+        </is>
+      </c>
       <c r="O465" t="n">
         <v>0</v>
       </c>
@@ -71120,7 +71520,11 @@
         <v>0</v>
       </c>
       <c r="V465" t="inlineStr"/>
-      <c r="W465" t="inlineStr"/>
+      <c r="W465" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6141/86464/a2d9e7a6-bf5b-4707-96ec-24e1f1f48432.jpg</t>
+        </is>
+      </c>
       <c r="X465" t="n">
         <v>0</v>
       </c>
@@ -71554,7 +71958,11 @@
         <v>162905</v>
       </c>
       <c r="M468" t="inlineStr"/>
-      <c r="N468" t="inlineStr"/>
+      <c r="N468" t="inlineStr">
+        <is>
+          <t>1781989197173</t>
+        </is>
+      </c>
       <c r="O468" t="n">
         <v>0</v>
       </c>
@@ -71575,7 +71983,11 @@
         <v>0</v>
       </c>
       <c r="V468" t="inlineStr"/>
-      <c r="W468" t="inlineStr"/>
+      <c r="W468" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6141/658199/71eb123d-b7d3-4dca-8f41-f02e0434bc78.jpg</t>
+        </is>
+      </c>
       <c r="X468" t="n">
         <v>0</v>
       </c>
@@ -71703,7 +72115,11 @@
         <v>162906</v>
       </c>
       <c r="M469" t="inlineStr"/>
-      <c r="N469" t="inlineStr"/>
+      <c r="N469" t="inlineStr">
+        <is>
+          <t>1781988578702</t>
+        </is>
+      </c>
       <c r="O469" t="n">
         <v>0</v>
       </c>
@@ -71724,7 +72140,11 @@
         <v>0</v>
       </c>
       <c r="V469" t="inlineStr"/>
-      <c r="W469" t="inlineStr"/>
+      <c r="W469" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6141/658200/0e8b0305-9f8a-445d-9b75-cb50d8fe1dfd.jpg</t>
+        </is>
+      </c>
       <c r="X469" t="n">
         <v>0</v>
       </c>
@@ -71852,7 +72272,11 @@
         <v>162907</v>
       </c>
       <c r="M470" t="inlineStr"/>
-      <c r="N470" t="inlineStr"/>
+      <c r="N470" t="inlineStr">
+        <is>
+          <t>1781988951192</t>
+        </is>
+      </c>
       <c r="O470" t="n">
         <v>0</v>
       </c>
@@ -71873,7 +72297,11 @@
         <v>0</v>
       </c>
       <c r="V470" t="inlineStr"/>
-      <c r="W470" t="inlineStr"/>
+      <c r="W470" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6141/658201/8b48c2a6-9367-449b-b4ae-efab4e9e1407.jpg</t>
+        </is>
+      </c>
       <c r="X470" t="n">
         <v>0</v>
       </c>
@@ -72464,7 +72892,11 @@
         <v>87566</v>
       </c>
       <c r="M474" t="inlineStr"/>
-      <c r="N474" t="inlineStr"/>
+      <c r="N474" t="inlineStr">
+        <is>
+          <t>1781989141901</t>
+        </is>
+      </c>
       <c r="O474" t="n">
         <v>0</v>
       </c>
@@ -72485,7 +72917,11 @@
         <v>0</v>
       </c>
       <c r="V474" t="inlineStr"/>
-      <c r="W474" t="inlineStr"/>
+      <c r="W474" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6143/86477/40e1c5f2-1a7c-4693-8e85-434659f4216c.jpg</t>
+        </is>
+      </c>
       <c r="X474" t="n">
         <v>0</v>
       </c>
@@ -73382,7 +73818,11 @@
         <v>162916</v>
       </c>
       <c r="M480" t="inlineStr"/>
-      <c r="N480" t="inlineStr"/>
+      <c r="N480" t="inlineStr">
+        <is>
+          <t>1781989208915</t>
+        </is>
+      </c>
       <c r="O480" t="n">
         <v>0</v>
       </c>
@@ -73403,7 +73843,11 @@
         <v>0</v>
       </c>
       <c r="V480" t="inlineStr"/>
-      <c r="W480" t="inlineStr"/>
+      <c r="W480" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6143/658206/c50017a3-48a0-404a-9ea6-7d119d3f0052.jpg</t>
+        </is>
+      </c>
       <c r="X480" t="n">
         <v>0</v>
       </c>
@@ -75655,7 +76099,11 @@
         <v>87576</v>
       </c>
       <c r="M495" t="inlineStr"/>
-      <c r="N495" t="inlineStr"/>
+      <c r="N495" t="inlineStr">
+        <is>
+          <t>1781989169282</t>
+        </is>
+      </c>
       <c r="O495" t="n">
         <v>0</v>
       </c>
@@ -75676,7 +76124,11 @@
         <v>0</v>
       </c>
       <c r="V495" t="inlineStr"/>
-      <c r="W495" t="inlineStr"/>
+      <c r="W495" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6145/86487/bb516fc9-1fe0-4280-9cdc-b288898b7f87.jpg</t>
+        </is>
+      </c>
       <c r="X495" t="n">
         <v>0</v>
       </c>
@@ -75953,7 +76405,11 @@
         <v>162927</v>
       </c>
       <c r="M497" t="inlineStr"/>
-      <c r="N497" t="inlineStr"/>
+      <c r="N497" t="inlineStr">
+        <is>
+          <t>1781989140947</t>
+        </is>
+      </c>
       <c r="O497" t="n">
         <v>0</v>
       </c>
@@ -75974,7 +76430,11 @@
         <v>0</v>
       </c>
       <c r="V497" t="inlineStr"/>
-      <c r="W497" t="inlineStr"/>
+      <c r="W497" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6145/658215/1f406afd-c763-4c0a-8622-7938a2f18983.jpg</t>
+        </is>
+      </c>
       <c r="X497" t="n">
         <v>0</v>
       </c>
@@ -78337,7 +78797,11 @@
         <v>87556</v>
       </c>
       <c r="M513" t="inlineStr"/>
-      <c r="N513" t="inlineStr"/>
+      <c r="N513" t="inlineStr">
+        <is>
+          <t>1781989196580</t>
+        </is>
+      </c>
       <c r="O513" t="n">
         <v>0</v>
       </c>
@@ -78358,7 +78822,11 @@
         <v>0</v>
       </c>
       <c r="V513" t="inlineStr"/>
-      <c r="W513" t="inlineStr"/>
+      <c r="W513" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6142/86467/ddf34096-6e2b-443d-b492-bad946226251.jpg</t>
+        </is>
+      </c>
       <c r="X513" t="n">
         <v>0</v>
       </c>
@@ -78486,7 +78954,11 @@
         <v>87557</v>
       </c>
       <c r="M514" t="inlineStr"/>
-      <c r="N514" t="inlineStr"/>
+      <c r="N514" t="inlineStr">
+        <is>
+          <t>1781989189925</t>
+        </is>
+      </c>
       <c r="O514" t="n">
         <v>0</v>
       </c>
@@ -78507,7 +78979,11 @@
         <v>0</v>
       </c>
       <c r="V514" t="inlineStr"/>
-      <c r="W514" t="inlineStr"/>
+      <c r="W514" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6142/86468/980e0fdf-55f5-4f9d-b881-10e6631b721f.jpg</t>
+        </is>
+      </c>
       <c r="X514" t="n">
         <v>0</v>
       </c>
@@ -78635,7 +79111,11 @@
         <v>87558</v>
       </c>
       <c r="M515" t="inlineStr"/>
-      <c r="N515" t="inlineStr"/>
+      <c r="N515" t="inlineStr">
+        <is>
+          <t>1781989208313</t>
+        </is>
+      </c>
       <c r="O515" t="n">
         <v>0</v>
       </c>
@@ -78656,7 +79136,11 @@
         <v>0</v>
       </c>
       <c r="V515" t="inlineStr"/>
-      <c r="W515" t="inlineStr"/>
+      <c r="W515" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6142/86469/a4c24448-3922-4d54-9e01-54d0fb13b027.jpg</t>
+        </is>
+      </c>
       <c r="X515" t="n">
         <v>0</v>
       </c>
@@ -78784,7 +79268,11 @@
         <v>87559</v>
       </c>
       <c r="M516" t="inlineStr"/>
-      <c r="N516" t="inlineStr"/>
+      <c r="N516" t="inlineStr">
+        <is>
+          <t>1781989128927</t>
+        </is>
+      </c>
       <c r="O516" t="n">
         <v>0</v>
       </c>
@@ -78805,7 +79293,11 @@
         <v>0</v>
       </c>
       <c r="V516" t="inlineStr"/>
-      <c r="W516" t="inlineStr"/>
+      <c r="W516" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6142/86470/e9bd2ae9-7dbb-4b33-bf5b-fb95903a5e31.jpg</t>
+        </is>
+      </c>
       <c r="X516" t="n">
         <v>0</v>
       </c>
@@ -79231,7 +79723,11 @@
         <v>87562</v>
       </c>
       <c r="M519" t="inlineStr"/>
-      <c r="N519" t="inlineStr"/>
+      <c r="N519" t="inlineStr">
+        <is>
+          <t>1781989203110</t>
+        </is>
+      </c>
       <c r="O519" t="n">
         <v>0</v>
       </c>
@@ -79252,7 +79748,11 @@
         <v>0</v>
       </c>
       <c r="V519" t="inlineStr"/>
-      <c r="W519" t="inlineStr"/>
+      <c r="W519" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6142/86473/2ef81ce0-37b3-408d-964e-7960212ceff3.jpg</t>
+        </is>
+      </c>
       <c r="X519" t="n">
         <v>0</v>
       </c>
@@ -79380,7 +79880,11 @@
         <v>162908</v>
       </c>
       <c r="M520" t="inlineStr"/>
-      <c r="N520" t="inlineStr"/>
+      <c r="N520" t="inlineStr">
+        <is>
+          <t>1781990463216</t>
+        </is>
+      </c>
       <c r="O520" t="n">
         <v>0</v>
       </c>
@@ -79401,7 +79905,11 @@
         <v>0</v>
       </c>
       <c r="V520" t="inlineStr"/>
-      <c r="W520" t="inlineStr"/>
+      <c r="W520" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6142/658225/8aeef5dd-42d5-41a1-87c7-a049cdac3797.jpg</t>
+        </is>
+      </c>
       <c r="X520" t="n">
         <v>0</v>
       </c>
@@ -79529,7 +80037,11 @@
         <v>162909</v>
       </c>
       <c r="M521" t="inlineStr"/>
-      <c r="N521" t="inlineStr"/>
+      <c r="N521" t="inlineStr">
+        <is>
+          <t>1781989191630</t>
+        </is>
+      </c>
       <c r="O521" t="n">
         <v>0</v>
       </c>
@@ -79550,7 +80062,11 @@
         <v>0</v>
       </c>
       <c r="V521" t="inlineStr"/>
-      <c r="W521" t="inlineStr"/>
+      <c r="W521" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6142/658226/5a6219bf-448a-41d3-8e25-d92d8cda4f63.jpg</t>
+        </is>
+      </c>
       <c r="X521" t="n">
         <v>0</v>
       </c>
@@ -79678,7 +80194,11 @@
         <v>162910</v>
       </c>
       <c r="M522" t="inlineStr"/>
-      <c r="N522" t="inlineStr"/>
+      <c r="N522" t="inlineStr">
+        <is>
+          <t>1781988908826</t>
+        </is>
+      </c>
       <c r="O522" t="n">
         <v>0</v>
       </c>
@@ -79699,7 +80219,11 @@
         <v>0</v>
       </c>
       <c r="V522" t="inlineStr"/>
-      <c r="W522" t="inlineStr"/>
+      <c r="W522" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6142/658227/f6bc36aa-1a22-4be5-9770-f98f3e100833.jpg</t>
+        </is>
+      </c>
       <c r="X522" t="n">
         <v>0</v>
       </c>
@@ -79827,7 +80351,11 @@
         <v>162911</v>
       </c>
       <c r="M523" t="inlineStr"/>
-      <c r="N523" t="inlineStr"/>
+      <c r="N523" t="inlineStr">
+        <is>
+          <t>1781989185674</t>
+        </is>
+      </c>
       <c r="O523" t="n">
         <v>0</v>
       </c>
@@ -79848,7 +80376,11 @@
         <v>0</v>
       </c>
       <c r="V523" t="inlineStr"/>
-      <c r="W523" t="inlineStr"/>
+      <c r="W523" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6142/658228/86c50d8f-5489-4292-9ddc-7b2e374d79fc.jpg</t>
+        </is>
+      </c>
       <c r="X523" t="n">
         <v>0</v>
       </c>
@@ -82009,7 +82541,11 @@
         <v>87592</v>
       </c>
       <c r="M537" t="inlineStr"/>
-      <c r="N537" t="inlineStr"/>
+      <c r="N537" t="inlineStr">
+        <is>
+          <t>1781989144040</t>
+        </is>
+      </c>
       <c r="O537" t="n">
         <v>0</v>
       </c>
@@ -82030,7 +82566,11 @@
         <v>0</v>
       </c>
       <c r="V537" t="inlineStr"/>
-      <c r="W537" t="inlineStr"/>
+      <c r="W537" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6148/86503/7ebd5872-8a69-426f-bd79-152a25022696.jpg</t>
+        </is>
+      </c>
       <c r="X537" t="n">
         <v>0</v>
       </c>
@@ -82315,7 +82855,11 @@
         <v>87594</v>
       </c>
       <c r="M539" t="inlineStr"/>
-      <c r="N539" t="inlineStr"/>
+      <c r="N539" t="inlineStr">
+        <is>
+          <t>1781989173559</t>
+        </is>
+      </c>
       <c r="O539" t="n">
         <v>0</v>
       </c>
@@ -82336,7 +82880,11 @@
         <v>0</v>
       </c>
       <c r="V539" t="inlineStr"/>
-      <c r="W539" t="inlineStr"/>
+      <c r="W539" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6148/86505/704aeba5-8167-4e0a-96a7-80ea9f08b7a6.jpg</t>
+        </is>
+      </c>
       <c r="X539" t="n">
         <v>0</v>
       </c>
@@ -82621,7 +83169,11 @@
         <v>87596</v>
       </c>
       <c r="M541" t="inlineStr"/>
-      <c r="N541" t="inlineStr"/>
+      <c r="N541" t="inlineStr">
+        <is>
+          <t>1781989154370</t>
+        </is>
+      </c>
       <c r="O541" t="n">
         <v>0</v>
       </c>
@@ -82642,7 +83194,11 @@
         <v>0</v>
       </c>
       <c r="V541" t="inlineStr"/>
-      <c r="W541" t="inlineStr"/>
+      <c r="W541" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6148/86507/cf10c0c4-d709-4575-a33b-752974d8762f.jpg</t>
+        </is>
+      </c>
       <c r="X541" t="n">
         <v>0</v>
       </c>
@@ -83084,7 +83640,11 @@
         <v>87599</v>
       </c>
       <c r="M544" t="inlineStr"/>
-      <c r="N544" t="inlineStr"/>
+      <c r="N544" t="inlineStr">
+        <is>
+          <t>1781988991535</t>
+        </is>
+      </c>
       <c r="O544" t="n">
         <v>0</v>
       </c>
@@ -83105,7 +83665,11 @@
         <v>0</v>
       </c>
       <c r="V544" t="inlineStr"/>
-      <c r="W544" t="inlineStr"/>
+      <c r="W544" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6148/86510/5182d592-31c4-46bb-8377-0d97804cc66a.jpg</t>
+        </is>
+      </c>
       <c r="X544" t="n">
         <v>0</v>
       </c>
@@ -84638,7 +85202,11 @@
         <v>87584</v>
       </c>
       <c r="M554" t="inlineStr"/>
-      <c r="N554" t="inlineStr"/>
+      <c r="N554" t="inlineStr">
+        <is>
+          <t>1781989924145</t>
+        </is>
+      </c>
       <c r="O554" t="n">
         <v>0</v>
       </c>
@@ -84659,7 +85227,11 @@
         <v>0</v>
       </c>
       <c r="V554" t="inlineStr"/>
-      <c r="W554" t="inlineStr"/>
+      <c r="W554" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6147/86495/342ea23b-cf94-412e-866b-d52b16caaa3c.jpg</t>
+        </is>
+      </c>
       <c r="X554" t="n">
         <v>0</v>
       </c>
@@ -85407,7 +85979,11 @@
         <v>87589</v>
       </c>
       <c r="M559" t="inlineStr"/>
-      <c r="N559" t="inlineStr"/>
+      <c r="N559" t="inlineStr">
+        <is>
+          <t>1781989192185</t>
+        </is>
+      </c>
       <c r="O559" t="n">
         <v>0</v>
       </c>
@@ -85428,7 +86004,11 @@
         <v>0</v>
       </c>
       <c r="V559" t="inlineStr"/>
-      <c r="W559" t="inlineStr"/>
+      <c r="W559" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6147/86500/3846fc5f-bf7d-4509-ac18-c0832f189512.jpg</t>
+        </is>
+      </c>
       <c r="X559" t="n">
         <v>0</v>
       </c>
@@ -87901,7 +88481,11 @@
         <v>87580</v>
       </c>
       <c r="M575" t="inlineStr"/>
-      <c r="N575" t="inlineStr"/>
+      <c r="N575" t="inlineStr">
+        <is>
+          <t>1781989564675</t>
+        </is>
+      </c>
       <c r="O575" t="n">
         <v>0</v>
       </c>
@@ -87922,7 +88506,11 @@
         <v>0</v>
       </c>
       <c r="V575" t="inlineStr"/>
-      <c r="W575" t="inlineStr"/>
+      <c r="W575" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6146/86491/80ab9fa5-de75-4da2-b7d7-e794a36f5b9b.jpg</t>
+        </is>
+      </c>
       <c r="X575" t="n">
         <v>0</v>
       </c>
@@ -88795,7 +89383,11 @@
         <v>162932</v>
       </c>
       <c r="M581" t="inlineStr"/>
-      <c r="N581" t="inlineStr"/>
+      <c r="N581" t="inlineStr">
+        <is>
+          <t>1781989924164</t>
+        </is>
+      </c>
       <c r="O581" t="n">
         <v>0</v>
       </c>
@@ -88816,7 +89408,11 @@
         <v>0</v>
       </c>
       <c r="V581" t="inlineStr"/>
-      <c r="W581" t="inlineStr"/>
+      <c r="W581" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6146/658258/0df570e7-7f84-48af-9dc9-cf05b1a63e81.jpg</t>
+        </is>
+      </c>
       <c r="X581" t="n">
         <v>0</v>
       </c>
@@ -89093,7 +89689,11 @@
         <v>162934</v>
       </c>
       <c r="M583" t="inlineStr"/>
-      <c r="N583" t="inlineStr"/>
+      <c r="N583" t="inlineStr">
+        <is>
+          <t>1781990285637</t>
+        </is>
+      </c>
       <c r="O583" t="n">
         <v>0</v>
       </c>
@@ -89114,7 +89714,11 @@
         <v>0</v>
       </c>
       <c r="V583" t="inlineStr"/>
-      <c r="W583" t="inlineStr"/>
+      <c r="W583" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6146/658260/40419aad-1392-4e4c-8707-699411730b70.jpg</t>
+        </is>
+      </c>
       <c r="X583" t="n">
         <v>0</v>
       </c>
@@ -89346,172 +89950,172 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>LGA</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Ward</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Polling Units</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>INEC Uploaded Results</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>INEC Upload Percent</t>
         </is>
@@ -89731,10 +90335,10 @@
         <v>40</v>
       </c>
       <c r="AG3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AH3" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4">
@@ -89951,10 +90555,10 @@
         <v>10</v>
       </c>
       <c r="AG5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH5" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6">
@@ -90061,10 +90665,10 @@
         <v>17</v>
       </c>
       <c r="AG6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH6" t="n">
-        <v>41.2</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="7">
@@ -90171,10 +90775,10 @@
         <v>14</v>
       </c>
       <c r="AG7" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AH7" t="n">
-        <v>42.9</v>
+        <v>92.90000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -90281,10 +90885,10 @@
         <v>14</v>
       </c>
       <c r="AG8" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AH8" t="n">
-        <v>78.59999999999999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">
@@ -90392,10 +90996,10 @@
         <v>12</v>
       </c>
       <c r="AG9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AH9" t="n">
-        <v>33.3</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="10">
@@ -90502,10 +91106,10 @@
         <v>17</v>
       </c>
       <c r="AG10" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AH10" t="n">
-        <v>17.6</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="11">
@@ -90722,10 +91326,10 @@
         <v>12</v>
       </c>
       <c r="AG12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AH12" t="n">
-        <v>58.3</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13">
@@ -91052,10 +91656,10 @@
         <v>22</v>
       </c>
       <c r="AG15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH15" t="n">
-        <v>9.1</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="16">
@@ -91162,10 +91766,10 @@
         <v>16</v>
       </c>
       <c r="AG16" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AH16" t="n">
-        <v>50</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="17">
@@ -91272,10 +91876,10 @@
         <v>19</v>
       </c>
       <c r="AG17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH17" t="n">
-        <v>10.5</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="18">
@@ -91492,10 +92096,10 @@
         <v>15</v>
       </c>
       <c r="AG19" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AH19" t="n">
-        <v>46.7</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20">
@@ -91602,10 +92206,10 @@
         <v>8</v>
       </c>
       <c r="AG20" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AH20" t="n">
-        <v>12.5</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21">
@@ -91712,10 +92316,10 @@
         <v>15</v>
       </c>
       <c r="AG21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH21" t="n">
-        <v>6.7</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="22">
@@ -92042,10 +92646,10 @@
         <v>14</v>
       </c>
       <c r="AG24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH24" t="n">
-        <v>92.90000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25">
@@ -92262,10 +92866,10 @@
         <v>22</v>
       </c>
       <c r="AG26" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AH26" t="n">
-        <v>63.6</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -92372,10 +92976,10 @@
         <v>8</v>
       </c>
       <c r="AG27" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AH27" t="n">
-        <v>12.5</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="28">
@@ -92482,10 +93086,10 @@
         <v>12</v>
       </c>
       <c r="AG28" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AH28" t="n">
-        <v>58.3</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29">
@@ -92702,10 +93306,10 @@
         <v>7</v>
       </c>
       <c r="AG30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AH30" t="n">
-        <v>28.6</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="31">
@@ -92922,10 +93526,10 @@
         <v>11</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="33">
@@ -93142,10 +93746,10 @@
         <v>17</v>
       </c>
       <c r="AG34" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AH34" t="n">
-        <v>70.59999999999999</v>
+        <v>94.09999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -93252,10 +93856,10 @@
         <v>19</v>
       </c>
       <c r="AG35" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AH35" t="n">
-        <v>84.2</v>
+        <v>94.7</v>
       </c>
     </row>
     <row r="36">
@@ -93362,10 +93966,10 @@
         <v>13</v>
       </c>
       <c r="AG36" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AH36" t="n">
-        <v>7.7</v>
+        <v>30.8</v>
       </c>
     </row>
   </sheetData>
@@ -93383,167 +93987,167 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>LGA</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Polling Units</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>INEC Uploaded Results</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>INEC Upload Percent</t>
         </is>
@@ -93648,10 +94252,10 @@
         <v>206</v>
       </c>
       <c r="AF2" t="n">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="AG2" t="n">
-        <v>51</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="3">
@@ -93753,10 +94357,10 @@
         <v>255</v>
       </c>
       <c r="AF3" t="n">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="AG3" t="n">
-        <v>26.3</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="4">
@@ -93858,10 +94462,10 @@
         <v>122</v>
       </c>
       <c r="AF4" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="AG4" t="n">
-        <v>41</v>
+        <v>63.9</v>
       </c>
     </row>
   </sheetData>
@@ -93879,167 +94483,167 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Polling Units</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>INEC Uploaded Results</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>INEC Expected Results</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>INEC Upload Percent</t>
         </is>
@@ -94139,13 +94743,13 @@
         <v>583</v>
       </c>
       <c r="AE2" t="n">
-        <v>222</v>
+        <v>300</v>
       </c>
       <c r="AF2" t="n">
         <v>583</v>
       </c>
       <c r="AG2" t="n">
-        <v>38.1</v>
+        <v>51.5</v>
       </c>
     </row>
   </sheetData>

--- a/output/Nasarawa/results.xlsx
+++ b/output/Nasarawa/results.xlsx
@@ -20,13 +20,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,227 +432,227 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>LGA</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Election ID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Election Name</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Election Date</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Ward</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Ward Code</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Ward ID</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Polling Unit</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>PU Code</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>PU ID</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Polling Unit ID</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Result Updated Time</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Session</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Result Info PU</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Image File</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Image URL</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
@@ -43364,7 +43376,11 @@
         <v>162622</v>
       </c>
       <c r="M280" t="inlineStr"/>
-      <c r="N280" t="inlineStr"/>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>1781993108603</t>
+        </is>
+      </c>
       <c r="O280" t="n">
         <v>0</v>
       </c>
@@ -43385,7 +43401,11 @@
         <v>0</v>
       </c>
       <c r="V280" t="inlineStr"/>
-      <c r="W280" t="inlineStr"/>
+      <c r="W280" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6107/657872/1859e954-4709-48f7-90eb-0e13ef7aec90.jpg</t>
+        </is>
+      </c>
       <c r="X280" t="n">
         <v>0</v>
       </c>
@@ -47286,7 +47306,11 @@
         <v>87241</v>
       </c>
       <c r="M306" t="inlineStr"/>
-      <c r="N306" t="inlineStr"/>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>1781992872767</t>
+        </is>
+      </c>
       <c r="O306" t="n">
         <v>0</v>
       </c>
@@ -47307,7 +47331,11 @@
         <v>0</v>
       </c>
       <c r="V306" t="inlineStr"/>
-      <c r="W306" t="inlineStr"/>
+      <c r="W306" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6112/86152/ab60799c-ee87-403d-be86-3d883b1ad4b8.jpg</t>
+        </is>
+      </c>
       <c r="X306" t="n">
         <v>0</v>
       </c>
@@ -47749,7 +47777,11 @@
         <v>87244</v>
       </c>
       <c r="M309" t="inlineStr"/>
-      <c r="N309" t="inlineStr"/>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>1781992778769</t>
+        </is>
+      </c>
       <c r="O309" t="n">
         <v>0</v>
       </c>
@@ -47770,7 +47802,11 @@
         <v>0</v>
       </c>
       <c r="V309" t="inlineStr"/>
-      <c r="W309" t="inlineStr"/>
+      <c r="W309" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6112/86155/a0f19808-5e31-4982-807e-5e5198a3705f.jpg</t>
+        </is>
+      </c>
       <c r="X309" t="n">
         <v>0</v>
       </c>
@@ -76711,7 +76747,11 @@
         <v>87600</v>
       </c>
       <c r="M499" t="inlineStr"/>
-      <c r="N499" t="inlineStr"/>
+      <c r="N499" t="inlineStr">
+        <is>
+          <t>1781993303126</t>
+        </is>
+      </c>
       <c r="O499" t="n">
         <v>0</v>
       </c>
@@ -76732,7 +76772,11 @@
         <v>0</v>
       </c>
       <c r="V499" t="inlineStr"/>
-      <c r="W499" t="inlineStr"/>
+      <c r="W499" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6149/86511/412e5ad4-555e-47d5-9e12-679e7aef843a.jpg</t>
+        </is>
+      </c>
       <c r="X499" t="n">
         <v>0</v>
       </c>
@@ -77009,7 +77053,11 @@
         <v>87602</v>
       </c>
       <c r="M501" t="inlineStr"/>
-      <c r="N501" t="inlineStr"/>
+      <c r="N501" t="inlineStr">
+        <is>
+          <t>1781993338838</t>
+        </is>
+      </c>
       <c r="O501" t="n">
         <v>0</v>
       </c>
@@ -77030,7 +77078,11 @@
         <v>0</v>
       </c>
       <c r="V501" t="inlineStr"/>
-      <c r="W501" t="inlineStr"/>
+      <c r="W501" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6149/86513/b9b656d8-e742-4591-9d7b-7dc5a2989bcf.jpg</t>
+        </is>
+      </c>
       <c r="X501" t="n">
         <v>0</v>
       </c>
@@ -77307,7 +77359,11 @@
         <v>87604</v>
       </c>
       <c r="M503" t="inlineStr"/>
-      <c r="N503" t="inlineStr"/>
+      <c r="N503" t="inlineStr">
+        <is>
+          <t>1781993327916</t>
+        </is>
+      </c>
       <c r="O503" t="n">
         <v>0</v>
       </c>
@@ -77328,7 +77384,11 @@
         <v>0</v>
       </c>
       <c r="V503" t="inlineStr"/>
-      <c r="W503" t="inlineStr"/>
+      <c r="W503" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6149/86515/4caccbeb-39d6-4091-9e5c-b4256ff95148.jpg</t>
+        </is>
+      </c>
       <c r="X503" t="n">
         <v>0</v>
       </c>
@@ -77903,7 +77963,11 @@
         <v>162957</v>
       </c>
       <c r="M507" t="inlineStr"/>
-      <c r="N507" t="inlineStr"/>
+      <c r="N507" t="inlineStr">
+        <is>
+          <t>1781993033645</t>
+        </is>
+      </c>
       <c r="O507" t="n">
         <v>0</v>
       </c>
@@ -77924,7 +77988,11 @@
         <v>0</v>
       </c>
       <c r="V507" t="inlineStr"/>
-      <c r="W507" t="inlineStr"/>
+      <c r="W507" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6149/658219/e129b7ac-f422-469b-8421-6f396ed93c4a.jpg</t>
+        </is>
+      </c>
       <c r="X507" t="n">
         <v>0</v>
       </c>
@@ -89950,172 +90018,172 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>LGA</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Ward</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Polling Units</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>INEC Uploaded Results</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>INEC Upload Percent</t>
         </is>
@@ -91876,10 +91944,10 @@
         <v>19</v>
       </c>
       <c r="AG17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH17" t="n">
-        <v>15.8</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="18">
@@ -92096,10 +92164,10 @@
         <v>15</v>
       </c>
       <c r="AG19" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AH19" t="n">
-        <v>80</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="20">
@@ -93416,10 +93484,10 @@
         <v>14</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="32">
@@ -93987,167 +94055,167 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>LGA</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Polling Units</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>INEC Uploaded Results</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>INEC Upload Percent</t>
         </is>
@@ -94357,10 +94425,10 @@
         <v>255</v>
       </c>
       <c r="AF3" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AG3" t="n">
-        <v>35.7</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="4">
@@ -94462,10 +94530,10 @@
         <v>122</v>
       </c>
       <c r="AF4" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AG4" t="n">
-        <v>63.9</v>
+        <v>67.2</v>
       </c>
     </row>
   </sheetData>
@@ -94483,167 +94551,167 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Polling Units</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>INEC Uploaded Results</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>INEC Expected Results</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>INEC Upload Percent</t>
         </is>
@@ -94743,13 +94811,13 @@
         <v>583</v>
       </c>
       <c r="AE2" t="n">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="AF2" t="n">
         <v>583</v>
       </c>
       <c r="AG2" t="n">
-        <v>51.5</v>
+        <v>52.5</v>
       </c>
     </row>
   </sheetData>

--- a/output/Nasarawa/results.xlsx
+++ b/output/Nasarawa/results.xlsx
@@ -20,16 +20,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,227 +420,227 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>LGA</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Election ID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Election Name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Election Date</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Ward</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Ward Code</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Ward ID</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Polling Unit</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>PU Code</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>PU ID</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Polling Unit ID</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Result Updated Time</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Session</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Result Info PU</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Image File</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Image URL</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
@@ -718,7 +706,11 @@
         <v>86098</v>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>1781994405742</t>
+        </is>
+      </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
@@ -739,7 +731,11 @@
         <v>0</v>
       </c>
       <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6005/85034/1ed6d477-83ed-4628-a8db-e8e991504f67.jpg</t>
+        </is>
+      </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
@@ -1463,7 +1459,11 @@
         <v>86103</v>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>1781994629083</t>
+        </is>
+      </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
@@ -1484,7 +1484,11 @@
         <v>0</v>
       </c>
       <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6005/85039/eaf38c98-b31c-4c2e-956e-3c0a0587eb58.jpg</t>
+        </is>
+      </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
@@ -1761,7 +1765,11 @@
         <v>161208</v>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>1781995266205</t>
+        </is>
+      </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
@@ -1782,7 +1790,11 @@
         <v>0</v>
       </c>
       <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6005/656509/a4f28a3a-dfea-4af9-83c2-f3f6b0213717.jpg</t>
+        </is>
+      </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
@@ -2357,7 +2369,11 @@
         <v>161212</v>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>1781995975724</t>
+        </is>
+      </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
@@ -2378,7 +2394,11 @@
         <v>0</v>
       </c>
       <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6005/656513/6de83031-c6a0-48c3-93c8-402726eaae15.jpg</t>
+        </is>
+      </c>
       <c r="X13" t="n">
         <v>0</v>
       </c>
@@ -9938,7 +9958,11 @@
         <v>86142</v>
       </c>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>1782025619591</t>
+        </is>
+      </c>
       <c r="O62" t="n">
         <v>0</v>
       </c>
@@ -9959,7 +9983,11 @@
         <v>0</v>
       </c>
       <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr"/>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6012/85078/3fd3383e-fed1-4417-9fcb-458580f6be75.jpg</t>
+        </is>
+      </c>
       <c r="X62" t="n">
         <v>0</v>
       </c>
@@ -11335,7 +11363,11 @@
         <v>161279</v>
       </c>
       <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>1782026621099</t>
+        </is>
+      </c>
       <c r="O71" t="n">
         <v>0</v>
       </c>
@@ -11356,7 +11388,11 @@
         <v>0</v>
       </c>
       <c r="V71" t="inlineStr"/>
-      <c r="W71" t="inlineStr"/>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6012/656550/25094bf9-b46f-4599-9cca-596c1b9f8319.jpg</t>
+        </is>
+      </c>
       <c r="X71" t="n">
         <v>0</v>
       </c>
@@ -11633,7 +11669,11 @@
         <v>161281</v>
       </c>
       <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>1782026645616</t>
+        </is>
+      </c>
       <c r="O73" t="n">
         <v>0</v>
       </c>
@@ -11654,7 +11694,11 @@
         <v>0</v>
       </c>
       <c r="V73" t="inlineStr"/>
-      <c r="W73" t="inlineStr"/>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6012/656552/b46a488e-75d3-4cf4-9034-b111b7b70dd5.jpg</t>
+        </is>
+      </c>
       <c r="X73" t="n">
         <v>0</v>
       </c>
@@ -12724,7 +12768,11 @@
         <v>161288</v>
       </c>
       <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>1782027790160</t>
+        </is>
+      </c>
       <c r="O80" t="n">
         <v>0</v>
       </c>
@@ -12745,7 +12793,11 @@
         <v>0</v>
       </c>
       <c r="V80" t="inlineStr"/>
-      <c r="W80" t="inlineStr"/>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6012/656559/aa78939b-7232-42bd-965f-435ce27458c6.jpg</t>
+        </is>
+      </c>
       <c r="X80" t="n">
         <v>0</v>
       </c>
@@ -13501,7 +13553,11 @@
         <v>161293</v>
       </c>
       <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>1782025922707</t>
+        </is>
+      </c>
       <c r="O85" t="n">
         <v>0</v>
       </c>
@@ -13522,7 +13578,11 @@
         <v>0</v>
       </c>
       <c r="V85" t="inlineStr"/>
-      <c r="W85" t="inlineStr"/>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6012/656564/50e3b4df-a1d9-48c7-852d-21684b24ebf0.jpg</t>
+        </is>
+      </c>
       <c r="X85" t="n">
         <v>0</v>
       </c>
@@ -13964,7 +14024,11 @@
         <v>161296</v>
       </c>
       <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>1782025839592</t>
+        </is>
+      </c>
       <c r="O88" t="n">
         <v>0</v>
       </c>
@@ -13985,7 +14049,11 @@
         <v>0</v>
       </c>
       <c r="V88" t="inlineStr"/>
-      <c r="W88" t="inlineStr"/>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6012/656567/bef12518-a141-4c25-97d6-f872d79f159c.jpg</t>
+        </is>
+      </c>
       <c r="X88" t="n">
         <v>0</v>
       </c>
@@ -14113,7 +14181,11 @@
         <v>161297</v>
       </c>
       <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>1782026004635</t>
+        </is>
+      </c>
       <c r="O89" t="n">
         <v>0</v>
       </c>
@@ -14134,7 +14206,11 @@
         <v>0</v>
       </c>
       <c r="V89" t="inlineStr"/>
-      <c r="W89" t="inlineStr"/>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6012/656568/859dd068-dd1d-449d-a17d-4f56f461459d.jpg</t>
+        </is>
+      </c>
       <c r="X89" t="n">
         <v>0</v>
       </c>
@@ -14568,7 +14644,11 @@
         <v>161300</v>
       </c>
       <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>1782025734104</t>
+        </is>
+      </c>
       <c r="O92" t="n">
         <v>0</v>
       </c>
@@ -14589,7 +14669,11 @@
         <v>0</v>
       </c>
       <c r="V92" t="inlineStr"/>
-      <c r="W92" t="inlineStr"/>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6012/656571/14494147-7c99-4b9d-b3d1-380fb0cf4138.jpg</t>
+        </is>
+      </c>
       <c r="X92" t="n">
         <v>0</v>
       </c>
@@ -15345,7 +15429,11 @@
         <v>161305</v>
       </c>
       <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>1782026005630</t>
+        </is>
+      </c>
       <c r="O97" t="n">
         <v>0</v>
       </c>
@@ -15366,7 +15454,11 @@
         <v>0</v>
       </c>
       <c r="V97" t="inlineStr"/>
-      <c r="W97" t="inlineStr"/>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6012/656576/9338a978-a04e-4256-8f51-21daed0a5521.jpg</t>
+        </is>
+      </c>
       <c r="X97" t="n">
         <v>0</v>
       </c>
@@ -15494,7 +15586,11 @@
         <v>161306</v>
       </c>
       <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>1782026277582</t>
+        </is>
+      </c>
       <c r="O98" t="n">
         <v>0</v>
       </c>
@@ -15515,7 +15611,11 @@
         <v>0</v>
       </c>
       <c r="V98" t="inlineStr"/>
-      <c r="W98" t="inlineStr"/>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6012/656577/73329dd0-4f3a-499a-aa50-5069b3dd736c.jpg</t>
+        </is>
+      </c>
       <c r="X98" t="n">
         <v>0</v>
       </c>
@@ -17346,7 +17446,11 @@
         <v>86090</v>
       </c>
       <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>1781999293925</t>
+        </is>
+      </c>
       <c r="O110" t="n">
         <v>0</v>
       </c>
@@ -17367,7 +17471,11 @@
         <v>0</v>
       </c>
       <c r="V110" t="inlineStr"/>
-      <c r="W110" t="inlineStr"/>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6004/85026/0e4eb543-6090-411b-80b1-e94832f4010d.jpg</t>
+        </is>
+      </c>
       <c r="X110" t="n">
         <v>0</v>
       </c>
@@ -17966,7 +18074,11 @@
         <v>86094</v>
       </c>
       <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>1781997184420</t>
+        </is>
+      </c>
       <c r="O114" t="n">
         <v>0</v>
       </c>
@@ -17987,7 +18099,11 @@
         <v>0</v>
       </c>
       <c r="V114" t="inlineStr"/>
-      <c r="W114" t="inlineStr"/>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6004/85030/75427c20-4c5d-4a6d-b34f-63e9c166332b.jpg</t>
+        </is>
+      </c>
       <c r="X114" t="n">
         <v>0</v>
       </c>
@@ -18115,7 +18231,11 @@
         <v>86095</v>
       </c>
       <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>1781994033581</t>
+        </is>
+      </c>
       <c r="O115" t="n">
         <v>0</v>
       </c>
@@ -18136,7 +18256,11 @@
         <v>0</v>
       </c>
       <c r="V115" t="inlineStr"/>
-      <c r="W115" t="inlineStr"/>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6004/85031/bc64803a-06a7-4e06-822d-a38e40bf4db3.jpg</t>
+        </is>
+      </c>
       <c r="X115" t="n">
         <v>0</v>
       </c>
@@ -18264,7 +18388,11 @@
         <v>86096</v>
       </c>
       <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>1781998852672</t>
+        </is>
+      </c>
       <c r="O116" t="n">
         <v>0</v>
       </c>
@@ -18285,7 +18413,11 @@
         <v>0</v>
       </c>
       <c r="V116" t="inlineStr"/>
-      <c r="W116" t="inlineStr"/>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6004/85032/2883f64f-e439-46d0-a8e6-6bb6eef4b978.jpg</t>
+        </is>
+      </c>
       <c r="X116" t="n">
         <v>0</v>
       </c>
@@ -18570,7 +18702,11 @@
         <v>161213</v>
       </c>
       <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>1782002497461</t>
+        </is>
+      </c>
       <c r="O118" t="n">
         <v>0</v>
       </c>
@@ -18591,7 +18727,11 @@
         <v>0</v>
       </c>
       <c r="V118" t="inlineStr"/>
-      <c r="W118" t="inlineStr"/>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6004/656579/8d92304b-d2cc-4b9e-a5a6-2c59365fe698.jpg</t>
+        </is>
+      </c>
       <c r="X118" t="n">
         <v>0</v>
       </c>
@@ -18719,7 +18859,11 @@
         <v>161214</v>
       </c>
       <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>1782003472812</t>
+        </is>
+      </c>
       <c r="O119" t="n">
         <v>0</v>
       </c>
@@ -18740,7 +18884,11 @@
         <v>0</v>
       </c>
       <c r="V119" t="inlineStr"/>
-      <c r="W119" t="inlineStr"/>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6004/656580/65956b81-c975-4a98-9607-de15450652cc.jpg</t>
+        </is>
+      </c>
       <c r="X119" t="n">
         <v>0</v>
       </c>
@@ -19025,7 +19173,11 @@
         <v>161216</v>
       </c>
       <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>1781997161057</t>
+        </is>
+      </c>
       <c r="O121" t="n">
         <v>0</v>
       </c>
@@ -19046,7 +19198,11 @@
         <v>0</v>
       </c>
       <c r="V121" t="inlineStr"/>
-      <c r="W121" t="inlineStr"/>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6004/656582/4639ac5e-67d5-489e-9d2a-2987974c0636.jpg</t>
+        </is>
+      </c>
       <c r="X121" t="n">
         <v>0</v>
       </c>
@@ -19480,7 +19636,11 @@
         <v>161219</v>
       </c>
       <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>1781997153793</t>
+        </is>
+      </c>
       <c r="O124" t="n">
         <v>0</v>
       </c>
@@ -19501,7 +19661,11 @@
         <v>0</v>
       </c>
       <c r="V124" t="inlineStr"/>
-      <c r="W124" t="inlineStr"/>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6004/656585/5a045da9-1013-4db8-8d92-9493c198873b.jpg</t>
+        </is>
+      </c>
       <c r="X124" t="n">
         <v>0</v>
       </c>
@@ -31397,7 +31561,11 @@
         <v>161244</v>
       </c>
       <c r="M201" t="inlineStr"/>
-      <c r="N201" t="inlineStr"/>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>1781996017191</t>
+        </is>
+      </c>
       <c r="O201" t="n">
         <v>0</v>
       </c>
@@ -31418,7 +31586,11 @@
         <v>0</v>
       </c>
       <c r="V201" t="inlineStr"/>
-      <c r="W201" t="inlineStr"/>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6009/656630/1393a230-480a-478a-b3a5-0f5dcf1886cc.jpg</t>
+        </is>
+      </c>
       <c r="X201" t="n">
         <v>0</v>
       </c>
@@ -32472,7 +32644,11 @@
         <v>87290</v>
       </c>
       <c r="M208" t="inlineStr"/>
-      <c r="N208" t="inlineStr"/>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>1781997421314</t>
+        </is>
+      </c>
       <c r="O208" t="n">
         <v>0</v>
       </c>
@@ -32493,7 +32669,11 @@
         <v>0</v>
       </c>
       <c r="V208" t="inlineStr"/>
-      <c r="W208" t="inlineStr"/>
+      <c r="W208" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6118/86201/2c228243-3877-4597-9983-b6db09207222.jpg</t>
+        </is>
+      </c>
       <c r="X208" t="n">
         <v>0</v>
       </c>
@@ -33390,7 +33570,11 @@
         <v>162701</v>
       </c>
       <c r="M214" t="inlineStr"/>
-      <c r="N214" t="inlineStr"/>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>1781997063577</t>
+        </is>
+      </c>
       <c r="O214" t="n">
         <v>0</v>
       </c>
@@ -33411,7 +33595,11 @@
         <v>0</v>
       </c>
       <c r="V214" t="inlineStr"/>
-      <c r="W214" t="inlineStr"/>
+      <c r="W214" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6118/657883/5218bae5-0620-44fa-8fab-8644ad9346ef.jpg</t>
+        </is>
+      </c>
       <c r="X214" t="n">
         <v>0</v>
       </c>
@@ -33853,7 +34041,11 @@
         <v>162704</v>
       </c>
       <c r="M217" t="inlineStr"/>
-      <c r="N217" t="inlineStr"/>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>1781997041009</t>
+        </is>
+      </c>
       <c r="O217" t="n">
         <v>0</v>
       </c>
@@ -33874,7 +34066,11 @@
         <v>0</v>
       </c>
       <c r="V217" t="inlineStr"/>
-      <c r="W217" t="inlineStr"/>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6118/657886/1ba6bc74-0223-4f09-a19a-881a49b730e5.jpg</t>
+        </is>
+      </c>
       <c r="X217" t="n">
         <v>0</v>
       </c>
@@ -35508,7 +35704,11 @@
         <v>162689</v>
       </c>
       <c r="M228" t="inlineStr"/>
-      <c r="N228" t="inlineStr"/>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>1781997931989</t>
+        </is>
+      </c>
       <c r="O228" t="n">
         <v>0</v>
       </c>
@@ -35529,7 +35729,11 @@
         <v>0</v>
       </c>
       <c r="V228" t="inlineStr"/>
-      <c r="W228" t="inlineStr"/>
+      <c r="W228" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6116/657891/83c425a4-1ff0-4202-acb8-655818219a2e.jpg</t>
+        </is>
+      </c>
       <c r="X228" t="n">
         <v>0</v>
       </c>
@@ -38959,7 +39163,11 @@
         <v>162700</v>
       </c>
       <c r="M251" t="inlineStr"/>
-      <c r="N251" t="inlineStr"/>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>1781999896507</t>
+        </is>
+      </c>
       <c r="O251" t="n">
         <v>0</v>
       </c>
@@ -38980,7 +39188,11 @@
         <v>0</v>
       </c>
       <c r="V251" t="inlineStr"/>
-      <c r="W251" t="inlineStr"/>
+      <c r="W251" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6117/657902/9b25333f-a919-47cd-aba3-d09a0a97982d.jpg</t>
+        </is>
+      </c>
       <c r="X251" t="n">
         <v>0</v>
       </c>
@@ -39265,7 +39477,11 @@
         <v>87259</v>
       </c>
       <c r="M253" t="inlineStr"/>
-      <c r="N253" t="inlineStr"/>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>1781998289858</t>
+        </is>
+      </c>
       <c r="O253" t="n">
         <v>0</v>
       </c>
@@ -39286,7 +39502,11 @@
         <v>0</v>
       </c>
       <c r="V253" t="inlineStr"/>
-      <c r="W253" t="inlineStr"/>
+      <c r="W253" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6114/86170/6d055022-6869-491c-a179-abc7cb47bfec.jpg</t>
+        </is>
+      </c>
       <c r="X253" t="n">
         <v>0</v>
       </c>
@@ -39414,7 +39634,11 @@
         <v>87260</v>
       </c>
       <c r="M254" t="inlineStr"/>
-      <c r="N254" t="inlineStr"/>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>1781998828399</t>
+        </is>
+      </c>
       <c r="O254" t="n">
         <v>0</v>
       </c>
@@ -39435,7 +39659,11 @@
         <v>0</v>
       </c>
       <c r="V254" t="inlineStr"/>
-      <c r="W254" t="inlineStr"/>
+      <c r="W254" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6114/86171/24fc3b81-d595-47a3-aa2a-e3b72cf51f08.jpg</t>
+        </is>
+      </c>
       <c r="X254" t="n">
         <v>0</v>
       </c>
@@ -40489,7 +40717,11 @@
         <v>162665</v>
       </c>
       <c r="M261" t="inlineStr"/>
-      <c r="N261" t="inlineStr"/>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>1782002353400</t>
+        </is>
+      </c>
       <c r="O261" t="n">
         <v>0</v>
       </c>
@@ -40510,7 +40742,11 @@
         <v>0</v>
       </c>
       <c r="V261" t="inlineStr"/>
-      <c r="W261" t="inlineStr"/>
+      <c r="W261" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6114/657907/67a35f8c-dfd1-441c-bf63-0cc4a07bf267.jpg</t>
+        </is>
+      </c>
       <c r="X261" t="n">
         <v>0</v>
       </c>
@@ -41878,7 +42114,11 @@
         <v>87193</v>
       </c>
       <c r="M270" t="inlineStr"/>
-      <c r="N270" t="inlineStr"/>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>1782000830591</t>
+        </is>
+      </c>
       <c r="O270" t="n">
         <v>0</v>
       </c>
@@ -41899,7 +42139,11 @@
         <v>0</v>
       </c>
       <c r="V270" t="inlineStr"/>
-      <c r="W270" t="inlineStr"/>
+      <c r="W270" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6107/86104/3d0a0d51-7127-45fe-8db5-eae83b5ab018.jpg</t>
+        </is>
+      </c>
       <c r="X270" t="n">
         <v>0</v>
       </c>
@@ -43533,7 +43777,11 @@
         <v>162623</v>
       </c>
       <c r="M281" t="inlineStr"/>
-      <c r="N281" t="inlineStr"/>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>1781997492024</t>
+        </is>
+      </c>
       <c r="O281" t="n">
         <v>0</v>
       </c>
@@ -43554,7 +43802,11 @@
         <v>0</v>
       </c>
       <c r="V281" t="inlineStr"/>
-      <c r="W281" t="inlineStr"/>
+      <c r="W281" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6107/657873/a5818a90-787f-4bb1-8fad-7fcd4679775b.jpg</t>
+        </is>
+      </c>
       <c r="X281" t="n">
         <v>0</v>
       </c>
@@ -45486,7 +45738,11 @@
         <v>87256</v>
       </c>
       <c r="M294" t="inlineStr"/>
-      <c r="N294" t="inlineStr"/>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>1782006313284</t>
+        </is>
+      </c>
       <c r="O294" t="n">
         <v>0</v>
       </c>
@@ -45507,7 +45763,11 @@
         <v>0</v>
       </c>
       <c r="V294" t="inlineStr"/>
-      <c r="W294" t="inlineStr"/>
+      <c r="W294" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6113/86167/91ba7389-a0e8-4068-acb4-eed6b47e4d70.jpg</t>
+        </is>
+      </c>
       <c r="X294" t="n">
         <v>0</v>
       </c>
@@ -45784,7 +46044,11 @@
         <v>162654</v>
       </c>
       <c r="M296" t="inlineStr"/>
-      <c r="N296" t="inlineStr"/>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>1782006174794</t>
+        </is>
+      </c>
       <c r="O296" t="n">
         <v>0</v>
       </c>
@@ -45805,7 +46069,11 @@
         <v>0</v>
       </c>
       <c r="V296" t="inlineStr"/>
-      <c r="W296" t="inlineStr"/>
+      <c r="W296" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6113/657914/a663bb9e-6af5-4c70-a9e2-f2db32c2f011.jpg</t>
+        </is>
+      </c>
       <c r="X296" t="n">
         <v>0</v>
       </c>
@@ -46239,7 +46507,11 @@
         <v>162657</v>
       </c>
       <c r="M299" t="inlineStr"/>
-      <c r="N299" t="inlineStr"/>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>1782006715296</t>
+        </is>
+      </c>
       <c r="O299" t="n">
         <v>0</v>
       </c>
@@ -46260,7 +46532,11 @@
         <v>0</v>
       </c>
       <c r="V299" t="inlineStr"/>
-      <c r="W299" t="inlineStr"/>
+      <c r="W299" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6113/657917/07cf26f0-9bfa-4848-b318-6fd8637c8bab.jpg</t>
+        </is>
+      </c>
       <c r="X299" t="n">
         <v>0</v>
       </c>
@@ -49661,7 +49937,11 @@
         <v>87236</v>
       </c>
       <c r="M321" t="inlineStr"/>
-      <c r="N321" t="inlineStr"/>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>1782002099890</t>
+        </is>
+      </c>
       <c r="O321" t="n">
         <v>0</v>
       </c>
@@ -49682,7 +49962,11 @@
         <v>0</v>
       </c>
       <c r="V321" t="inlineStr"/>
-      <c r="W321" t="inlineStr"/>
+      <c r="W321" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6111/86147/033f896f-fdce-4554-b4c9-5066d78c31dd.jpg</t>
+        </is>
+      </c>
       <c r="X321" t="n">
         <v>0</v>
       </c>
@@ -51026,7 +51310,11 @@
         <v>87228</v>
       </c>
       <c r="M330" t="inlineStr"/>
-      <c r="N330" t="inlineStr"/>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>1781999707208</t>
+        </is>
+      </c>
       <c r="O330" t="n">
         <v>0</v>
       </c>
@@ -51047,7 +51335,11 @@
         <v>0</v>
       </c>
       <c r="V330" t="inlineStr"/>
-      <c r="W330" t="inlineStr"/>
+      <c r="W330" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6110/86139/d01c3db4-02b1-4404-9065-d16a0b06eea5.jpg</t>
+        </is>
+      </c>
       <c r="X330" t="n">
         <v>0</v>
       </c>
@@ -51175,7 +51467,11 @@
         <v>87229</v>
       </c>
       <c r="M331" t="inlineStr"/>
-      <c r="N331" t="inlineStr"/>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>1781998947382</t>
+        </is>
+      </c>
       <c r="O331" t="n">
         <v>0</v>
       </c>
@@ -51196,7 +51492,11 @@
         <v>0</v>
       </c>
       <c r="V331" t="inlineStr"/>
-      <c r="W331" t="inlineStr"/>
+      <c r="W331" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6110/86140/03624c18-351c-4799-9de1-c4116427641c.jpg</t>
+        </is>
+      </c>
       <c r="X331" t="n">
         <v>0</v>
       </c>
@@ -51324,7 +51624,11 @@
         <v>87230</v>
       </c>
       <c r="M332" t="inlineStr"/>
-      <c r="N332" t="inlineStr"/>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>1781999464164</t>
+        </is>
+      </c>
       <c r="O332" t="n">
         <v>0</v>
       </c>
@@ -51345,7 +51649,11 @@
         <v>0</v>
       </c>
       <c r="V332" t="inlineStr"/>
-      <c r="W332" t="inlineStr"/>
+      <c r="W332" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6110/86141/27b3a5e7-bbfe-4a6a-8554-85a140e890ec.jpg</t>
+        </is>
+      </c>
       <c r="X332" t="n">
         <v>0</v>
       </c>
@@ -52532,7 +52840,11 @@
         <v>162646</v>
       </c>
       <c r="M340" t="inlineStr"/>
-      <c r="N340" t="inlineStr"/>
+      <c r="N340" t="inlineStr">
+        <is>
+          <t>1781998561307</t>
+        </is>
+      </c>
       <c r="O340" t="n">
         <v>0</v>
       </c>
@@ -52553,7 +52865,11 @@
         <v>0</v>
       </c>
       <c r="V340" t="inlineStr"/>
-      <c r="W340" t="inlineStr"/>
+      <c r="W340" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/534/6110/657929/781b644f-22fa-43ae-9d30-142f5210e97d.jpg</t>
+        </is>
+      </c>
       <c r="X340" t="n">
         <v>0</v>
       </c>
@@ -74474,7 +74790,11 @@
         <v>87607</v>
       </c>
       <c r="M484" t="inlineStr"/>
-      <c r="N484" t="inlineStr"/>
+      <c r="N484" t="inlineStr">
+        <is>
+          <t>1782019944197</t>
+        </is>
+      </c>
       <c r="O484" t="n">
         <v>0</v>
       </c>
@@ -74495,7 +74815,11 @@
         <v>0</v>
       </c>
       <c r="V484" t="inlineStr"/>
-      <c r="W484" t="inlineStr"/>
+      <c r="W484" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6150/86518/fecc3d7f-434a-476c-adb2-679828b8ee3a.jpg</t>
+        </is>
+      </c>
       <c r="X484" t="n">
         <v>0</v>
       </c>
@@ -74623,7 +74947,11 @@
         <v>87608</v>
       </c>
       <c r="M485" t="inlineStr"/>
-      <c r="N485" t="inlineStr"/>
+      <c r="N485" t="inlineStr">
+        <is>
+          <t>1782020667095</t>
+        </is>
+      </c>
       <c r="O485" t="n">
         <v>0</v>
       </c>
@@ -74644,7 +74972,11 @@
         <v>0</v>
       </c>
       <c r="V485" t="inlineStr"/>
-      <c r="W485" t="inlineStr"/>
+      <c r="W485" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6150/86519/06061cac-e2f3-4c5f-90d6-821772caf9eb.jpg</t>
+        </is>
+      </c>
       <c r="X485" t="n">
         <v>0</v>
       </c>
@@ -74772,7 +75104,11 @@
         <v>87609</v>
       </c>
       <c r="M486" t="inlineStr"/>
-      <c r="N486" t="inlineStr"/>
+      <c r="N486" t="inlineStr">
+        <is>
+          <t>1782020533727</t>
+        </is>
+      </c>
       <c r="O486" t="n">
         <v>0</v>
       </c>
@@ -74793,7 +75129,11 @@
         <v>0</v>
       </c>
       <c r="V486" t="inlineStr"/>
-      <c r="W486" t="inlineStr"/>
+      <c r="W486" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6150/86520/c06477a5-9236-4256-8842-c2370ab136f2.jpg</t>
+        </is>
+      </c>
       <c r="X486" t="n">
         <v>0</v>
       </c>
@@ -75368,7 +75708,11 @@
         <v>162966</v>
       </c>
       <c r="M490" t="inlineStr"/>
-      <c r="N490" t="inlineStr"/>
+      <c r="N490" t="inlineStr">
+        <is>
+          <t>1782019934072</t>
+        </is>
+      </c>
       <c r="O490" t="n">
         <v>0</v>
       </c>
@@ -75389,7 +75733,11 @@
         <v>0</v>
       </c>
       <c r="V490" t="inlineStr"/>
-      <c r="W490" t="inlineStr"/>
+      <c r="W490" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6150/658212/84bd80c1-95b0-4d37-9a17-f8fce7f7e7d9.jpg</t>
+        </is>
+      </c>
       <c r="X490" t="n">
         <v>0</v>
       </c>
@@ -75517,7 +75865,11 @@
         <v>162967</v>
       </c>
       <c r="M491" t="inlineStr"/>
-      <c r="N491" t="inlineStr"/>
+      <c r="N491" t="inlineStr">
+        <is>
+          <t>1782018923840</t>
+        </is>
+      </c>
       <c r="O491" t="n">
         <v>0</v>
       </c>
@@ -75538,7 +75890,11 @@
         <v>0</v>
       </c>
       <c r="V491" t="inlineStr"/>
-      <c r="W491" t="inlineStr"/>
+      <c r="W491" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6150/658213/671c3014-7cc7-42d4-9902-e556a170852e.jpg</t>
+        </is>
+      </c>
       <c r="X491" t="n">
         <v>0</v>
       </c>
@@ -76904,7 +77260,11 @@
         <v>87601</v>
       </c>
       <c r="M500" t="inlineStr"/>
-      <c r="N500" t="inlineStr"/>
+      <c r="N500" t="inlineStr">
+        <is>
+          <t>1781994570748</t>
+        </is>
+      </c>
       <c r="O500" t="n">
         <v>0</v>
       </c>
@@ -76925,7 +77285,11 @@
         <v>0</v>
       </c>
       <c r="V500" t="inlineStr"/>
-      <c r="W500" t="inlineStr"/>
+      <c r="W500" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6149/86512/37a1ddeb-a64e-4f66-9a4b-71c1a7231a53.jpg</t>
+        </is>
+      </c>
       <c r="X500" t="n">
         <v>0</v>
       </c>
@@ -77665,7 +78029,11 @@
         <v>162955</v>
       </c>
       <c r="M505" t="inlineStr"/>
-      <c r="N505" t="inlineStr"/>
+      <c r="N505" t="inlineStr">
+        <is>
+          <t>1781993539959</t>
+        </is>
+      </c>
       <c r="O505" t="n">
         <v>0</v>
       </c>
@@ -77686,7 +78054,11 @@
         <v>0</v>
       </c>
       <c r="V505" t="inlineStr"/>
-      <c r="W505" t="inlineStr"/>
+      <c r="W505" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6149/658217/d172fdd7-eb0c-4980-9282-152078599505.jpg</t>
+        </is>
+      </c>
       <c r="X505" t="n">
         <v>0</v>
       </c>
@@ -77814,7 +78186,11 @@
         <v>162956</v>
       </c>
       <c r="M506" t="inlineStr"/>
-      <c r="N506" t="inlineStr"/>
+      <c r="N506" t="inlineStr">
+        <is>
+          <t>1781994931002</t>
+        </is>
+      </c>
       <c r="O506" t="n">
         <v>0</v>
       </c>
@@ -77835,7 +78211,11 @@
         <v>0</v>
       </c>
       <c r="V506" t="inlineStr"/>
-      <c r="W506" t="inlineStr"/>
+      <c r="W506" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6149/658218/87bf7669-6891-4021-bcfa-d96ab1c37cfa.jpg</t>
+        </is>
+      </c>
       <c r="X506" t="n">
         <v>0</v>
       </c>
@@ -78120,7 +78500,11 @@
         <v>162958</v>
       </c>
       <c r="M508" t="inlineStr"/>
-      <c r="N508" t="inlineStr"/>
+      <c r="N508" t="inlineStr">
+        <is>
+          <t>1781994948955</t>
+        </is>
+      </c>
       <c r="O508" t="n">
         <v>0</v>
       </c>
@@ -78141,7 +78525,11 @@
         <v>0</v>
       </c>
       <c r="V508" t="inlineStr"/>
-      <c r="W508" t="inlineStr"/>
+      <c r="W508" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6149/658220/5e266a6c-08c4-4757-944e-58b5d0ae7e42.jpg</t>
+        </is>
+      </c>
       <c r="X508" t="n">
         <v>0</v>
       </c>
@@ -78269,7 +78657,11 @@
         <v>162959</v>
       </c>
       <c r="M509" t="inlineStr"/>
-      <c r="N509" t="inlineStr"/>
+      <c r="N509" t="inlineStr">
+        <is>
+          <t>1781994956082</t>
+        </is>
+      </c>
       <c r="O509" t="n">
         <v>0</v>
       </c>
@@ -78290,7 +78682,11 @@
         <v>0</v>
       </c>
       <c r="V509" t="inlineStr"/>
-      <c r="W509" t="inlineStr"/>
+      <c r="W509" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6149/658221/66e55ae5-839f-4e8c-851d-5d13d4bc5e9c.jpg</t>
+        </is>
+      </c>
       <c r="X509" t="n">
         <v>0</v>
       </c>
@@ -78418,7 +78814,11 @@
         <v>162960</v>
       </c>
       <c r="M510" t="inlineStr"/>
-      <c r="N510" t="inlineStr"/>
+      <c r="N510" t="inlineStr">
+        <is>
+          <t>1781994951015</t>
+        </is>
+      </c>
       <c r="O510" t="n">
         <v>0</v>
       </c>
@@ -78439,7 +78839,11 @@
         <v>0</v>
       </c>
       <c r="V510" t="inlineStr"/>
-      <c r="W510" t="inlineStr"/>
+      <c r="W510" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6149/658222/e2f88b6c-bf11-4570-84b2-1b9755d8a77e.jpg</t>
+        </is>
+      </c>
       <c r="X510" t="n">
         <v>0</v>
       </c>
@@ -78567,7 +78971,11 @@
         <v>162961</v>
       </c>
       <c r="M511" t="inlineStr"/>
-      <c r="N511" t="inlineStr"/>
+      <c r="N511" t="inlineStr">
+        <is>
+          <t>1781994976933</t>
+        </is>
+      </c>
       <c r="O511" t="n">
         <v>0</v>
       </c>
@@ -78588,7 +78996,11 @@
         <v>0</v>
       </c>
       <c r="V511" t="inlineStr"/>
-      <c r="W511" t="inlineStr"/>
+      <c r="W511" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6149/658223/a26be436-8dc0-4305-ba36-c43ea3e44caa.jpg</t>
+        </is>
+      </c>
       <c r="X511" t="n">
         <v>0</v>
       </c>
@@ -78716,7 +79128,11 @@
         <v>162962</v>
       </c>
       <c r="M512" t="inlineStr"/>
-      <c r="N512" t="inlineStr"/>
+      <c r="N512" t="inlineStr">
+        <is>
+          <t>1781994958718</t>
+        </is>
+      </c>
       <c r="O512" t="n">
         <v>0</v>
       </c>
@@ -78737,7 +79153,11 @@
         <v>0</v>
       </c>
       <c r="V512" t="inlineStr"/>
-      <c r="W512" t="inlineStr"/>
+      <c r="W512" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6149/658224/528237ae-c023-42f3-81d0-188e7efdef6d.jpg</t>
+        </is>
+      </c>
       <c r="X512" t="n">
         <v>0</v>
       </c>
@@ -84336,7 +84756,11 @@
         <v>162950</v>
       </c>
       <c r="M548" t="inlineStr"/>
-      <c r="N548" t="inlineStr"/>
+      <c r="N548" t="inlineStr">
+        <is>
+          <t>1781999709723</t>
+        </is>
+      </c>
       <c r="O548" t="n">
         <v>0</v>
       </c>
@@ -84357,7 +84781,11 @@
         <v>0</v>
       </c>
       <c r="V548" t="inlineStr"/>
-      <c r="W548" t="inlineStr"/>
+      <c r="W548" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/536/6148/658239/201a70b6-dc41-493f-b4e4-01533ec83503.jpg</t>
+        </is>
+      </c>
       <c r="X548" t="n">
         <v>0</v>
       </c>
@@ -90018,172 +90446,172 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>LGA</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Ward</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Polling Units</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>INEC Uploaded Results</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>INEC Upload Percent</t>
         </is>
@@ -90293,10 +90721,10 @@
         <v>12</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="3">
@@ -90513,10 +90941,10 @@
         <v>46</v>
       </c>
       <c r="AG4" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AH4" t="n">
-        <v>69.59999999999999</v>
+        <v>91.3</v>
       </c>
     </row>
     <row r="5">
@@ -90733,10 +91161,10 @@
         <v>17</v>
       </c>
       <c r="AG6" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AH6" t="n">
-        <v>47.1</v>
+        <v>94.09999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -91394,10 +91822,10 @@
         <v>12</v>
       </c>
       <c r="AG12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH12" t="n">
-        <v>75</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="13">
@@ -91504,10 +91932,10 @@
         <v>10</v>
       </c>
       <c r="AG13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AH13" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14">
@@ -91614,10 +92042,10 @@
         <v>12</v>
       </c>
       <c r="AG14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH14" t="n">
-        <v>16.7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
@@ -91724,10 +92152,10 @@
         <v>22</v>
       </c>
       <c r="AG15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH15" t="n">
-        <v>13.6</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="16">
@@ -91834,10 +92262,10 @@
         <v>16</v>
       </c>
       <c r="AG16" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AH16" t="n">
-        <v>68.8</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="17">
@@ -91944,10 +92372,10 @@
         <v>19</v>
       </c>
       <c r="AG17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AH17" t="n">
-        <v>21.1</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="18">
@@ -92054,10 +92482,10 @@
         <v>16</v>
       </c>
       <c r="AG18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AH18" t="n">
-        <v>12.5</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="19">
@@ -92274,10 +92702,10 @@
         <v>8</v>
       </c>
       <c r="AG20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH20" t="n">
-        <v>75</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="21">
@@ -92384,10 +92812,10 @@
         <v>15</v>
       </c>
       <c r="AG21" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AH21" t="n">
-        <v>13.3</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22">
@@ -93264,10 +93692,10 @@
         <v>9</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="30">
@@ -93484,10 +93912,10 @@
         <v>14</v>
       </c>
       <c r="AG31" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AH31" t="n">
-        <v>28.6</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="32">
@@ -93814,10 +94242,10 @@
         <v>17</v>
       </c>
       <c r="AG34" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH34" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35">
@@ -94055,167 +94483,167 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>LGA</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Polling Units</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>INEC Uploaded Results</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>INEC Upload Percent</t>
         </is>
@@ -94320,10 +94748,10 @@
         <v>206</v>
       </c>
       <c r="AF2" t="n">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="AG2" t="n">
-        <v>63.6</v>
+        <v>74.8</v>
       </c>
     </row>
     <row r="3">
@@ -94425,10 +94853,10 @@
         <v>255</v>
       </c>
       <c r="AF3" t="n">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="AG3" t="n">
-        <v>36.5</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="4">
@@ -94530,10 +94958,10 @@
         <v>122</v>
       </c>
       <c r="AF4" t="n">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="AG4" t="n">
-        <v>67.2</v>
+        <v>78.7</v>
       </c>
     </row>
   </sheetData>
@@ -94551,167 +94979,167 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Polling Units</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>INEC Uploaded Results</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>INEC Expected Results</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>INEC Upload Percent</t>
         </is>
@@ -94811,13 +95239,13 @@
         <v>583</v>
       </c>
       <c r="AE2" t="n">
-        <v>306</v>
+        <v>361</v>
       </c>
       <c r="AF2" t="n">
         <v>583</v>
       </c>
       <c r="AG2" t="n">
-        <v>52.5</v>
+        <v>61.9</v>
       </c>
     </row>
   </sheetData>

--- a/output/Nasarawa/results.xlsx
+++ b/output/Nasarawa/results.xlsx
@@ -20,13 +20,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,227 +432,227 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>LGA</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Election ID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Election Name</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Election Date</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Ward</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Ward Code</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Ward ID</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Polling Unit</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>PU Code</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>PU ID</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Polling Unit ID</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Result Updated Time</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Session</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Result Info PU</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Image File</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Image URL</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
@@ -90446,172 +90458,172 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>LGA</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Ward</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Polling Units</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>INEC Uploaded Results</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>INEC Upload Percent</t>
         </is>
@@ -94483,167 +94495,167 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>LGA</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Polling Units</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>INEC Uploaded Results</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>INEC Upload Percent</t>
         </is>
@@ -94979,167 +94991,167 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Polling Units</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>INEC Uploaded Results</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>INEC Expected Results</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>INEC Upload Percent</t>
         </is>

--- a/output/Nasarawa/results.xlsx
+++ b/output/Nasarawa/results.xlsx
@@ -20,16 +20,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,227 +420,227 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>LGA</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Election ID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Election Name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Election Date</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Ward</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Ward Code</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Ward ID</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Polling Unit</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>PU Code</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>PU ID</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Polling Unit ID</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Result Updated Time</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Session</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Result Info PU</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Image File</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Image URL</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
@@ -28678,7 +28666,11 @@
         <v>161269</v>
       </c>
       <c r="M182" t="inlineStr"/>
-      <c r="N182" t="inlineStr"/>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>1782066613289</t>
+        </is>
+      </c>
       <c r="O182" t="n">
         <v>0</v>
       </c>
@@ -28699,7 +28691,11 @@
         <v>0</v>
       </c>
       <c r="V182" t="inlineStr"/>
-      <c r="W182" t="inlineStr"/>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2987/26/526/6011/656628/15b8fa6e-e9bf-4dd6-892d-c161bef01a84.jpg</t>
+        </is>
+      </c>
       <c r="X182" t="n">
         <v>0</v>
       </c>
@@ -90458,172 +90454,172 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>LGA</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Ward</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Polling Units</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>INEC Uploaded Results</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>INEC Upload Percent</t>
         </is>
@@ -91614,10 +91610,10 @@
         <v>17</v>
       </c>
       <c r="AG10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>58.8</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="11">
@@ -94495,167 +94491,167 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>LGA</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Polling Units</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>INEC Uploaded Results</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>INEC Upload Percent</t>
         </is>
@@ -94760,10 +94756,10 @@
         <v>206</v>
       </c>
       <c r="AF2" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG2" t="n">
-        <v>74.8</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="3">
@@ -94991,167 +94987,167 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Polling Units</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>INEC Uploaded Results</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>INEC Expected Results</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>INEC Upload Percent</t>
         </is>
@@ -95251,13 +95247,13 @@
         <v>583</v>
       </c>
       <c r="AE2" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AF2" t="n">
         <v>583</v>
       </c>
       <c r="AG2" t="n">
-        <v>61.9</v>
+        <v>62.1</v>
       </c>
     </row>
   </sheetData>

--- a/output/Nasarawa/results.xlsx
+++ b/output/Nasarawa/results.xlsx
@@ -94756,10 +94756,10 @@
         <v>206</v>
       </c>
       <c r="AF2" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>75.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -94861,10 +94861,10 @@
         <v>255</v>
       </c>
       <c r="AF3" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>43.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -94966,10 +94966,10 @@
         <v>122</v>
       </c>
       <c r="AF4" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>78.7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -95247,13 +95247,13 @@
         <v>583</v>
       </c>
       <c r="AE2" t="n">
-        <v>362</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
         <v>583</v>
       </c>
       <c r="AG2" t="n">
-        <v>62.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/Nasarawa/results.xlsx
+++ b/output/Nasarawa/results.xlsx
@@ -94756,10 +94756,10 @@
         <v>206</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="3">
@@ -94861,10 +94861,10 @@
         <v>255</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="4">
@@ -94966,10 +94966,10 @@
         <v>122</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>78.7</v>
       </c>
     </row>
   </sheetData>
@@ -95247,13 +95247,13 @@
         <v>583</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>362</v>
       </c>
       <c r="AF2" t="n">
         <v>583</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>62.1</v>
       </c>
     </row>
   </sheetData>

--- a/output/Nasarawa/results.xlsx
+++ b/output/Nasarawa/results.xlsx
@@ -91940,10 +91940,10 @@
         <v>10</v>
       </c>
       <c r="AG13" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -92050,10 +92050,10 @@
         <v>12</v>
       </c>
       <c r="AG14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -92160,10 +92160,10 @@
         <v>22</v>
       </c>
       <c r="AG15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>18.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -92270,10 +92270,10 @@
         <v>16</v>
       </c>
       <c r="AG16" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>87.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -92380,10 +92380,10 @@
         <v>19</v>
       </c>
       <c r="AG17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>31.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -92490,10 +92490,10 @@
         <v>16</v>
       </c>
       <c r="AG18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>31.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -92600,10 +92600,10 @@
         <v>15</v>
       </c>
       <c r="AG19" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>93.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -92710,10 +92710,10 @@
         <v>8</v>
       </c>
       <c r="AG20" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>87.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -92820,10 +92820,10 @@
         <v>15</v>
       </c>
       <c r="AG21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -92930,10 +92930,10 @@
         <v>17</v>
       </c>
       <c r="AG22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>29.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -93040,10 +93040,10 @@
         <v>50</v>
       </c>
       <c r="AG23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -93150,10 +93150,10 @@
         <v>14</v>
       </c>
       <c r="AG24" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -93260,10 +93260,10 @@
         <v>19</v>
       </c>
       <c r="AG25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>21.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -93370,10 +93370,10 @@
         <v>22</v>
       </c>
       <c r="AG26" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>90.90000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">

--- a/output/Nasarawa/results.xlsx
+++ b/output/Nasarawa/results.xlsx
@@ -91940,10 +91940,10 @@
         <v>10</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14">
@@ -92050,10 +92050,10 @@
         <v>12</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
@@ -92160,10 +92160,10 @@
         <v>22</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="16">
@@ -92270,10 +92270,10 @@
         <v>16</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="17">
@@ -92380,10 +92380,10 @@
         <v>19</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="18">
@@ -92490,10 +92490,10 @@
         <v>16</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="19">
@@ -92600,10 +92600,10 @@
         <v>15</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="20">
@@ -92710,10 +92710,10 @@
         <v>8</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="21">
@@ -92820,10 +92820,10 @@
         <v>15</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22">
@@ -92930,10 +92930,10 @@
         <v>17</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="23">
@@ -93040,10 +93040,10 @@
         <v>50</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -93150,10 +93150,10 @@
         <v>14</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25">
@@ -93260,10 +93260,10 @@
         <v>19</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="26">
@@ -93370,10 +93370,10 @@
         <v>22</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="27">

--- a/output/Nasarawa/results.xlsx
+++ b/output/Nasarawa/results.xlsx
@@ -90729,10 +90729,10 @@
         <v>12</v>
       </c>
       <c r="AG2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -90839,10 +90839,10 @@
         <v>40</v>
       </c>
       <c r="AG3" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -90949,10 +90949,10 @@
         <v>46</v>
       </c>
       <c r="AG4" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>91.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -91059,10 +91059,10 @@
         <v>10</v>
       </c>
       <c r="AG5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -91169,10 +91169,10 @@
         <v>17</v>
       </c>
       <c r="AG6" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>94.09999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -91279,10 +91279,10 @@
         <v>14</v>
       </c>
       <c r="AG7" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>92.90000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -91389,10 +91389,10 @@
         <v>14</v>
       </c>
       <c r="AG8" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -91500,10 +91500,10 @@
         <v>12</v>
       </c>
       <c r="AG9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>58.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -91610,10 +91610,10 @@
         <v>17</v>
       </c>
       <c r="AG10" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>64.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -91720,10 +91720,10 @@
         <v>12</v>
       </c>
       <c r="AG11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -91830,10 +91830,10 @@
         <v>12</v>
       </c>
       <c r="AG12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>83.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">

--- a/output/Nasarawa/results.xlsx
+++ b/output/Nasarawa/results.xlsx
@@ -90729,10 +90729,10 @@
         <v>12</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="3">
@@ -90839,10 +90839,10 @@
         <v>40</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4">
@@ -90949,10 +90949,10 @@
         <v>46</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>91.3</v>
       </c>
     </row>
     <row r="5">
@@ -91059,10 +91059,10 @@
         <v>10</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6">
@@ -91169,10 +91169,10 @@
         <v>17</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>94.09999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -91279,10 +91279,10 @@
         <v>14</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -91389,10 +91389,10 @@
         <v>14</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">
@@ -91500,10 +91500,10 @@
         <v>12</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="10">
@@ -91610,10 +91610,10 @@
         <v>17</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="11">
@@ -91720,10 +91720,10 @@
         <v>12</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12">
@@ -91830,10 +91830,10 @@
         <v>12</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="13">

--- a/output/Nasarawa/results.xlsx
+++ b/output/Nasarawa/results.xlsx
@@ -91940,10 +91940,10 @@
         <v>10</v>
       </c>
       <c r="AG13" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -92050,10 +92050,10 @@
         <v>12</v>
       </c>
       <c r="AG14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -92160,10 +92160,10 @@
         <v>22</v>
       </c>
       <c r="AG15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>18.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -92270,10 +92270,10 @@
         <v>16</v>
       </c>
       <c r="AG16" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>87.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -92380,10 +92380,10 @@
         <v>19</v>
       </c>
       <c r="AG17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>31.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -92490,10 +92490,10 @@
         <v>16</v>
       </c>
       <c r="AG18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>31.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -92600,10 +92600,10 @@
         <v>15</v>
       </c>
       <c r="AG19" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>93.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -92710,10 +92710,10 @@
         <v>8</v>
       </c>
       <c r="AG20" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>87.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -92820,10 +92820,10 @@
         <v>15</v>
       </c>
       <c r="AG21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -92930,10 +92930,10 @@
         <v>17</v>
       </c>
       <c r="AG22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>29.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -93040,10 +93040,10 @@
         <v>50</v>
       </c>
       <c r="AG23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -93150,10 +93150,10 @@
         <v>14</v>
       </c>
       <c r="AG24" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -93260,10 +93260,10 @@
         <v>19</v>
       </c>
       <c r="AG25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>21.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -93370,10 +93370,10 @@
         <v>22</v>
       </c>
       <c r="AG26" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>90.90000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -93480,10 +93480,10 @@
         <v>8</v>
       </c>
       <c r="AG27" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>87.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -93590,10 +93590,10 @@
         <v>12</v>
       </c>
       <c r="AG28" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -93700,10 +93700,10 @@
         <v>9</v>
       </c>
       <c r="AG29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>55.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -93810,10 +93810,10 @@
         <v>7</v>
       </c>
       <c r="AG30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>57.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -93920,10 +93920,10 @@
         <v>14</v>
       </c>
       <c r="AG31" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>85.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -94030,10 +94030,10 @@
         <v>11</v>
       </c>
       <c r="AG32" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>81.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -94140,10 +94140,10 @@
         <v>12</v>
       </c>
       <c r="AG33" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>91.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -94250,10 +94250,10 @@
         <v>17</v>
       </c>
       <c r="AG34" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -94360,10 +94360,10 @@
         <v>19</v>
       </c>
       <c r="AG35" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>94.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -94470,10 +94470,10 @@
         <v>13</v>
       </c>
       <c r="AG36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>30.8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/Nasarawa/results.xlsx
+++ b/output/Nasarawa/results.xlsx
@@ -91940,10 +91940,10 @@
         <v>10</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14">
@@ -92050,10 +92050,10 @@
         <v>12</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
@@ -92160,10 +92160,10 @@
         <v>22</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="16">
@@ -92270,10 +92270,10 @@
         <v>16</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="17">
@@ -92380,10 +92380,10 @@
         <v>19</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="18">
@@ -92490,10 +92490,10 @@
         <v>16</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="19">
@@ -92600,10 +92600,10 @@
         <v>15</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="20">
@@ -92710,10 +92710,10 @@
         <v>8</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="21">
@@ -92820,10 +92820,10 @@
         <v>15</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22">
@@ -92930,10 +92930,10 @@
         <v>17</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="23">
@@ -93040,10 +93040,10 @@
         <v>50</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -93150,10 +93150,10 @@
         <v>14</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25">
@@ -93260,10 +93260,10 @@
         <v>19</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="26">
@@ -93370,10 +93370,10 @@
         <v>22</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -93480,10 +93480,10 @@
         <v>8</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="28">
@@ -93590,10 +93590,10 @@
         <v>12</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29">
@@ -93700,10 +93700,10 @@
         <v>9</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="30">
@@ -93810,10 +93810,10 @@
         <v>7</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="31">
@@ -93920,10 +93920,10 @@
         <v>14</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="32">
@@ -94030,10 +94030,10 @@
         <v>11</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="33">
@@ -94140,10 +94140,10 @@
         <v>12</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="34">
@@ -94250,10 +94250,10 @@
         <v>17</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35">
@@ -94360,10 +94360,10 @@
         <v>19</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>94.7</v>
       </c>
     </row>
     <row r="36">
@@ -94470,10 +94470,10 @@
         <v>13</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>30.8</v>
       </c>
     </row>
   </sheetData>
@@ -94756,10 +94756,10 @@
         <v>206</v>
       </c>
       <c r="AF2" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>75.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -94861,10 +94861,10 @@
         <v>255</v>
       </c>
       <c r="AF3" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>43.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -94966,10 +94966,10 @@
         <v>122</v>
       </c>
       <c r="AF4" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>78.7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -95247,13 +95247,13 @@
         <v>583</v>
       </c>
       <c r="AE2" t="n">
-        <v>362</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
         <v>583</v>
       </c>
       <c r="AG2" t="n">
-        <v>62.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
